--- a/data/coherence.xlsx
+++ b/data/coherence.xlsx
@@ -429,1146 +429,1146 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HT29"/>
+  <dimension ref="A1:HT33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>subject</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>group</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>FP1-FP2</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>FP1-F3</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>FP1-F4</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>FP1-F7</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>FP1-F8</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>FP1-FZ</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>FP1-C3</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>FP1-C4</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>FP1-CZ</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>FP1-T3</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>FP1-T4</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>FP1-T5</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>FP1-T6</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>FP1-P3</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>FP1-P4</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>FP1-PZ</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>FP1-O1</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>FP1-O2</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>FP2-F3</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>FP2-F4</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>FP2-F7</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>FP2-F8</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>FP2-FZ</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>FP2-C3</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>FP2-C4</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>FP2-CZ</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>FP2-T3</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>FP2-T4</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>FP2-T5</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>FP2-T6</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>FP2-P3</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>FP2-P4</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>FP2-PZ</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>FP2-O1</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>FP2-O2</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>F3-F4</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>F3-F7</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>F3-F8</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>F3-FZ</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>F3-C3</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>F3-C4</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>F3-CZ</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>F3-T3</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>F3-T4</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>F3-T5</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>F3-T6</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>F3-P3</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>F3-P4</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>F3-PZ</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>F3-O1</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>F3-O2</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>F4-F7</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>F4-F8</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>F4-FZ</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>F4-C3</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>F4-C4</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>F4-CZ</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>F4-T3</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>F4-T4</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>F4-T5</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>F4-T6</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>F4-P3</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>F4-P4</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>F4-PZ</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>F4-O1</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>F4-O2</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>F7-F8</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>F7-FZ</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>F7-C3</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>F7-C4</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>F7-CZ</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>F7-T3</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>F7-T4</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>F7-T5</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>F7-T6</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>F7-P3</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>F7-P4</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>F7-PZ</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>F7-O1</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>F7-O2</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>F8-FZ</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>F8-C3</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>F8-C4</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>F8-CZ</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>F8-T3</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>F8-T4</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>F8-T5</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>F8-T6</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>F8-P3</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>F8-P4</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>F8-PZ</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>F8-O1</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>F8-O2</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>FZ-C3</t>
         </is>
       </c>
-      <c r="CS1" s="1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>FZ-C4</t>
         </is>
       </c>
-      <c r="CT1" s="1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>FZ-CZ</t>
         </is>
       </c>
-      <c r="CU1" s="1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>FZ-T3</t>
         </is>
       </c>
-      <c r="CV1" s="1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>FZ-T4</t>
         </is>
       </c>
-      <c r="CW1" s="1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>FZ-T5</t>
         </is>
       </c>
-      <c r="CX1" s="1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>FZ-T6</t>
         </is>
       </c>
-      <c r="CY1" s="1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
         <is>
           <t>FZ-P3</t>
         </is>
       </c>
-      <c r="CZ1" s="1" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>FZ-P4</t>
         </is>
       </c>
-      <c r="DA1" s="1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>FZ-PZ</t>
         </is>
       </c>
-      <c r="DB1" s="1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
         <is>
           <t>FZ-O1</t>
         </is>
       </c>
-      <c r="DC1" s="1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
         <is>
           <t>FZ-O2</t>
         </is>
       </c>
-      <c r="DD1" s="1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>C3-C4</t>
         </is>
       </c>
-      <c r="DE1" s="1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>C3-CZ</t>
         </is>
       </c>
-      <c r="DF1" s="1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>C3-T3</t>
         </is>
       </c>
-      <c r="DG1" s="1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>C3-T4</t>
         </is>
       </c>
-      <c r="DH1" s="1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>C3-T5</t>
         </is>
       </c>
-      <c r="DI1" s="1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>C3-T6</t>
         </is>
       </c>
-      <c r="DJ1" s="1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>C3-P3</t>
         </is>
       </c>
-      <c r="DK1" s="1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>C3-P4</t>
         </is>
       </c>
-      <c r="DL1" s="1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>C3-PZ</t>
         </is>
       </c>
-      <c r="DM1" s="1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>C3-O1</t>
         </is>
       </c>
-      <c r="DN1" s="1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>C3-O2</t>
         </is>
       </c>
-      <c r="DO1" s="1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>C4-CZ</t>
         </is>
       </c>
-      <c r="DP1" s="1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>C4-T3</t>
         </is>
       </c>
-      <c r="DQ1" s="1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>C4-T4</t>
         </is>
       </c>
-      <c r="DR1" s="1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>C4-T5</t>
         </is>
       </c>
-      <c r="DS1" s="1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>C4-T6</t>
         </is>
       </c>
-      <c r="DT1" s="1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>C4-P3</t>
         </is>
       </c>
-      <c r="DU1" s="1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>C4-P4</t>
         </is>
       </c>
-      <c r="DV1" s="1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>C4-PZ</t>
         </is>
       </c>
-      <c r="DW1" s="1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>C4-O1</t>
         </is>
       </c>
-      <c r="DX1" s="1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>C4-O2</t>
         </is>
       </c>
-      <c r="DY1" s="1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>CZ-T3</t>
         </is>
       </c>
-      <c r="DZ1" s="1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>CZ-T4</t>
         </is>
       </c>
-      <c r="EA1" s="1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>CZ-T5</t>
         </is>
       </c>
-      <c r="EB1" s="1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>CZ-T6</t>
         </is>
       </c>
-      <c r="EC1" s="1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>CZ-P3</t>
         </is>
       </c>
-      <c r="ED1" s="1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>CZ-P4</t>
         </is>
       </c>
-      <c r="EE1" s="1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>CZ-PZ</t>
         </is>
       </c>
-      <c r="EF1" s="1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>CZ-O1</t>
         </is>
       </c>
-      <c r="EG1" s="1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>CZ-O2</t>
         </is>
       </c>
-      <c r="EH1" s="1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>T3-T4</t>
         </is>
       </c>
-      <c r="EI1" s="1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>T3-T5</t>
         </is>
       </c>
-      <c r="EJ1" s="1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>T3-T6</t>
         </is>
       </c>
-      <c r="EK1" s="1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>T3-P3</t>
         </is>
       </c>
-      <c r="EL1" s="1" t="inlineStr">
+      <c r="EL1" t="inlineStr">
         <is>
           <t>T3-P4</t>
         </is>
       </c>
-      <c r="EM1" s="1" t="inlineStr">
+      <c r="EM1" t="inlineStr">
         <is>
           <t>T3-PZ</t>
         </is>
       </c>
-      <c r="EN1" s="1" t="inlineStr">
+      <c r="EN1" t="inlineStr">
         <is>
           <t>T3-O1</t>
         </is>
       </c>
-      <c r="EO1" s="1" t="inlineStr">
+      <c r="EO1" t="inlineStr">
         <is>
           <t>T3-O2</t>
         </is>
       </c>
-      <c r="EP1" s="1" t="inlineStr">
+      <c r="EP1" t="inlineStr">
         <is>
           <t>T4-T5</t>
         </is>
       </c>
-      <c r="EQ1" s="1" t="inlineStr">
+      <c r="EQ1" t="inlineStr">
         <is>
           <t>T4-T6</t>
         </is>
       </c>
-      <c r="ER1" s="1" t="inlineStr">
+      <c r="ER1" t="inlineStr">
         <is>
           <t>T4-P3</t>
         </is>
       </c>
-      <c r="ES1" s="1" t="inlineStr">
+      <c r="ES1" t="inlineStr">
         <is>
           <t>T4-P4</t>
         </is>
       </c>
-      <c r="ET1" s="1" t="inlineStr">
+      <c r="ET1" t="inlineStr">
         <is>
           <t>T4-PZ</t>
         </is>
       </c>
-      <c r="EU1" s="1" t="inlineStr">
+      <c r="EU1" t="inlineStr">
         <is>
           <t>T4-O1</t>
         </is>
       </c>
-      <c r="EV1" s="1" t="inlineStr">
+      <c r="EV1" t="inlineStr">
         <is>
           <t>T4-O2</t>
         </is>
       </c>
-      <c r="EW1" s="1" t="inlineStr">
+      <c r="EW1" t="inlineStr">
         <is>
           <t>T5-T6</t>
         </is>
       </c>
-      <c r="EX1" s="1" t="inlineStr">
+      <c r="EX1" t="inlineStr">
         <is>
           <t>T5-P3</t>
         </is>
       </c>
-      <c r="EY1" s="1" t="inlineStr">
+      <c r="EY1" t="inlineStr">
         <is>
           <t>T5-P4</t>
         </is>
       </c>
-      <c r="EZ1" s="1" t="inlineStr">
+      <c r="EZ1" t="inlineStr">
         <is>
           <t>T5-PZ</t>
         </is>
       </c>
-      <c r="FA1" s="1" t="inlineStr">
+      <c r="FA1" t="inlineStr">
         <is>
           <t>T5-O1</t>
         </is>
       </c>
-      <c r="FB1" s="1" t="inlineStr">
+      <c r="FB1" t="inlineStr">
         <is>
           <t>T5-O2</t>
         </is>
       </c>
-      <c r="FC1" s="1" t="inlineStr">
+      <c r="FC1" t="inlineStr">
         <is>
           <t>T6-P3</t>
         </is>
       </c>
-      <c r="FD1" s="1" t="inlineStr">
+      <c r="FD1" t="inlineStr">
         <is>
           <t>T6-P4</t>
         </is>
       </c>
-      <c r="FE1" s="1" t="inlineStr">
+      <c r="FE1" t="inlineStr">
         <is>
           <t>T6-PZ</t>
         </is>
       </c>
-      <c r="FF1" s="1" t="inlineStr">
+      <c r="FF1" t="inlineStr">
         <is>
           <t>T6-O1</t>
         </is>
       </c>
-      <c r="FG1" s="1" t="inlineStr">
+      <c r="FG1" t="inlineStr">
         <is>
           <t>T6-O2</t>
         </is>
       </c>
-      <c r="FH1" s="1" t="inlineStr">
+      <c r="FH1" t="inlineStr">
         <is>
           <t>P3-P4</t>
         </is>
       </c>
-      <c r="FI1" s="1" t="inlineStr">
+      <c r="FI1" t="inlineStr">
         <is>
           <t>P3-PZ</t>
         </is>
       </c>
-      <c r="FJ1" s="1" t="inlineStr">
+      <c r="FJ1" t="inlineStr">
         <is>
           <t>P3-O1</t>
         </is>
       </c>
-      <c r="FK1" s="1" t="inlineStr">
+      <c r="FK1" t="inlineStr">
         <is>
           <t>P3-O2</t>
         </is>
       </c>
-      <c r="FL1" s="1" t="inlineStr">
+      <c r="FL1" t="inlineStr">
         <is>
           <t>P4-PZ</t>
         </is>
       </c>
-      <c r="FM1" s="1" t="inlineStr">
+      <c r="FM1" t="inlineStr">
         <is>
           <t>P4-O1</t>
         </is>
       </c>
-      <c r="FN1" s="1" t="inlineStr">
+      <c r="FN1" t="inlineStr">
         <is>
           <t>P4-O2</t>
         </is>
       </c>
-      <c r="FO1" s="1" t="inlineStr">
+      <c r="FO1" t="inlineStr">
         <is>
           <t>PZ-O1</t>
         </is>
       </c>
-      <c r="FP1" s="1" t="inlineStr">
+      <c r="FP1" t="inlineStr">
         <is>
           <t>PZ-O2</t>
         </is>
       </c>
-      <c r="FQ1" s="1" t="inlineStr">
+      <c r="FQ1" t="inlineStr">
         <is>
           <t>O1-O2</t>
         </is>
       </c>
-      <c r="FR1" s="1" t="inlineStr">
+      <c r="FR1" t="inlineStr">
         <is>
           <t>C3-F3</t>
         </is>
       </c>
-      <c r="FS1" s="1" t="inlineStr">
+      <c r="FS1" t="inlineStr">
         <is>
           <t>C3-F4</t>
         </is>
       </c>
-      <c r="FT1" s="1" t="inlineStr">
+      <c r="FT1" t="inlineStr">
         <is>
           <t>C3-F7</t>
         </is>
       </c>
-      <c r="FU1" s="1" t="inlineStr">
+      <c r="FU1" t="inlineStr">
         <is>
           <t>C3-F8</t>
         </is>
       </c>
-      <c r="FV1" s="1" t="inlineStr">
+      <c r="FV1" t="inlineStr">
         <is>
           <t>C3-FP1</t>
         </is>
       </c>
-      <c r="FW1" s="1" t="inlineStr">
+      <c r="FW1" t="inlineStr">
         <is>
           <t>C3-FP2</t>
         </is>
       </c>
-      <c r="FX1" s="1" t="inlineStr">
+      <c r="FX1" t="inlineStr">
         <is>
           <t>C3-FZ</t>
         </is>
       </c>
-      <c r="FY1" s="1" t="inlineStr">
+      <c r="FY1" t="inlineStr">
         <is>
           <t>C4-F3</t>
         </is>
       </c>
-      <c r="FZ1" s="1" t="inlineStr">
+      <c r="FZ1" t="inlineStr">
         <is>
           <t>C4-F4</t>
         </is>
       </c>
-      <c r="GA1" s="1" t="inlineStr">
+      <c r="GA1" t="inlineStr">
         <is>
           <t>C4-F7</t>
         </is>
       </c>
-      <c r="GB1" s="1" t="inlineStr">
+      <c r="GB1" t="inlineStr">
         <is>
           <t>C4-F8</t>
         </is>
       </c>
-      <c r="GC1" s="1" t="inlineStr">
+      <c r="GC1" t="inlineStr">
         <is>
           <t>C4-FP1</t>
         </is>
       </c>
-      <c r="GD1" s="1" t="inlineStr">
+      <c r="GD1" t="inlineStr">
         <is>
           <t>C4-FP2</t>
         </is>
       </c>
-      <c r="GE1" s="1" t="inlineStr">
+      <c r="GE1" t="inlineStr">
         <is>
           <t>C4-FZ</t>
         </is>
       </c>
-      <c r="GF1" s="1" t="inlineStr">
+      <c r="GF1" t="inlineStr">
         <is>
           <t>CZ-F3</t>
         </is>
       </c>
-      <c r="GG1" s="1" t="inlineStr">
+      <c r="GG1" t="inlineStr">
         <is>
           <t>CZ-F4</t>
         </is>
       </c>
-      <c r="GH1" s="1" t="inlineStr">
+      <c r="GH1" t="inlineStr">
         <is>
           <t>CZ-F7</t>
         </is>
       </c>
-      <c r="GI1" s="1" t="inlineStr">
+      <c r="GI1" t="inlineStr">
         <is>
           <t>CZ-F8</t>
         </is>
       </c>
-      <c r="GJ1" s="1" t="inlineStr">
+      <c r="GJ1" t="inlineStr">
         <is>
           <t>CZ-FP1</t>
         </is>
       </c>
-      <c r="GK1" s="1" t="inlineStr">
+      <c r="GK1" t="inlineStr">
         <is>
           <t>CZ-FP2</t>
         </is>
       </c>
-      <c r="GL1" s="1" t="inlineStr">
+      <c r="GL1" t="inlineStr">
         <is>
           <t>CZ-FZ</t>
         </is>
       </c>
-      <c r="GM1" s="1" t="inlineStr">
+      <c r="GM1" t="inlineStr">
         <is>
           <t>F3-FP1</t>
         </is>
       </c>
-      <c r="GN1" s="1" t="inlineStr">
+      <c r="GN1" t="inlineStr">
         <is>
           <t>F3-FP2</t>
         </is>
       </c>
-      <c r="GO1" s="1" t="inlineStr">
+      <c r="GO1" t="inlineStr">
         <is>
           <t>F4-FP1</t>
         </is>
       </c>
-      <c r="GP1" s="1" t="inlineStr">
+      <c r="GP1" t="inlineStr">
         <is>
           <t>F4-FP2</t>
         </is>
       </c>
-      <c r="GQ1" s="1" t="inlineStr">
+      <c r="GQ1" t="inlineStr">
         <is>
           <t>F7-FP1</t>
         </is>
       </c>
-      <c r="GR1" s="1" t="inlineStr">
+      <c r="GR1" t="inlineStr">
         <is>
           <t>F7-FP2</t>
         </is>
       </c>
-      <c r="GS1" s="1" t="inlineStr">
+      <c r="GS1" t="inlineStr">
         <is>
           <t>F8-FP1</t>
         </is>
       </c>
-      <c r="GT1" s="1" t="inlineStr">
+      <c r="GT1" t="inlineStr">
         <is>
           <t>F8-FP2</t>
         </is>
       </c>
-      <c r="GU1" s="1" t="inlineStr">
+      <c r="GU1" t="inlineStr">
         <is>
           <t>O1-P3</t>
         </is>
       </c>
-      <c r="GV1" s="1" t="inlineStr">
+      <c r="GV1" t="inlineStr">
         <is>
           <t>O1-P4</t>
         </is>
       </c>
-      <c r="GW1" s="1" t="inlineStr">
+      <c r="GW1" t="inlineStr">
         <is>
           <t>O1-PZ</t>
         </is>
       </c>
-      <c r="GX1" s="1" t="inlineStr">
+      <c r="GX1" t="inlineStr">
         <is>
           <t>O1-T3</t>
         </is>
       </c>
-      <c r="GY1" s="1" t="inlineStr">
+      <c r="GY1" t="inlineStr">
         <is>
           <t>O1-T4</t>
         </is>
       </c>
-      <c r="GZ1" s="1" t="inlineStr">
+      <c r="GZ1" t="inlineStr">
         <is>
           <t>O1-T5</t>
         </is>
       </c>
-      <c r="HA1" s="1" t="inlineStr">
+      <c r="HA1" t="inlineStr">
         <is>
           <t>O1-T6</t>
         </is>
       </c>
-      <c r="HB1" s="1" t="inlineStr">
+      <c r="HB1" t="inlineStr">
         <is>
           <t>O2-P3</t>
         </is>
       </c>
-      <c r="HC1" s="1" t="inlineStr">
+      <c r="HC1" t="inlineStr">
         <is>
           <t>O2-P4</t>
         </is>
       </c>
-      <c r="HD1" s="1" t="inlineStr">
+      <c r="HD1" t="inlineStr">
         <is>
           <t>O2-PZ</t>
         </is>
       </c>
-      <c r="HE1" s="1" t="inlineStr">
+      <c r="HE1" t="inlineStr">
         <is>
           <t>O2-T3</t>
         </is>
       </c>
-      <c r="HF1" s="1" t="inlineStr">
+      <c r="HF1" t="inlineStr">
         <is>
           <t>O2-T4</t>
         </is>
       </c>
-      <c r="HG1" s="1" t="inlineStr">
+      <c r="HG1" t="inlineStr">
         <is>
           <t>O2-T5</t>
         </is>
       </c>
-      <c r="HH1" s="1" t="inlineStr">
+      <c r="HH1" t="inlineStr">
         <is>
           <t>O2-T6</t>
         </is>
       </c>
-      <c r="HI1" s="1" t="inlineStr">
+      <c r="HI1" t="inlineStr">
         <is>
           <t>P3-T3</t>
         </is>
       </c>
-      <c r="HJ1" s="1" t="inlineStr">
+      <c r="HJ1" t="inlineStr">
         <is>
           <t>P3-T4</t>
         </is>
       </c>
-      <c r="HK1" s="1" t="inlineStr">
+      <c r="HK1" t="inlineStr">
         <is>
           <t>P3-T5</t>
         </is>
       </c>
-      <c r="HL1" s="1" t="inlineStr">
+      <c r="HL1" t="inlineStr">
         <is>
           <t>P3-T6</t>
         </is>
       </c>
-      <c r="HM1" s="1" t="inlineStr">
+      <c r="HM1" t="inlineStr">
         <is>
           <t>P4-T3</t>
         </is>
       </c>
-      <c r="HN1" s="1" t="inlineStr">
+      <c r="HN1" t="inlineStr">
         <is>
           <t>P4-T4</t>
         </is>
       </c>
-      <c r="HO1" s="1" t="inlineStr">
+      <c r="HO1" t="inlineStr">
         <is>
           <t>P4-T5</t>
         </is>
       </c>
-      <c r="HP1" s="1" t="inlineStr">
+      <c r="HP1" t="inlineStr">
         <is>
           <t>P4-T6</t>
         </is>
       </c>
-      <c r="HQ1" s="1" t="inlineStr">
+      <c r="HQ1" t="inlineStr">
         <is>
           <t>PZ-T3</t>
         </is>
       </c>
-      <c r="HR1" s="1" t="inlineStr">
+      <c r="HR1" t="inlineStr">
         <is>
           <t>PZ-T4</t>
         </is>
       </c>
-      <c r="HS1" s="1" t="inlineStr">
+      <c r="HS1" t="inlineStr">
         <is>
           <t>PZ-T5</t>
         </is>
       </c>
-      <c r="HT1" s="1" t="inlineStr">
+      <c r="HT1" t="inlineStr">
         <is>
           <t>PZ-T6</t>
         </is>
@@ -2098,6 +2098,171 @@
       <c r="FQ2" t="n">
         <v>0.7272980217475143</v>
       </c>
+      <c r="FR2" t="n">
+        <v/>
+      </c>
+      <c r="FS2" t="n">
+        <v/>
+      </c>
+      <c r="FT2" t="n">
+        <v/>
+      </c>
+      <c r="FU2" t="n">
+        <v/>
+      </c>
+      <c r="FV2" t="n">
+        <v/>
+      </c>
+      <c r="FW2" t="n">
+        <v/>
+      </c>
+      <c r="FX2" t="n">
+        <v/>
+      </c>
+      <c r="FY2" t="n">
+        <v/>
+      </c>
+      <c r="FZ2" t="n">
+        <v/>
+      </c>
+      <c r="GA2" t="n">
+        <v/>
+      </c>
+      <c r="GB2" t="n">
+        <v/>
+      </c>
+      <c r="GC2" t="n">
+        <v/>
+      </c>
+      <c r="GD2" t="n">
+        <v/>
+      </c>
+      <c r="GE2" t="n">
+        <v/>
+      </c>
+      <c r="GF2" t="n">
+        <v/>
+      </c>
+      <c r="GG2" t="n">
+        <v/>
+      </c>
+      <c r="GH2" t="n">
+        <v/>
+      </c>
+      <c r="GI2" t="n">
+        <v/>
+      </c>
+      <c r="GJ2" t="n">
+        <v/>
+      </c>
+      <c r="GK2" t="n">
+        <v/>
+      </c>
+      <c r="GL2" t="n">
+        <v/>
+      </c>
+      <c r="GM2" t="n">
+        <v/>
+      </c>
+      <c r="GN2" t="n">
+        <v/>
+      </c>
+      <c r="GO2" t="n">
+        <v/>
+      </c>
+      <c r="GP2" t="n">
+        <v/>
+      </c>
+      <c r="GQ2" t="n">
+        <v/>
+      </c>
+      <c r="GR2" t="n">
+        <v/>
+      </c>
+      <c r="GS2" t="n">
+        <v/>
+      </c>
+      <c r="GT2" t="n">
+        <v/>
+      </c>
+      <c r="GU2" t="n">
+        <v/>
+      </c>
+      <c r="GV2" t="n">
+        <v/>
+      </c>
+      <c r="GW2" t="n">
+        <v/>
+      </c>
+      <c r="GX2" t="n">
+        <v/>
+      </c>
+      <c r="GY2" t="n">
+        <v/>
+      </c>
+      <c r="GZ2" t="n">
+        <v/>
+      </c>
+      <c r="HA2" t="n">
+        <v/>
+      </c>
+      <c r="HB2" t="n">
+        <v/>
+      </c>
+      <c r="HC2" t="n">
+        <v/>
+      </c>
+      <c r="HD2" t="n">
+        <v/>
+      </c>
+      <c r="HE2" t="n">
+        <v/>
+      </c>
+      <c r="HF2" t="n">
+        <v/>
+      </c>
+      <c r="HG2" t="n">
+        <v/>
+      </c>
+      <c r="HH2" t="n">
+        <v/>
+      </c>
+      <c r="HI2" t="n">
+        <v/>
+      </c>
+      <c r="HJ2" t="n">
+        <v/>
+      </c>
+      <c r="HK2" t="n">
+        <v/>
+      </c>
+      <c r="HL2" t="n">
+        <v/>
+      </c>
+      <c r="HM2" t="n">
+        <v/>
+      </c>
+      <c r="HN2" t="n">
+        <v/>
+      </c>
+      <c r="HO2" t="n">
+        <v/>
+      </c>
+      <c r="HP2" t="n">
+        <v/>
+      </c>
+      <c r="HQ2" t="n">
+        <v/>
+      </c>
+      <c r="HR2" t="n">
+        <v/>
+      </c>
+      <c r="HS2" t="n">
+        <v/>
+      </c>
+      <c r="HT2" t="n">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2623,6 +2788,171 @@
       <c r="FQ3" t="n">
         <v>0.3377778959668855</v>
       </c>
+      <c r="FR3" t="n">
+        <v/>
+      </c>
+      <c r="FS3" t="n">
+        <v/>
+      </c>
+      <c r="FT3" t="n">
+        <v/>
+      </c>
+      <c r="FU3" t="n">
+        <v/>
+      </c>
+      <c r="FV3" t="n">
+        <v/>
+      </c>
+      <c r="FW3" t="n">
+        <v/>
+      </c>
+      <c r="FX3" t="n">
+        <v/>
+      </c>
+      <c r="FY3" t="n">
+        <v/>
+      </c>
+      <c r="FZ3" t="n">
+        <v/>
+      </c>
+      <c r="GA3" t="n">
+        <v/>
+      </c>
+      <c r="GB3" t="n">
+        <v/>
+      </c>
+      <c r="GC3" t="n">
+        <v/>
+      </c>
+      <c r="GD3" t="n">
+        <v/>
+      </c>
+      <c r="GE3" t="n">
+        <v/>
+      </c>
+      <c r="GF3" t="n">
+        <v/>
+      </c>
+      <c r="GG3" t="n">
+        <v/>
+      </c>
+      <c r="GH3" t="n">
+        <v/>
+      </c>
+      <c r="GI3" t="n">
+        <v/>
+      </c>
+      <c r="GJ3" t="n">
+        <v/>
+      </c>
+      <c r="GK3" t="n">
+        <v/>
+      </c>
+      <c r="GL3" t="n">
+        <v/>
+      </c>
+      <c r="GM3" t="n">
+        <v/>
+      </c>
+      <c r="GN3" t="n">
+        <v/>
+      </c>
+      <c r="GO3" t="n">
+        <v/>
+      </c>
+      <c r="GP3" t="n">
+        <v/>
+      </c>
+      <c r="GQ3" t="n">
+        <v/>
+      </c>
+      <c r="GR3" t="n">
+        <v/>
+      </c>
+      <c r="GS3" t="n">
+        <v/>
+      </c>
+      <c r="GT3" t="n">
+        <v/>
+      </c>
+      <c r="GU3" t="n">
+        <v/>
+      </c>
+      <c r="GV3" t="n">
+        <v/>
+      </c>
+      <c r="GW3" t="n">
+        <v/>
+      </c>
+      <c r="GX3" t="n">
+        <v/>
+      </c>
+      <c r="GY3" t="n">
+        <v/>
+      </c>
+      <c r="GZ3" t="n">
+        <v/>
+      </c>
+      <c r="HA3" t="n">
+        <v/>
+      </c>
+      <c r="HB3" t="n">
+        <v/>
+      </c>
+      <c r="HC3" t="n">
+        <v/>
+      </c>
+      <c r="HD3" t="n">
+        <v/>
+      </c>
+      <c r="HE3" t="n">
+        <v/>
+      </c>
+      <c r="HF3" t="n">
+        <v/>
+      </c>
+      <c r="HG3" t="n">
+        <v/>
+      </c>
+      <c r="HH3" t="n">
+        <v/>
+      </c>
+      <c r="HI3" t="n">
+        <v/>
+      </c>
+      <c r="HJ3" t="n">
+        <v/>
+      </c>
+      <c r="HK3" t="n">
+        <v/>
+      </c>
+      <c r="HL3" t="n">
+        <v/>
+      </c>
+      <c r="HM3" t="n">
+        <v/>
+      </c>
+      <c r="HN3" t="n">
+        <v/>
+      </c>
+      <c r="HO3" t="n">
+        <v/>
+      </c>
+      <c r="HP3" t="n">
+        <v/>
+      </c>
+      <c r="HQ3" t="n">
+        <v/>
+      </c>
+      <c r="HR3" t="n">
+        <v/>
+      </c>
+      <c r="HS3" t="n">
+        <v/>
+      </c>
+      <c r="HT3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3148,6 +3478,171 @@
       <c r="FQ4" t="n">
         <v>0.8356981273355846</v>
       </c>
+      <c r="FR4" t="n">
+        <v/>
+      </c>
+      <c r="FS4" t="n">
+        <v/>
+      </c>
+      <c r="FT4" t="n">
+        <v/>
+      </c>
+      <c r="FU4" t="n">
+        <v/>
+      </c>
+      <c r="FV4" t="n">
+        <v/>
+      </c>
+      <c r="FW4" t="n">
+        <v/>
+      </c>
+      <c r="FX4" t="n">
+        <v/>
+      </c>
+      <c r="FY4" t="n">
+        <v/>
+      </c>
+      <c r="FZ4" t="n">
+        <v/>
+      </c>
+      <c r="GA4" t="n">
+        <v/>
+      </c>
+      <c r="GB4" t="n">
+        <v/>
+      </c>
+      <c r="GC4" t="n">
+        <v/>
+      </c>
+      <c r="GD4" t="n">
+        <v/>
+      </c>
+      <c r="GE4" t="n">
+        <v/>
+      </c>
+      <c r="GF4" t="n">
+        <v/>
+      </c>
+      <c r="GG4" t="n">
+        <v/>
+      </c>
+      <c r="GH4" t="n">
+        <v/>
+      </c>
+      <c r="GI4" t="n">
+        <v/>
+      </c>
+      <c r="GJ4" t="n">
+        <v/>
+      </c>
+      <c r="GK4" t="n">
+        <v/>
+      </c>
+      <c r="GL4" t="n">
+        <v/>
+      </c>
+      <c r="GM4" t="n">
+        <v/>
+      </c>
+      <c r="GN4" t="n">
+        <v/>
+      </c>
+      <c r="GO4" t="n">
+        <v/>
+      </c>
+      <c r="GP4" t="n">
+        <v/>
+      </c>
+      <c r="GQ4" t="n">
+        <v/>
+      </c>
+      <c r="GR4" t="n">
+        <v/>
+      </c>
+      <c r="GS4" t="n">
+        <v/>
+      </c>
+      <c r="GT4" t="n">
+        <v/>
+      </c>
+      <c r="GU4" t="n">
+        <v/>
+      </c>
+      <c r="GV4" t="n">
+        <v/>
+      </c>
+      <c r="GW4" t="n">
+        <v/>
+      </c>
+      <c r="GX4" t="n">
+        <v/>
+      </c>
+      <c r="GY4" t="n">
+        <v/>
+      </c>
+      <c r="GZ4" t="n">
+        <v/>
+      </c>
+      <c r="HA4" t="n">
+        <v/>
+      </c>
+      <c r="HB4" t="n">
+        <v/>
+      </c>
+      <c r="HC4" t="n">
+        <v/>
+      </c>
+      <c r="HD4" t="n">
+        <v/>
+      </c>
+      <c r="HE4" t="n">
+        <v/>
+      </c>
+      <c r="HF4" t="n">
+        <v/>
+      </c>
+      <c r="HG4" t="n">
+        <v/>
+      </c>
+      <c r="HH4" t="n">
+        <v/>
+      </c>
+      <c r="HI4" t="n">
+        <v/>
+      </c>
+      <c r="HJ4" t="n">
+        <v/>
+      </c>
+      <c r="HK4" t="n">
+        <v/>
+      </c>
+      <c r="HL4" t="n">
+        <v/>
+      </c>
+      <c r="HM4" t="n">
+        <v/>
+      </c>
+      <c r="HN4" t="n">
+        <v/>
+      </c>
+      <c r="HO4" t="n">
+        <v/>
+      </c>
+      <c r="HP4" t="n">
+        <v/>
+      </c>
+      <c r="HQ4" t="n">
+        <v/>
+      </c>
+      <c r="HR4" t="n">
+        <v/>
+      </c>
+      <c r="HS4" t="n">
+        <v/>
+      </c>
+      <c r="HT4" t="n">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3673,6 +4168,171 @@
       <c r="FQ5" t="n">
         <v>0.829657658994315</v>
       </c>
+      <c r="FR5" t="n">
+        <v/>
+      </c>
+      <c r="FS5" t="n">
+        <v/>
+      </c>
+      <c r="FT5" t="n">
+        <v/>
+      </c>
+      <c r="FU5" t="n">
+        <v/>
+      </c>
+      <c r="FV5" t="n">
+        <v/>
+      </c>
+      <c r="FW5" t="n">
+        <v/>
+      </c>
+      <c r="FX5" t="n">
+        <v/>
+      </c>
+      <c r="FY5" t="n">
+        <v/>
+      </c>
+      <c r="FZ5" t="n">
+        <v/>
+      </c>
+      <c r="GA5" t="n">
+        <v/>
+      </c>
+      <c r="GB5" t="n">
+        <v/>
+      </c>
+      <c r="GC5" t="n">
+        <v/>
+      </c>
+      <c r="GD5" t="n">
+        <v/>
+      </c>
+      <c r="GE5" t="n">
+        <v/>
+      </c>
+      <c r="GF5" t="n">
+        <v/>
+      </c>
+      <c r="GG5" t="n">
+        <v/>
+      </c>
+      <c r="GH5" t="n">
+        <v/>
+      </c>
+      <c r="GI5" t="n">
+        <v/>
+      </c>
+      <c r="GJ5" t="n">
+        <v/>
+      </c>
+      <c r="GK5" t="n">
+        <v/>
+      </c>
+      <c r="GL5" t="n">
+        <v/>
+      </c>
+      <c r="GM5" t="n">
+        <v/>
+      </c>
+      <c r="GN5" t="n">
+        <v/>
+      </c>
+      <c r="GO5" t="n">
+        <v/>
+      </c>
+      <c r="GP5" t="n">
+        <v/>
+      </c>
+      <c r="GQ5" t="n">
+        <v/>
+      </c>
+      <c r="GR5" t="n">
+        <v/>
+      </c>
+      <c r="GS5" t="n">
+        <v/>
+      </c>
+      <c r="GT5" t="n">
+        <v/>
+      </c>
+      <c r="GU5" t="n">
+        <v/>
+      </c>
+      <c r="GV5" t="n">
+        <v/>
+      </c>
+      <c r="GW5" t="n">
+        <v/>
+      </c>
+      <c r="GX5" t="n">
+        <v/>
+      </c>
+      <c r="GY5" t="n">
+        <v/>
+      </c>
+      <c r="GZ5" t="n">
+        <v/>
+      </c>
+      <c r="HA5" t="n">
+        <v/>
+      </c>
+      <c r="HB5" t="n">
+        <v/>
+      </c>
+      <c r="HC5" t="n">
+        <v/>
+      </c>
+      <c r="HD5" t="n">
+        <v/>
+      </c>
+      <c r="HE5" t="n">
+        <v/>
+      </c>
+      <c r="HF5" t="n">
+        <v/>
+      </c>
+      <c r="HG5" t="n">
+        <v/>
+      </c>
+      <c r="HH5" t="n">
+        <v/>
+      </c>
+      <c r="HI5" t="n">
+        <v/>
+      </c>
+      <c r="HJ5" t="n">
+        <v/>
+      </c>
+      <c r="HK5" t="n">
+        <v/>
+      </c>
+      <c r="HL5" t="n">
+        <v/>
+      </c>
+      <c r="HM5" t="n">
+        <v/>
+      </c>
+      <c r="HN5" t="n">
+        <v/>
+      </c>
+      <c r="HO5" t="n">
+        <v/>
+      </c>
+      <c r="HP5" t="n">
+        <v/>
+      </c>
+      <c r="HQ5" t="n">
+        <v/>
+      </c>
+      <c r="HR5" t="n">
+        <v/>
+      </c>
+      <c r="HS5" t="n">
+        <v/>
+      </c>
+      <c r="HT5" t="n">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4198,6 +4858,171 @@
       <c r="FQ6" t="n">
         <v>0.7152293509963119</v>
       </c>
+      <c r="FR6" t="n">
+        <v/>
+      </c>
+      <c r="FS6" t="n">
+        <v/>
+      </c>
+      <c r="FT6" t="n">
+        <v/>
+      </c>
+      <c r="FU6" t="n">
+        <v/>
+      </c>
+      <c r="FV6" t="n">
+        <v/>
+      </c>
+      <c r="FW6" t="n">
+        <v/>
+      </c>
+      <c r="FX6" t="n">
+        <v/>
+      </c>
+      <c r="FY6" t="n">
+        <v/>
+      </c>
+      <c r="FZ6" t="n">
+        <v/>
+      </c>
+      <c r="GA6" t="n">
+        <v/>
+      </c>
+      <c r="GB6" t="n">
+        <v/>
+      </c>
+      <c r="GC6" t="n">
+        <v/>
+      </c>
+      <c r="GD6" t="n">
+        <v/>
+      </c>
+      <c r="GE6" t="n">
+        <v/>
+      </c>
+      <c r="GF6" t="n">
+        <v/>
+      </c>
+      <c r="GG6" t="n">
+        <v/>
+      </c>
+      <c r="GH6" t="n">
+        <v/>
+      </c>
+      <c r="GI6" t="n">
+        <v/>
+      </c>
+      <c r="GJ6" t="n">
+        <v/>
+      </c>
+      <c r="GK6" t="n">
+        <v/>
+      </c>
+      <c r="GL6" t="n">
+        <v/>
+      </c>
+      <c r="GM6" t="n">
+        <v/>
+      </c>
+      <c r="GN6" t="n">
+        <v/>
+      </c>
+      <c r="GO6" t="n">
+        <v/>
+      </c>
+      <c r="GP6" t="n">
+        <v/>
+      </c>
+      <c r="GQ6" t="n">
+        <v/>
+      </c>
+      <c r="GR6" t="n">
+        <v/>
+      </c>
+      <c r="GS6" t="n">
+        <v/>
+      </c>
+      <c r="GT6" t="n">
+        <v/>
+      </c>
+      <c r="GU6" t="n">
+        <v/>
+      </c>
+      <c r="GV6" t="n">
+        <v/>
+      </c>
+      <c r="GW6" t="n">
+        <v/>
+      </c>
+      <c r="GX6" t="n">
+        <v/>
+      </c>
+      <c r="GY6" t="n">
+        <v/>
+      </c>
+      <c r="GZ6" t="n">
+        <v/>
+      </c>
+      <c r="HA6" t="n">
+        <v/>
+      </c>
+      <c r="HB6" t="n">
+        <v/>
+      </c>
+      <c r="HC6" t="n">
+        <v/>
+      </c>
+      <c r="HD6" t="n">
+        <v/>
+      </c>
+      <c r="HE6" t="n">
+        <v/>
+      </c>
+      <c r="HF6" t="n">
+        <v/>
+      </c>
+      <c r="HG6" t="n">
+        <v/>
+      </c>
+      <c r="HH6" t="n">
+        <v/>
+      </c>
+      <c r="HI6" t="n">
+        <v/>
+      </c>
+      <c r="HJ6" t="n">
+        <v/>
+      </c>
+      <c r="HK6" t="n">
+        <v/>
+      </c>
+      <c r="HL6" t="n">
+        <v/>
+      </c>
+      <c r="HM6" t="n">
+        <v/>
+      </c>
+      <c r="HN6" t="n">
+        <v/>
+      </c>
+      <c r="HO6" t="n">
+        <v/>
+      </c>
+      <c r="HP6" t="n">
+        <v/>
+      </c>
+      <c r="HQ6" t="n">
+        <v/>
+      </c>
+      <c r="HR6" t="n">
+        <v/>
+      </c>
+      <c r="HS6" t="n">
+        <v/>
+      </c>
+      <c r="HT6" t="n">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5413,6 +6238,171 @@
       <c r="FQ8" t="n">
         <v>0.7888627970240634</v>
       </c>
+      <c r="FR8" t="n">
+        <v/>
+      </c>
+      <c r="FS8" t="n">
+        <v/>
+      </c>
+      <c r="FT8" t="n">
+        <v/>
+      </c>
+      <c r="FU8" t="n">
+        <v/>
+      </c>
+      <c r="FV8" t="n">
+        <v/>
+      </c>
+      <c r="FW8" t="n">
+        <v/>
+      </c>
+      <c r="FX8" t="n">
+        <v/>
+      </c>
+      <c r="FY8" t="n">
+        <v/>
+      </c>
+      <c r="FZ8" t="n">
+        <v/>
+      </c>
+      <c r="GA8" t="n">
+        <v/>
+      </c>
+      <c r="GB8" t="n">
+        <v/>
+      </c>
+      <c r="GC8" t="n">
+        <v/>
+      </c>
+      <c r="GD8" t="n">
+        <v/>
+      </c>
+      <c r="GE8" t="n">
+        <v/>
+      </c>
+      <c r="GF8" t="n">
+        <v/>
+      </c>
+      <c r="GG8" t="n">
+        <v/>
+      </c>
+      <c r="GH8" t="n">
+        <v/>
+      </c>
+      <c r="GI8" t="n">
+        <v/>
+      </c>
+      <c r="GJ8" t="n">
+        <v/>
+      </c>
+      <c r="GK8" t="n">
+        <v/>
+      </c>
+      <c r="GL8" t="n">
+        <v/>
+      </c>
+      <c r="GM8" t="n">
+        <v/>
+      </c>
+      <c r="GN8" t="n">
+        <v/>
+      </c>
+      <c r="GO8" t="n">
+        <v/>
+      </c>
+      <c r="GP8" t="n">
+        <v/>
+      </c>
+      <c r="GQ8" t="n">
+        <v/>
+      </c>
+      <c r="GR8" t="n">
+        <v/>
+      </c>
+      <c r="GS8" t="n">
+        <v/>
+      </c>
+      <c r="GT8" t="n">
+        <v/>
+      </c>
+      <c r="GU8" t="n">
+        <v/>
+      </c>
+      <c r="GV8" t="n">
+        <v/>
+      </c>
+      <c r="GW8" t="n">
+        <v/>
+      </c>
+      <c r="GX8" t="n">
+        <v/>
+      </c>
+      <c r="GY8" t="n">
+        <v/>
+      </c>
+      <c r="GZ8" t="n">
+        <v/>
+      </c>
+      <c r="HA8" t="n">
+        <v/>
+      </c>
+      <c r="HB8" t="n">
+        <v/>
+      </c>
+      <c r="HC8" t="n">
+        <v/>
+      </c>
+      <c r="HD8" t="n">
+        <v/>
+      </c>
+      <c r="HE8" t="n">
+        <v/>
+      </c>
+      <c r="HF8" t="n">
+        <v/>
+      </c>
+      <c r="HG8" t="n">
+        <v/>
+      </c>
+      <c r="HH8" t="n">
+        <v/>
+      </c>
+      <c r="HI8" t="n">
+        <v/>
+      </c>
+      <c r="HJ8" t="n">
+        <v/>
+      </c>
+      <c r="HK8" t="n">
+        <v/>
+      </c>
+      <c r="HL8" t="n">
+        <v/>
+      </c>
+      <c r="HM8" t="n">
+        <v/>
+      </c>
+      <c r="HN8" t="n">
+        <v/>
+      </c>
+      <c r="HO8" t="n">
+        <v/>
+      </c>
+      <c r="HP8" t="n">
+        <v/>
+      </c>
+      <c r="HQ8" t="n">
+        <v/>
+      </c>
+      <c r="HR8" t="n">
+        <v/>
+      </c>
+      <c r="HS8" t="n">
+        <v/>
+      </c>
+      <c r="HT8" t="n">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5938,6 +6928,171 @@
       <c r="FQ9" t="n">
         <v>0.8070564223399311</v>
       </c>
+      <c r="FR9" t="n">
+        <v/>
+      </c>
+      <c r="FS9" t="n">
+        <v/>
+      </c>
+      <c r="FT9" t="n">
+        <v/>
+      </c>
+      <c r="FU9" t="n">
+        <v/>
+      </c>
+      <c r="FV9" t="n">
+        <v/>
+      </c>
+      <c r="FW9" t="n">
+        <v/>
+      </c>
+      <c r="FX9" t="n">
+        <v/>
+      </c>
+      <c r="FY9" t="n">
+        <v/>
+      </c>
+      <c r="FZ9" t="n">
+        <v/>
+      </c>
+      <c r="GA9" t="n">
+        <v/>
+      </c>
+      <c r="GB9" t="n">
+        <v/>
+      </c>
+      <c r="GC9" t="n">
+        <v/>
+      </c>
+      <c r="GD9" t="n">
+        <v/>
+      </c>
+      <c r="GE9" t="n">
+        <v/>
+      </c>
+      <c r="GF9" t="n">
+        <v/>
+      </c>
+      <c r="GG9" t="n">
+        <v/>
+      </c>
+      <c r="GH9" t="n">
+        <v/>
+      </c>
+      <c r="GI9" t="n">
+        <v/>
+      </c>
+      <c r="GJ9" t="n">
+        <v/>
+      </c>
+      <c r="GK9" t="n">
+        <v/>
+      </c>
+      <c r="GL9" t="n">
+        <v/>
+      </c>
+      <c r="GM9" t="n">
+        <v/>
+      </c>
+      <c r="GN9" t="n">
+        <v/>
+      </c>
+      <c r="GO9" t="n">
+        <v/>
+      </c>
+      <c r="GP9" t="n">
+        <v/>
+      </c>
+      <c r="GQ9" t="n">
+        <v/>
+      </c>
+      <c r="GR9" t="n">
+        <v/>
+      </c>
+      <c r="GS9" t="n">
+        <v/>
+      </c>
+      <c r="GT9" t="n">
+        <v/>
+      </c>
+      <c r="GU9" t="n">
+        <v/>
+      </c>
+      <c r="GV9" t="n">
+        <v/>
+      </c>
+      <c r="GW9" t="n">
+        <v/>
+      </c>
+      <c r="GX9" t="n">
+        <v/>
+      </c>
+      <c r="GY9" t="n">
+        <v/>
+      </c>
+      <c r="GZ9" t="n">
+        <v/>
+      </c>
+      <c r="HA9" t="n">
+        <v/>
+      </c>
+      <c r="HB9" t="n">
+        <v/>
+      </c>
+      <c r="HC9" t="n">
+        <v/>
+      </c>
+      <c r="HD9" t="n">
+        <v/>
+      </c>
+      <c r="HE9" t="n">
+        <v/>
+      </c>
+      <c r="HF9" t="n">
+        <v/>
+      </c>
+      <c r="HG9" t="n">
+        <v/>
+      </c>
+      <c r="HH9" t="n">
+        <v/>
+      </c>
+      <c r="HI9" t="n">
+        <v/>
+      </c>
+      <c r="HJ9" t="n">
+        <v/>
+      </c>
+      <c r="HK9" t="n">
+        <v/>
+      </c>
+      <c r="HL9" t="n">
+        <v/>
+      </c>
+      <c r="HM9" t="n">
+        <v/>
+      </c>
+      <c r="HN9" t="n">
+        <v/>
+      </c>
+      <c r="HO9" t="n">
+        <v/>
+      </c>
+      <c r="HP9" t="n">
+        <v/>
+      </c>
+      <c r="HQ9" t="n">
+        <v/>
+      </c>
+      <c r="HR9" t="n">
+        <v/>
+      </c>
+      <c r="HS9" t="n">
+        <v/>
+      </c>
+      <c r="HT9" t="n">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6463,6 +7618,171 @@
       <c r="FQ10" t="n">
         <v>0.7751195310355163</v>
       </c>
+      <c r="FR10" t="n">
+        <v/>
+      </c>
+      <c r="FS10" t="n">
+        <v/>
+      </c>
+      <c r="FT10" t="n">
+        <v/>
+      </c>
+      <c r="FU10" t="n">
+        <v/>
+      </c>
+      <c r="FV10" t="n">
+        <v/>
+      </c>
+      <c r="FW10" t="n">
+        <v/>
+      </c>
+      <c r="FX10" t="n">
+        <v/>
+      </c>
+      <c r="FY10" t="n">
+        <v/>
+      </c>
+      <c r="FZ10" t="n">
+        <v/>
+      </c>
+      <c r="GA10" t="n">
+        <v/>
+      </c>
+      <c r="GB10" t="n">
+        <v/>
+      </c>
+      <c r="GC10" t="n">
+        <v/>
+      </c>
+      <c r="GD10" t="n">
+        <v/>
+      </c>
+      <c r="GE10" t="n">
+        <v/>
+      </c>
+      <c r="GF10" t="n">
+        <v/>
+      </c>
+      <c r="GG10" t="n">
+        <v/>
+      </c>
+      <c r="GH10" t="n">
+        <v/>
+      </c>
+      <c r="GI10" t="n">
+        <v/>
+      </c>
+      <c r="GJ10" t="n">
+        <v/>
+      </c>
+      <c r="GK10" t="n">
+        <v/>
+      </c>
+      <c r="GL10" t="n">
+        <v/>
+      </c>
+      <c r="GM10" t="n">
+        <v/>
+      </c>
+      <c r="GN10" t="n">
+        <v/>
+      </c>
+      <c r="GO10" t="n">
+        <v/>
+      </c>
+      <c r="GP10" t="n">
+        <v/>
+      </c>
+      <c r="GQ10" t="n">
+        <v/>
+      </c>
+      <c r="GR10" t="n">
+        <v/>
+      </c>
+      <c r="GS10" t="n">
+        <v/>
+      </c>
+      <c r="GT10" t="n">
+        <v/>
+      </c>
+      <c r="GU10" t="n">
+        <v/>
+      </c>
+      <c r="GV10" t="n">
+        <v/>
+      </c>
+      <c r="GW10" t="n">
+        <v/>
+      </c>
+      <c r="GX10" t="n">
+        <v/>
+      </c>
+      <c r="GY10" t="n">
+        <v/>
+      </c>
+      <c r="GZ10" t="n">
+        <v/>
+      </c>
+      <c r="HA10" t="n">
+        <v/>
+      </c>
+      <c r="HB10" t="n">
+        <v/>
+      </c>
+      <c r="HC10" t="n">
+        <v/>
+      </c>
+      <c r="HD10" t="n">
+        <v/>
+      </c>
+      <c r="HE10" t="n">
+        <v/>
+      </c>
+      <c r="HF10" t="n">
+        <v/>
+      </c>
+      <c r="HG10" t="n">
+        <v/>
+      </c>
+      <c r="HH10" t="n">
+        <v/>
+      </c>
+      <c r="HI10" t="n">
+        <v/>
+      </c>
+      <c r="HJ10" t="n">
+        <v/>
+      </c>
+      <c r="HK10" t="n">
+        <v/>
+      </c>
+      <c r="HL10" t="n">
+        <v/>
+      </c>
+      <c r="HM10" t="n">
+        <v/>
+      </c>
+      <c r="HN10" t="n">
+        <v/>
+      </c>
+      <c r="HO10" t="n">
+        <v/>
+      </c>
+      <c r="HP10" t="n">
+        <v/>
+      </c>
+      <c r="HQ10" t="n">
+        <v/>
+      </c>
+      <c r="HR10" t="n">
+        <v/>
+      </c>
+      <c r="HS10" t="n">
+        <v/>
+      </c>
+      <c r="HT10" t="n">
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6988,6 +8308,171 @@
       <c r="FQ11" t="n">
         <v>0.3471850069157838</v>
       </c>
+      <c r="FR11" t="n">
+        <v/>
+      </c>
+      <c r="FS11" t="n">
+        <v/>
+      </c>
+      <c r="FT11" t="n">
+        <v/>
+      </c>
+      <c r="FU11" t="n">
+        <v/>
+      </c>
+      <c r="FV11" t="n">
+        <v/>
+      </c>
+      <c r="FW11" t="n">
+        <v/>
+      </c>
+      <c r="FX11" t="n">
+        <v/>
+      </c>
+      <c r="FY11" t="n">
+        <v/>
+      </c>
+      <c r="FZ11" t="n">
+        <v/>
+      </c>
+      <c r="GA11" t="n">
+        <v/>
+      </c>
+      <c r="GB11" t="n">
+        <v/>
+      </c>
+      <c r="GC11" t="n">
+        <v/>
+      </c>
+      <c r="GD11" t="n">
+        <v/>
+      </c>
+      <c r="GE11" t="n">
+        <v/>
+      </c>
+      <c r="GF11" t="n">
+        <v/>
+      </c>
+      <c r="GG11" t="n">
+        <v/>
+      </c>
+      <c r="GH11" t="n">
+        <v/>
+      </c>
+      <c r="GI11" t="n">
+        <v/>
+      </c>
+      <c r="GJ11" t="n">
+        <v/>
+      </c>
+      <c r="GK11" t="n">
+        <v/>
+      </c>
+      <c r="GL11" t="n">
+        <v/>
+      </c>
+      <c r="GM11" t="n">
+        <v/>
+      </c>
+      <c r="GN11" t="n">
+        <v/>
+      </c>
+      <c r="GO11" t="n">
+        <v/>
+      </c>
+      <c r="GP11" t="n">
+        <v/>
+      </c>
+      <c r="GQ11" t="n">
+        <v/>
+      </c>
+      <c r="GR11" t="n">
+        <v/>
+      </c>
+      <c r="GS11" t="n">
+        <v/>
+      </c>
+      <c r="GT11" t="n">
+        <v/>
+      </c>
+      <c r="GU11" t="n">
+        <v/>
+      </c>
+      <c r="GV11" t="n">
+        <v/>
+      </c>
+      <c r="GW11" t="n">
+        <v/>
+      </c>
+      <c r="GX11" t="n">
+        <v/>
+      </c>
+      <c r="GY11" t="n">
+        <v/>
+      </c>
+      <c r="GZ11" t="n">
+        <v/>
+      </c>
+      <c r="HA11" t="n">
+        <v/>
+      </c>
+      <c r="HB11" t="n">
+        <v/>
+      </c>
+      <c r="HC11" t="n">
+        <v/>
+      </c>
+      <c r="HD11" t="n">
+        <v/>
+      </c>
+      <c r="HE11" t="n">
+        <v/>
+      </c>
+      <c r="HF11" t="n">
+        <v/>
+      </c>
+      <c r="HG11" t="n">
+        <v/>
+      </c>
+      <c r="HH11" t="n">
+        <v/>
+      </c>
+      <c r="HI11" t="n">
+        <v/>
+      </c>
+      <c r="HJ11" t="n">
+        <v/>
+      </c>
+      <c r="HK11" t="n">
+        <v/>
+      </c>
+      <c r="HL11" t="n">
+        <v/>
+      </c>
+      <c r="HM11" t="n">
+        <v/>
+      </c>
+      <c r="HN11" t="n">
+        <v/>
+      </c>
+      <c r="HO11" t="n">
+        <v/>
+      </c>
+      <c r="HP11" t="n">
+        <v/>
+      </c>
+      <c r="HQ11" t="n">
+        <v/>
+      </c>
+      <c r="HR11" t="n">
+        <v/>
+      </c>
+      <c r="HS11" t="n">
+        <v/>
+      </c>
+      <c r="HT11" t="n">
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -7513,6 +8998,171 @@
       <c r="FQ12" t="n">
         <v>0.4706339270537613</v>
       </c>
+      <c r="FR12" t="n">
+        <v/>
+      </c>
+      <c r="FS12" t="n">
+        <v/>
+      </c>
+      <c r="FT12" t="n">
+        <v/>
+      </c>
+      <c r="FU12" t="n">
+        <v/>
+      </c>
+      <c r="FV12" t="n">
+        <v/>
+      </c>
+      <c r="FW12" t="n">
+        <v/>
+      </c>
+      <c r="FX12" t="n">
+        <v/>
+      </c>
+      <c r="FY12" t="n">
+        <v/>
+      </c>
+      <c r="FZ12" t="n">
+        <v/>
+      </c>
+      <c r="GA12" t="n">
+        <v/>
+      </c>
+      <c r="GB12" t="n">
+        <v/>
+      </c>
+      <c r="GC12" t="n">
+        <v/>
+      </c>
+      <c r="GD12" t="n">
+        <v/>
+      </c>
+      <c r="GE12" t="n">
+        <v/>
+      </c>
+      <c r="GF12" t="n">
+        <v/>
+      </c>
+      <c r="GG12" t="n">
+        <v/>
+      </c>
+      <c r="GH12" t="n">
+        <v/>
+      </c>
+      <c r="GI12" t="n">
+        <v/>
+      </c>
+      <c r="GJ12" t="n">
+        <v/>
+      </c>
+      <c r="GK12" t="n">
+        <v/>
+      </c>
+      <c r="GL12" t="n">
+        <v/>
+      </c>
+      <c r="GM12" t="n">
+        <v/>
+      </c>
+      <c r="GN12" t="n">
+        <v/>
+      </c>
+      <c r="GO12" t="n">
+        <v/>
+      </c>
+      <c r="GP12" t="n">
+        <v/>
+      </c>
+      <c r="GQ12" t="n">
+        <v/>
+      </c>
+      <c r="GR12" t="n">
+        <v/>
+      </c>
+      <c r="GS12" t="n">
+        <v/>
+      </c>
+      <c r="GT12" t="n">
+        <v/>
+      </c>
+      <c r="GU12" t="n">
+        <v/>
+      </c>
+      <c r="GV12" t="n">
+        <v/>
+      </c>
+      <c r="GW12" t="n">
+        <v/>
+      </c>
+      <c r="GX12" t="n">
+        <v/>
+      </c>
+      <c r="GY12" t="n">
+        <v/>
+      </c>
+      <c r="GZ12" t="n">
+        <v/>
+      </c>
+      <c r="HA12" t="n">
+        <v/>
+      </c>
+      <c r="HB12" t="n">
+        <v/>
+      </c>
+      <c r="HC12" t="n">
+        <v/>
+      </c>
+      <c r="HD12" t="n">
+        <v/>
+      </c>
+      <c r="HE12" t="n">
+        <v/>
+      </c>
+      <c r="HF12" t="n">
+        <v/>
+      </c>
+      <c r="HG12" t="n">
+        <v/>
+      </c>
+      <c r="HH12" t="n">
+        <v/>
+      </c>
+      <c r="HI12" t="n">
+        <v/>
+      </c>
+      <c r="HJ12" t="n">
+        <v/>
+      </c>
+      <c r="HK12" t="n">
+        <v/>
+      </c>
+      <c r="HL12" t="n">
+        <v/>
+      </c>
+      <c r="HM12" t="n">
+        <v/>
+      </c>
+      <c r="HN12" t="n">
+        <v/>
+      </c>
+      <c r="HO12" t="n">
+        <v/>
+      </c>
+      <c r="HP12" t="n">
+        <v/>
+      </c>
+      <c r="HQ12" t="n">
+        <v/>
+      </c>
+      <c r="HR12" t="n">
+        <v/>
+      </c>
+      <c r="HS12" t="n">
+        <v/>
+      </c>
+      <c r="HT12" t="n">
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -8038,6 +9688,171 @@
       <c r="FQ13" t="n">
         <v>0.4425606563864467</v>
       </c>
+      <c r="FR13" t="n">
+        <v/>
+      </c>
+      <c r="FS13" t="n">
+        <v/>
+      </c>
+      <c r="FT13" t="n">
+        <v/>
+      </c>
+      <c r="FU13" t="n">
+        <v/>
+      </c>
+      <c r="FV13" t="n">
+        <v/>
+      </c>
+      <c r="FW13" t="n">
+        <v/>
+      </c>
+      <c r="FX13" t="n">
+        <v/>
+      </c>
+      <c r="FY13" t="n">
+        <v/>
+      </c>
+      <c r="FZ13" t="n">
+        <v/>
+      </c>
+      <c r="GA13" t="n">
+        <v/>
+      </c>
+      <c r="GB13" t="n">
+        <v/>
+      </c>
+      <c r="GC13" t="n">
+        <v/>
+      </c>
+      <c r="GD13" t="n">
+        <v/>
+      </c>
+      <c r="GE13" t="n">
+        <v/>
+      </c>
+      <c r="GF13" t="n">
+        <v/>
+      </c>
+      <c r="GG13" t="n">
+        <v/>
+      </c>
+      <c r="GH13" t="n">
+        <v/>
+      </c>
+      <c r="GI13" t="n">
+        <v/>
+      </c>
+      <c r="GJ13" t="n">
+        <v/>
+      </c>
+      <c r="GK13" t="n">
+        <v/>
+      </c>
+      <c r="GL13" t="n">
+        <v/>
+      </c>
+      <c r="GM13" t="n">
+        <v/>
+      </c>
+      <c r="GN13" t="n">
+        <v/>
+      </c>
+      <c r="GO13" t="n">
+        <v/>
+      </c>
+      <c r="GP13" t="n">
+        <v/>
+      </c>
+      <c r="GQ13" t="n">
+        <v/>
+      </c>
+      <c r="GR13" t="n">
+        <v/>
+      </c>
+      <c r="GS13" t="n">
+        <v/>
+      </c>
+      <c r="GT13" t="n">
+        <v/>
+      </c>
+      <c r="GU13" t="n">
+        <v/>
+      </c>
+      <c r="GV13" t="n">
+        <v/>
+      </c>
+      <c r="GW13" t="n">
+        <v/>
+      </c>
+      <c r="GX13" t="n">
+        <v/>
+      </c>
+      <c r="GY13" t="n">
+        <v/>
+      </c>
+      <c r="GZ13" t="n">
+        <v/>
+      </c>
+      <c r="HA13" t="n">
+        <v/>
+      </c>
+      <c r="HB13" t="n">
+        <v/>
+      </c>
+      <c r="HC13" t="n">
+        <v/>
+      </c>
+      <c r="HD13" t="n">
+        <v/>
+      </c>
+      <c r="HE13" t="n">
+        <v/>
+      </c>
+      <c r="HF13" t="n">
+        <v/>
+      </c>
+      <c r="HG13" t="n">
+        <v/>
+      </c>
+      <c r="HH13" t="n">
+        <v/>
+      </c>
+      <c r="HI13" t="n">
+        <v/>
+      </c>
+      <c r="HJ13" t="n">
+        <v/>
+      </c>
+      <c r="HK13" t="n">
+        <v/>
+      </c>
+      <c r="HL13" t="n">
+        <v/>
+      </c>
+      <c r="HM13" t="n">
+        <v/>
+      </c>
+      <c r="HN13" t="n">
+        <v/>
+      </c>
+      <c r="HO13" t="n">
+        <v/>
+      </c>
+      <c r="HP13" t="n">
+        <v/>
+      </c>
+      <c r="HQ13" t="n">
+        <v/>
+      </c>
+      <c r="HR13" t="n">
+        <v/>
+      </c>
+      <c r="HS13" t="n">
+        <v/>
+      </c>
+      <c r="HT13" t="n">
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -8563,6 +10378,171 @@
       <c r="FQ14" t="n">
         <v>0.6863002226203669</v>
       </c>
+      <c r="FR14" t="n">
+        <v/>
+      </c>
+      <c r="FS14" t="n">
+        <v/>
+      </c>
+      <c r="FT14" t="n">
+        <v/>
+      </c>
+      <c r="FU14" t="n">
+        <v/>
+      </c>
+      <c r="FV14" t="n">
+        <v/>
+      </c>
+      <c r="FW14" t="n">
+        <v/>
+      </c>
+      <c r="FX14" t="n">
+        <v/>
+      </c>
+      <c r="FY14" t="n">
+        <v/>
+      </c>
+      <c r="FZ14" t="n">
+        <v/>
+      </c>
+      <c r="GA14" t="n">
+        <v/>
+      </c>
+      <c r="GB14" t="n">
+        <v/>
+      </c>
+      <c r="GC14" t="n">
+        <v/>
+      </c>
+      <c r="GD14" t="n">
+        <v/>
+      </c>
+      <c r="GE14" t="n">
+        <v/>
+      </c>
+      <c r="GF14" t="n">
+        <v/>
+      </c>
+      <c r="GG14" t="n">
+        <v/>
+      </c>
+      <c r="GH14" t="n">
+        <v/>
+      </c>
+      <c r="GI14" t="n">
+        <v/>
+      </c>
+      <c r="GJ14" t="n">
+        <v/>
+      </c>
+      <c r="GK14" t="n">
+        <v/>
+      </c>
+      <c r="GL14" t="n">
+        <v/>
+      </c>
+      <c r="GM14" t="n">
+        <v/>
+      </c>
+      <c r="GN14" t="n">
+        <v/>
+      </c>
+      <c r="GO14" t="n">
+        <v/>
+      </c>
+      <c r="GP14" t="n">
+        <v/>
+      </c>
+      <c r="GQ14" t="n">
+        <v/>
+      </c>
+      <c r="GR14" t="n">
+        <v/>
+      </c>
+      <c r="GS14" t="n">
+        <v/>
+      </c>
+      <c r="GT14" t="n">
+        <v/>
+      </c>
+      <c r="GU14" t="n">
+        <v/>
+      </c>
+      <c r="GV14" t="n">
+        <v/>
+      </c>
+      <c r="GW14" t="n">
+        <v/>
+      </c>
+      <c r="GX14" t="n">
+        <v/>
+      </c>
+      <c r="GY14" t="n">
+        <v/>
+      </c>
+      <c r="GZ14" t="n">
+        <v/>
+      </c>
+      <c r="HA14" t="n">
+        <v/>
+      </c>
+      <c r="HB14" t="n">
+        <v/>
+      </c>
+      <c r="HC14" t="n">
+        <v/>
+      </c>
+      <c r="HD14" t="n">
+        <v/>
+      </c>
+      <c r="HE14" t="n">
+        <v/>
+      </c>
+      <c r="HF14" t="n">
+        <v/>
+      </c>
+      <c r="HG14" t="n">
+        <v/>
+      </c>
+      <c r="HH14" t="n">
+        <v/>
+      </c>
+      <c r="HI14" t="n">
+        <v/>
+      </c>
+      <c r="HJ14" t="n">
+        <v/>
+      </c>
+      <c r="HK14" t="n">
+        <v/>
+      </c>
+      <c r="HL14" t="n">
+        <v/>
+      </c>
+      <c r="HM14" t="n">
+        <v/>
+      </c>
+      <c r="HN14" t="n">
+        <v/>
+      </c>
+      <c r="HO14" t="n">
+        <v/>
+      </c>
+      <c r="HP14" t="n">
+        <v/>
+      </c>
+      <c r="HQ14" t="n">
+        <v/>
+      </c>
+      <c r="HR14" t="n">
+        <v/>
+      </c>
+      <c r="HS14" t="n">
+        <v/>
+      </c>
+      <c r="HT14" t="n">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -9088,6 +11068,171 @@
       <c r="FQ15" t="n">
         <v>0.7485094932497678</v>
       </c>
+      <c r="FR15" t="n">
+        <v/>
+      </c>
+      <c r="FS15" t="n">
+        <v/>
+      </c>
+      <c r="FT15" t="n">
+        <v/>
+      </c>
+      <c r="FU15" t="n">
+        <v/>
+      </c>
+      <c r="FV15" t="n">
+        <v/>
+      </c>
+      <c r="FW15" t="n">
+        <v/>
+      </c>
+      <c r="FX15" t="n">
+        <v/>
+      </c>
+      <c r="FY15" t="n">
+        <v/>
+      </c>
+      <c r="FZ15" t="n">
+        <v/>
+      </c>
+      <c r="GA15" t="n">
+        <v/>
+      </c>
+      <c r="GB15" t="n">
+        <v/>
+      </c>
+      <c r="GC15" t="n">
+        <v/>
+      </c>
+      <c r="GD15" t="n">
+        <v/>
+      </c>
+      <c r="GE15" t="n">
+        <v/>
+      </c>
+      <c r="GF15" t="n">
+        <v/>
+      </c>
+      <c r="GG15" t="n">
+        <v/>
+      </c>
+      <c r="GH15" t="n">
+        <v/>
+      </c>
+      <c r="GI15" t="n">
+        <v/>
+      </c>
+      <c r="GJ15" t="n">
+        <v/>
+      </c>
+      <c r="GK15" t="n">
+        <v/>
+      </c>
+      <c r="GL15" t="n">
+        <v/>
+      </c>
+      <c r="GM15" t="n">
+        <v/>
+      </c>
+      <c r="GN15" t="n">
+        <v/>
+      </c>
+      <c r="GO15" t="n">
+        <v/>
+      </c>
+      <c r="GP15" t="n">
+        <v/>
+      </c>
+      <c r="GQ15" t="n">
+        <v/>
+      </c>
+      <c r="GR15" t="n">
+        <v/>
+      </c>
+      <c r="GS15" t="n">
+        <v/>
+      </c>
+      <c r="GT15" t="n">
+        <v/>
+      </c>
+      <c r="GU15" t="n">
+        <v/>
+      </c>
+      <c r="GV15" t="n">
+        <v/>
+      </c>
+      <c r="GW15" t="n">
+        <v/>
+      </c>
+      <c r="GX15" t="n">
+        <v/>
+      </c>
+      <c r="GY15" t="n">
+        <v/>
+      </c>
+      <c r="GZ15" t="n">
+        <v/>
+      </c>
+      <c r="HA15" t="n">
+        <v/>
+      </c>
+      <c r="HB15" t="n">
+        <v/>
+      </c>
+      <c r="HC15" t="n">
+        <v/>
+      </c>
+      <c r="HD15" t="n">
+        <v/>
+      </c>
+      <c r="HE15" t="n">
+        <v/>
+      </c>
+      <c r="HF15" t="n">
+        <v/>
+      </c>
+      <c r="HG15" t="n">
+        <v/>
+      </c>
+      <c r="HH15" t="n">
+        <v/>
+      </c>
+      <c r="HI15" t="n">
+        <v/>
+      </c>
+      <c r="HJ15" t="n">
+        <v/>
+      </c>
+      <c r="HK15" t="n">
+        <v/>
+      </c>
+      <c r="HL15" t="n">
+        <v/>
+      </c>
+      <c r="HM15" t="n">
+        <v/>
+      </c>
+      <c r="HN15" t="n">
+        <v/>
+      </c>
+      <c r="HO15" t="n">
+        <v/>
+      </c>
+      <c r="HP15" t="n">
+        <v/>
+      </c>
+      <c r="HQ15" t="n">
+        <v/>
+      </c>
+      <c r="HR15" t="n">
+        <v/>
+      </c>
+      <c r="HS15" t="n">
+        <v/>
+      </c>
+      <c r="HT15" t="n">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -9613,6 +11758,171 @@
       <c r="FQ16" t="n">
         <v>0.6941502650794812</v>
       </c>
+      <c r="FR16" t="n">
+        <v/>
+      </c>
+      <c r="FS16" t="n">
+        <v/>
+      </c>
+      <c r="FT16" t="n">
+        <v/>
+      </c>
+      <c r="FU16" t="n">
+        <v/>
+      </c>
+      <c r="FV16" t="n">
+        <v/>
+      </c>
+      <c r="FW16" t="n">
+        <v/>
+      </c>
+      <c r="FX16" t="n">
+        <v/>
+      </c>
+      <c r="FY16" t="n">
+        <v/>
+      </c>
+      <c r="FZ16" t="n">
+        <v/>
+      </c>
+      <c r="GA16" t="n">
+        <v/>
+      </c>
+      <c r="GB16" t="n">
+        <v/>
+      </c>
+      <c r="GC16" t="n">
+        <v/>
+      </c>
+      <c r="GD16" t="n">
+        <v/>
+      </c>
+      <c r="GE16" t="n">
+        <v/>
+      </c>
+      <c r="GF16" t="n">
+        <v/>
+      </c>
+      <c r="GG16" t="n">
+        <v/>
+      </c>
+      <c r="GH16" t="n">
+        <v/>
+      </c>
+      <c r="GI16" t="n">
+        <v/>
+      </c>
+      <c r="GJ16" t="n">
+        <v/>
+      </c>
+      <c r="GK16" t="n">
+        <v/>
+      </c>
+      <c r="GL16" t="n">
+        <v/>
+      </c>
+      <c r="GM16" t="n">
+        <v/>
+      </c>
+      <c r="GN16" t="n">
+        <v/>
+      </c>
+      <c r="GO16" t="n">
+        <v/>
+      </c>
+      <c r="GP16" t="n">
+        <v/>
+      </c>
+      <c r="GQ16" t="n">
+        <v/>
+      </c>
+      <c r="GR16" t="n">
+        <v/>
+      </c>
+      <c r="GS16" t="n">
+        <v/>
+      </c>
+      <c r="GT16" t="n">
+        <v/>
+      </c>
+      <c r="GU16" t="n">
+        <v/>
+      </c>
+      <c r="GV16" t="n">
+        <v/>
+      </c>
+      <c r="GW16" t="n">
+        <v/>
+      </c>
+      <c r="GX16" t="n">
+        <v/>
+      </c>
+      <c r="GY16" t="n">
+        <v/>
+      </c>
+      <c r="GZ16" t="n">
+        <v/>
+      </c>
+      <c r="HA16" t="n">
+        <v/>
+      </c>
+      <c r="HB16" t="n">
+        <v/>
+      </c>
+      <c r="HC16" t="n">
+        <v/>
+      </c>
+      <c r="HD16" t="n">
+        <v/>
+      </c>
+      <c r="HE16" t="n">
+        <v/>
+      </c>
+      <c r="HF16" t="n">
+        <v/>
+      </c>
+      <c r="HG16" t="n">
+        <v/>
+      </c>
+      <c r="HH16" t="n">
+        <v/>
+      </c>
+      <c r="HI16" t="n">
+        <v/>
+      </c>
+      <c r="HJ16" t="n">
+        <v/>
+      </c>
+      <c r="HK16" t="n">
+        <v/>
+      </c>
+      <c r="HL16" t="n">
+        <v/>
+      </c>
+      <c r="HM16" t="n">
+        <v/>
+      </c>
+      <c r="HN16" t="n">
+        <v/>
+      </c>
+      <c r="HO16" t="n">
+        <v/>
+      </c>
+      <c r="HP16" t="n">
+        <v/>
+      </c>
+      <c r="HQ16" t="n">
+        <v/>
+      </c>
+      <c r="HR16" t="n">
+        <v/>
+      </c>
+      <c r="HS16" t="n">
+        <v/>
+      </c>
+      <c r="HT16" t="n">
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -10138,6 +12448,171 @@
       <c r="FQ17" t="n">
         <v>0.8486151471889958</v>
       </c>
+      <c r="FR17" t="n">
+        <v/>
+      </c>
+      <c r="FS17" t="n">
+        <v/>
+      </c>
+      <c r="FT17" t="n">
+        <v/>
+      </c>
+      <c r="FU17" t="n">
+        <v/>
+      </c>
+      <c r="FV17" t="n">
+        <v/>
+      </c>
+      <c r="FW17" t="n">
+        <v/>
+      </c>
+      <c r="FX17" t="n">
+        <v/>
+      </c>
+      <c r="FY17" t="n">
+        <v/>
+      </c>
+      <c r="FZ17" t="n">
+        <v/>
+      </c>
+      <c r="GA17" t="n">
+        <v/>
+      </c>
+      <c r="GB17" t="n">
+        <v/>
+      </c>
+      <c r="GC17" t="n">
+        <v/>
+      </c>
+      <c r="GD17" t="n">
+        <v/>
+      </c>
+      <c r="GE17" t="n">
+        <v/>
+      </c>
+      <c r="GF17" t="n">
+        <v/>
+      </c>
+      <c r="GG17" t="n">
+        <v/>
+      </c>
+      <c r="GH17" t="n">
+        <v/>
+      </c>
+      <c r="GI17" t="n">
+        <v/>
+      </c>
+      <c r="GJ17" t="n">
+        <v/>
+      </c>
+      <c r="GK17" t="n">
+        <v/>
+      </c>
+      <c r="GL17" t="n">
+        <v/>
+      </c>
+      <c r="GM17" t="n">
+        <v/>
+      </c>
+      <c r="GN17" t="n">
+        <v/>
+      </c>
+      <c r="GO17" t="n">
+        <v/>
+      </c>
+      <c r="GP17" t="n">
+        <v/>
+      </c>
+      <c r="GQ17" t="n">
+        <v/>
+      </c>
+      <c r="GR17" t="n">
+        <v/>
+      </c>
+      <c r="GS17" t="n">
+        <v/>
+      </c>
+      <c r="GT17" t="n">
+        <v/>
+      </c>
+      <c r="GU17" t="n">
+        <v/>
+      </c>
+      <c r="GV17" t="n">
+        <v/>
+      </c>
+      <c r="GW17" t="n">
+        <v/>
+      </c>
+      <c r="GX17" t="n">
+        <v/>
+      </c>
+      <c r="GY17" t="n">
+        <v/>
+      </c>
+      <c r="GZ17" t="n">
+        <v/>
+      </c>
+      <c r="HA17" t="n">
+        <v/>
+      </c>
+      <c r="HB17" t="n">
+        <v/>
+      </c>
+      <c r="HC17" t="n">
+        <v/>
+      </c>
+      <c r="HD17" t="n">
+        <v/>
+      </c>
+      <c r="HE17" t="n">
+        <v/>
+      </c>
+      <c r="HF17" t="n">
+        <v/>
+      </c>
+      <c r="HG17" t="n">
+        <v/>
+      </c>
+      <c r="HH17" t="n">
+        <v/>
+      </c>
+      <c r="HI17" t="n">
+        <v/>
+      </c>
+      <c r="HJ17" t="n">
+        <v/>
+      </c>
+      <c r="HK17" t="n">
+        <v/>
+      </c>
+      <c r="HL17" t="n">
+        <v/>
+      </c>
+      <c r="HM17" t="n">
+        <v/>
+      </c>
+      <c r="HN17" t="n">
+        <v/>
+      </c>
+      <c r="HO17" t="n">
+        <v/>
+      </c>
+      <c r="HP17" t="n">
+        <v/>
+      </c>
+      <c r="HQ17" t="n">
+        <v/>
+      </c>
+      <c r="HR17" t="n">
+        <v/>
+      </c>
+      <c r="HS17" t="n">
+        <v/>
+      </c>
+      <c r="HT17" t="n">
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -10663,6 +13138,171 @@
       <c r="FQ18" t="n">
         <v>0.6751723604675262</v>
       </c>
+      <c r="FR18" t="n">
+        <v/>
+      </c>
+      <c r="FS18" t="n">
+        <v/>
+      </c>
+      <c r="FT18" t="n">
+        <v/>
+      </c>
+      <c r="FU18" t="n">
+        <v/>
+      </c>
+      <c r="FV18" t="n">
+        <v/>
+      </c>
+      <c r="FW18" t="n">
+        <v/>
+      </c>
+      <c r="FX18" t="n">
+        <v/>
+      </c>
+      <c r="FY18" t="n">
+        <v/>
+      </c>
+      <c r="FZ18" t="n">
+        <v/>
+      </c>
+      <c r="GA18" t="n">
+        <v/>
+      </c>
+      <c r="GB18" t="n">
+        <v/>
+      </c>
+      <c r="GC18" t="n">
+        <v/>
+      </c>
+      <c r="GD18" t="n">
+        <v/>
+      </c>
+      <c r="GE18" t="n">
+        <v/>
+      </c>
+      <c r="GF18" t="n">
+        <v/>
+      </c>
+      <c r="GG18" t="n">
+        <v/>
+      </c>
+      <c r="GH18" t="n">
+        <v/>
+      </c>
+      <c r="GI18" t="n">
+        <v/>
+      </c>
+      <c r="GJ18" t="n">
+        <v/>
+      </c>
+      <c r="GK18" t="n">
+        <v/>
+      </c>
+      <c r="GL18" t="n">
+        <v/>
+      </c>
+      <c r="GM18" t="n">
+        <v/>
+      </c>
+      <c r="GN18" t="n">
+        <v/>
+      </c>
+      <c r="GO18" t="n">
+        <v/>
+      </c>
+      <c r="GP18" t="n">
+        <v/>
+      </c>
+      <c r="GQ18" t="n">
+        <v/>
+      </c>
+      <c r="GR18" t="n">
+        <v/>
+      </c>
+      <c r="GS18" t="n">
+        <v/>
+      </c>
+      <c r="GT18" t="n">
+        <v/>
+      </c>
+      <c r="GU18" t="n">
+        <v/>
+      </c>
+      <c r="GV18" t="n">
+        <v/>
+      </c>
+      <c r="GW18" t="n">
+        <v/>
+      </c>
+      <c r="GX18" t="n">
+        <v/>
+      </c>
+      <c r="GY18" t="n">
+        <v/>
+      </c>
+      <c r="GZ18" t="n">
+        <v/>
+      </c>
+      <c r="HA18" t="n">
+        <v/>
+      </c>
+      <c r="HB18" t="n">
+        <v/>
+      </c>
+      <c r="HC18" t="n">
+        <v/>
+      </c>
+      <c r="HD18" t="n">
+        <v/>
+      </c>
+      <c r="HE18" t="n">
+        <v/>
+      </c>
+      <c r="HF18" t="n">
+        <v/>
+      </c>
+      <c r="HG18" t="n">
+        <v/>
+      </c>
+      <c r="HH18" t="n">
+        <v/>
+      </c>
+      <c r="HI18" t="n">
+        <v/>
+      </c>
+      <c r="HJ18" t="n">
+        <v/>
+      </c>
+      <c r="HK18" t="n">
+        <v/>
+      </c>
+      <c r="HL18" t="n">
+        <v/>
+      </c>
+      <c r="HM18" t="n">
+        <v/>
+      </c>
+      <c r="HN18" t="n">
+        <v/>
+      </c>
+      <c r="HO18" t="n">
+        <v/>
+      </c>
+      <c r="HP18" t="n">
+        <v/>
+      </c>
+      <c r="HQ18" t="n">
+        <v/>
+      </c>
+      <c r="HR18" t="n">
+        <v/>
+      </c>
+      <c r="HS18" t="n">
+        <v/>
+      </c>
+      <c r="HT18" t="n">
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -11188,6 +13828,171 @@
       <c r="FQ19" t="n">
         <v>0.8041945454926983</v>
       </c>
+      <c r="FR19" t="n">
+        <v/>
+      </c>
+      <c r="FS19" t="n">
+        <v/>
+      </c>
+      <c r="FT19" t="n">
+        <v/>
+      </c>
+      <c r="FU19" t="n">
+        <v/>
+      </c>
+      <c r="FV19" t="n">
+        <v/>
+      </c>
+      <c r="FW19" t="n">
+        <v/>
+      </c>
+      <c r="FX19" t="n">
+        <v/>
+      </c>
+      <c r="FY19" t="n">
+        <v/>
+      </c>
+      <c r="FZ19" t="n">
+        <v/>
+      </c>
+      <c r="GA19" t="n">
+        <v/>
+      </c>
+      <c r="GB19" t="n">
+        <v/>
+      </c>
+      <c r="GC19" t="n">
+        <v/>
+      </c>
+      <c r="GD19" t="n">
+        <v/>
+      </c>
+      <c r="GE19" t="n">
+        <v/>
+      </c>
+      <c r="GF19" t="n">
+        <v/>
+      </c>
+      <c r="GG19" t="n">
+        <v/>
+      </c>
+      <c r="GH19" t="n">
+        <v/>
+      </c>
+      <c r="GI19" t="n">
+        <v/>
+      </c>
+      <c r="GJ19" t="n">
+        <v/>
+      </c>
+      <c r="GK19" t="n">
+        <v/>
+      </c>
+      <c r="GL19" t="n">
+        <v/>
+      </c>
+      <c r="GM19" t="n">
+        <v/>
+      </c>
+      <c r="GN19" t="n">
+        <v/>
+      </c>
+      <c r="GO19" t="n">
+        <v/>
+      </c>
+      <c r="GP19" t="n">
+        <v/>
+      </c>
+      <c r="GQ19" t="n">
+        <v/>
+      </c>
+      <c r="GR19" t="n">
+        <v/>
+      </c>
+      <c r="GS19" t="n">
+        <v/>
+      </c>
+      <c r="GT19" t="n">
+        <v/>
+      </c>
+      <c r="GU19" t="n">
+        <v/>
+      </c>
+      <c r="GV19" t="n">
+        <v/>
+      </c>
+      <c r="GW19" t="n">
+        <v/>
+      </c>
+      <c r="GX19" t="n">
+        <v/>
+      </c>
+      <c r="GY19" t="n">
+        <v/>
+      </c>
+      <c r="GZ19" t="n">
+        <v/>
+      </c>
+      <c r="HA19" t="n">
+        <v/>
+      </c>
+      <c r="HB19" t="n">
+        <v/>
+      </c>
+      <c r="HC19" t="n">
+        <v/>
+      </c>
+      <c r="HD19" t="n">
+        <v/>
+      </c>
+      <c r="HE19" t="n">
+        <v/>
+      </c>
+      <c r="HF19" t="n">
+        <v/>
+      </c>
+      <c r="HG19" t="n">
+        <v/>
+      </c>
+      <c r="HH19" t="n">
+        <v/>
+      </c>
+      <c r="HI19" t="n">
+        <v/>
+      </c>
+      <c r="HJ19" t="n">
+        <v/>
+      </c>
+      <c r="HK19" t="n">
+        <v/>
+      </c>
+      <c r="HL19" t="n">
+        <v/>
+      </c>
+      <c r="HM19" t="n">
+        <v/>
+      </c>
+      <c r="HN19" t="n">
+        <v/>
+      </c>
+      <c r="HO19" t="n">
+        <v/>
+      </c>
+      <c r="HP19" t="n">
+        <v/>
+      </c>
+      <c r="HQ19" t="n">
+        <v/>
+      </c>
+      <c r="HR19" t="n">
+        <v/>
+      </c>
+      <c r="HS19" t="n">
+        <v/>
+      </c>
+      <c r="HT19" t="n">
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -11713,6 +14518,171 @@
       <c r="FQ20" t="n">
         <v>0.9744597867050284</v>
       </c>
+      <c r="FR20" t="n">
+        <v/>
+      </c>
+      <c r="FS20" t="n">
+        <v/>
+      </c>
+      <c r="FT20" t="n">
+        <v/>
+      </c>
+      <c r="FU20" t="n">
+        <v/>
+      </c>
+      <c r="FV20" t="n">
+        <v/>
+      </c>
+      <c r="FW20" t="n">
+        <v/>
+      </c>
+      <c r="FX20" t="n">
+        <v/>
+      </c>
+      <c r="FY20" t="n">
+        <v/>
+      </c>
+      <c r="FZ20" t="n">
+        <v/>
+      </c>
+      <c r="GA20" t="n">
+        <v/>
+      </c>
+      <c r="GB20" t="n">
+        <v/>
+      </c>
+      <c r="GC20" t="n">
+        <v/>
+      </c>
+      <c r="GD20" t="n">
+        <v/>
+      </c>
+      <c r="GE20" t="n">
+        <v/>
+      </c>
+      <c r="GF20" t="n">
+        <v/>
+      </c>
+      <c r="GG20" t="n">
+        <v/>
+      </c>
+      <c r="GH20" t="n">
+        <v/>
+      </c>
+      <c r="GI20" t="n">
+        <v/>
+      </c>
+      <c r="GJ20" t="n">
+        <v/>
+      </c>
+      <c r="GK20" t="n">
+        <v/>
+      </c>
+      <c r="GL20" t="n">
+        <v/>
+      </c>
+      <c r="GM20" t="n">
+        <v/>
+      </c>
+      <c r="GN20" t="n">
+        <v/>
+      </c>
+      <c r="GO20" t="n">
+        <v/>
+      </c>
+      <c r="GP20" t="n">
+        <v/>
+      </c>
+      <c r="GQ20" t="n">
+        <v/>
+      </c>
+      <c r="GR20" t="n">
+        <v/>
+      </c>
+      <c r="GS20" t="n">
+        <v/>
+      </c>
+      <c r="GT20" t="n">
+        <v/>
+      </c>
+      <c r="GU20" t="n">
+        <v/>
+      </c>
+      <c r="GV20" t="n">
+        <v/>
+      </c>
+      <c r="GW20" t="n">
+        <v/>
+      </c>
+      <c r="GX20" t="n">
+        <v/>
+      </c>
+      <c r="GY20" t="n">
+        <v/>
+      </c>
+      <c r="GZ20" t="n">
+        <v/>
+      </c>
+      <c r="HA20" t="n">
+        <v/>
+      </c>
+      <c r="HB20" t="n">
+        <v/>
+      </c>
+      <c r="HC20" t="n">
+        <v/>
+      </c>
+      <c r="HD20" t="n">
+        <v/>
+      </c>
+      <c r="HE20" t="n">
+        <v/>
+      </c>
+      <c r="HF20" t="n">
+        <v/>
+      </c>
+      <c r="HG20" t="n">
+        <v/>
+      </c>
+      <c r="HH20" t="n">
+        <v/>
+      </c>
+      <c r="HI20" t="n">
+        <v/>
+      </c>
+      <c r="HJ20" t="n">
+        <v/>
+      </c>
+      <c r="HK20" t="n">
+        <v/>
+      </c>
+      <c r="HL20" t="n">
+        <v/>
+      </c>
+      <c r="HM20" t="n">
+        <v/>
+      </c>
+      <c r="HN20" t="n">
+        <v/>
+      </c>
+      <c r="HO20" t="n">
+        <v/>
+      </c>
+      <c r="HP20" t="n">
+        <v/>
+      </c>
+      <c r="HQ20" t="n">
+        <v/>
+      </c>
+      <c r="HR20" t="n">
+        <v/>
+      </c>
+      <c r="HS20" t="n">
+        <v/>
+      </c>
+      <c r="HT20" t="n">
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -12238,6 +15208,171 @@
       <c r="FQ21" t="n">
         <v>0.5147464131898006</v>
       </c>
+      <c r="FR21" t="n">
+        <v/>
+      </c>
+      <c r="FS21" t="n">
+        <v/>
+      </c>
+      <c r="FT21" t="n">
+        <v/>
+      </c>
+      <c r="FU21" t="n">
+        <v/>
+      </c>
+      <c r="FV21" t="n">
+        <v/>
+      </c>
+      <c r="FW21" t="n">
+        <v/>
+      </c>
+      <c r="FX21" t="n">
+        <v/>
+      </c>
+      <c r="FY21" t="n">
+        <v/>
+      </c>
+      <c r="FZ21" t="n">
+        <v/>
+      </c>
+      <c r="GA21" t="n">
+        <v/>
+      </c>
+      <c r="GB21" t="n">
+        <v/>
+      </c>
+      <c r="GC21" t="n">
+        <v/>
+      </c>
+      <c r="GD21" t="n">
+        <v/>
+      </c>
+      <c r="GE21" t="n">
+        <v/>
+      </c>
+      <c r="GF21" t="n">
+        <v/>
+      </c>
+      <c r="GG21" t="n">
+        <v/>
+      </c>
+      <c r="GH21" t="n">
+        <v/>
+      </c>
+      <c r="GI21" t="n">
+        <v/>
+      </c>
+      <c r="GJ21" t="n">
+        <v/>
+      </c>
+      <c r="GK21" t="n">
+        <v/>
+      </c>
+      <c r="GL21" t="n">
+        <v/>
+      </c>
+      <c r="GM21" t="n">
+        <v/>
+      </c>
+      <c r="GN21" t="n">
+        <v/>
+      </c>
+      <c r="GO21" t="n">
+        <v/>
+      </c>
+      <c r="GP21" t="n">
+        <v/>
+      </c>
+      <c r="GQ21" t="n">
+        <v/>
+      </c>
+      <c r="GR21" t="n">
+        <v/>
+      </c>
+      <c r="GS21" t="n">
+        <v/>
+      </c>
+      <c r="GT21" t="n">
+        <v/>
+      </c>
+      <c r="GU21" t="n">
+        <v/>
+      </c>
+      <c r="GV21" t="n">
+        <v/>
+      </c>
+      <c r="GW21" t="n">
+        <v/>
+      </c>
+      <c r="GX21" t="n">
+        <v/>
+      </c>
+      <c r="GY21" t="n">
+        <v/>
+      </c>
+      <c r="GZ21" t="n">
+        <v/>
+      </c>
+      <c r="HA21" t="n">
+        <v/>
+      </c>
+      <c r="HB21" t="n">
+        <v/>
+      </c>
+      <c r="HC21" t="n">
+        <v/>
+      </c>
+      <c r="HD21" t="n">
+        <v/>
+      </c>
+      <c r="HE21" t="n">
+        <v/>
+      </c>
+      <c r="HF21" t="n">
+        <v/>
+      </c>
+      <c r="HG21" t="n">
+        <v/>
+      </c>
+      <c r="HH21" t="n">
+        <v/>
+      </c>
+      <c r="HI21" t="n">
+        <v/>
+      </c>
+      <c r="HJ21" t="n">
+        <v/>
+      </c>
+      <c r="HK21" t="n">
+        <v/>
+      </c>
+      <c r="HL21" t="n">
+        <v/>
+      </c>
+      <c r="HM21" t="n">
+        <v/>
+      </c>
+      <c r="HN21" t="n">
+        <v/>
+      </c>
+      <c r="HO21" t="n">
+        <v/>
+      </c>
+      <c r="HP21" t="n">
+        <v/>
+      </c>
+      <c r="HQ21" t="n">
+        <v/>
+      </c>
+      <c r="HR21" t="n">
+        <v/>
+      </c>
+      <c r="HS21" t="n">
+        <v/>
+      </c>
+      <c r="HT21" t="n">
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -12253,9 +15388,30 @@
       <c r="C22" t="n">
         <v>0.6912801166163477</v>
       </c>
+      <c r="D22" t="n">
+        <v/>
+      </c>
+      <c r="E22" t="n">
+        <v/>
+      </c>
+      <c r="F22" t="n">
+        <v/>
+      </c>
+      <c r="G22" t="n">
+        <v/>
+      </c>
       <c r="H22" t="n">
         <v>0.4559415877157832</v>
       </c>
+      <c r="I22" t="n">
+        <v/>
+      </c>
+      <c r="J22" t="n">
+        <v/>
+      </c>
+      <c r="K22" t="n">
+        <v/>
+      </c>
       <c r="L22" t="n">
         <v>0.07134139008162273</v>
       </c>
@@ -12283,9 +15439,30 @@
       <c r="T22" t="n">
         <v>0.0763982408500236</v>
       </c>
+      <c r="U22" t="n">
+        <v/>
+      </c>
+      <c r="V22" t="n">
+        <v/>
+      </c>
+      <c r="W22" t="n">
+        <v/>
+      </c>
+      <c r="X22" t="n">
+        <v/>
+      </c>
       <c r="Y22" t="n">
         <v>0.6697631357726209</v>
       </c>
+      <c r="Z22" t="n">
+        <v/>
+      </c>
+      <c r="AA22" t="n">
+        <v/>
+      </c>
+      <c r="AB22" t="n">
+        <v/>
+      </c>
       <c r="AC22" t="n">
         <v>0.0521725673015682</v>
       </c>
@@ -12325,6 +15502,15 @@
       <c r="AO22" t="n">
         <v>0.2155461661834987</v>
       </c>
+      <c r="AP22" t="n">
+        <v/>
+      </c>
+      <c r="AQ22" t="n">
+        <v/>
+      </c>
+      <c r="AR22" t="n">
+        <v/>
+      </c>
       <c r="AS22" t="n">
         <v>0.2500919860869169</v>
       </c>
@@ -12361,6 +15547,15 @@
       <c r="BD22" t="n">
         <v>0.5607403890215767</v>
       </c>
+      <c r="BE22" t="n">
+        <v/>
+      </c>
+      <c r="BF22" t="n">
+        <v/>
+      </c>
+      <c r="BG22" t="n">
+        <v/>
+      </c>
       <c r="BH22" t="n">
         <v>0.06210148834488308</v>
       </c>
@@ -12394,6 +15589,15 @@
       <c r="BR22" t="n">
         <v>0.07884632511709891</v>
       </c>
+      <c r="BS22" t="n">
+        <v/>
+      </c>
+      <c r="BT22" t="n">
+        <v/>
+      </c>
+      <c r="BU22" t="n">
+        <v/>
+      </c>
       <c r="BV22" t="n">
         <v>0.6408235185712765</v>
       </c>
@@ -12424,6 +15628,15 @@
       <c r="CE22" t="n">
         <v>0.4280479967440056</v>
       </c>
+      <c r="CF22" t="n">
+        <v/>
+      </c>
+      <c r="CG22" t="n">
+        <v/>
+      </c>
+      <c r="CH22" t="n">
+        <v/>
+      </c>
       <c r="CI22" t="n">
         <v>0.08774655552402913</v>
       </c>
@@ -12451,6 +15664,15 @@
       <c r="CQ22" t="n">
         <v>0.1147215113258301</v>
       </c>
+      <c r="CR22" t="n">
+        <v/>
+      </c>
+      <c r="CS22" t="n">
+        <v/>
+      </c>
+      <c r="CT22" t="n">
+        <v/>
+      </c>
       <c r="CU22" t="n">
         <v>0.06000849811272498</v>
       </c>
@@ -12577,23 +15799,101 @@
       <c r="EJ22" t="n">
         <v>0.1328601841334441</v>
       </c>
+      <c r="EK22" t="n">
+        <v/>
+      </c>
+      <c r="EL22" t="n">
+        <v/>
+      </c>
+      <c r="EM22" t="n">
+        <v/>
+      </c>
+      <c r="EN22" t="n">
+        <v/>
+      </c>
+      <c r="EO22" t="n">
+        <v/>
+      </c>
       <c r="EP22" t="n">
         <v>0.2308356897045039</v>
       </c>
       <c r="EQ22" t="n">
         <v>0.5809192283907729</v>
       </c>
+      <c r="ER22" t="n">
+        <v/>
+      </c>
+      <c r="ES22" t="n">
+        <v/>
+      </c>
+      <c r="ET22" t="n">
+        <v/>
+      </c>
+      <c r="EU22" t="n">
+        <v/>
+      </c>
+      <c r="EV22" t="n">
+        <v/>
+      </c>
       <c r="EW22" t="n">
         <v>0.4478985185719159</v>
       </c>
+      <c r="EX22" t="n">
+        <v/>
+      </c>
+      <c r="EY22" t="n">
+        <v/>
+      </c>
+      <c r="EZ22" t="n">
+        <v/>
+      </c>
+      <c r="FA22" t="n">
+        <v/>
+      </c>
+      <c r="FB22" t="n">
+        <v/>
+      </c>
+      <c r="FC22" t="n">
+        <v/>
+      </c>
+      <c r="FD22" t="n">
+        <v/>
+      </c>
+      <c r="FE22" t="n">
+        <v/>
+      </c>
+      <c r="FF22" t="n">
+        <v/>
+      </c>
+      <c r="FG22" t="n">
+        <v/>
+      </c>
       <c r="FH22" t="n">
         <v>0.2605480594700561</v>
       </c>
       <c r="FI22" t="n">
         <v>0.1854604729813533</v>
       </c>
+      <c r="FJ22" t="n">
+        <v/>
+      </c>
+      <c r="FK22" t="n">
+        <v/>
+      </c>
       <c r="FL22" t="n">
         <v>0.6719809431144379</v>
+      </c>
+      <c r="FM22" t="n">
+        <v/>
+      </c>
+      <c r="FN22" t="n">
+        <v/>
+      </c>
+      <c r="FO22" t="n">
+        <v/>
+      </c>
+      <c r="FP22" t="n">
+        <v/>
       </c>
       <c r="FQ22" t="n">
         <v>0.624139049713951</v>
@@ -12778,9 +16078,30 @@
       <c r="C23" t="n">
         <v>0.8272860226250103</v>
       </c>
+      <c r="D23" t="n">
+        <v/>
+      </c>
+      <c r="E23" t="n">
+        <v/>
+      </c>
+      <c r="F23" t="n">
+        <v/>
+      </c>
+      <c r="G23" t="n">
+        <v/>
+      </c>
       <c r="H23" t="n">
         <v>0.3638161215578422</v>
       </c>
+      <c r="I23" t="n">
+        <v/>
+      </c>
+      <c r="J23" t="n">
+        <v/>
+      </c>
+      <c r="K23" t="n">
+        <v/>
+      </c>
       <c r="L23" t="n">
         <v>0.1267682073908091</v>
       </c>
@@ -12808,9 +16129,30 @@
       <c r="T23" t="n">
         <v>0.04039804330393394</v>
       </c>
+      <c r="U23" t="n">
+        <v/>
+      </c>
+      <c r="V23" t="n">
+        <v/>
+      </c>
+      <c r="W23" t="n">
+        <v/>
+      </c>
+      <c r="X23" t="n">
+        <v/>
+      </c>
       <c r="Y23" t="n">
         <v>0.4425706518790135</v>
       </c>
+      <c r="Z23" t="n">
+        <v/>
+      </c>
+      <c r="AA23" t="n">
+        <v/>
+      </c>
+      <c r="AB23" t="n">
+        <v/>
+      </c>
       <c r="AC23" t="n">
         <v>0.1057078050712678</v>
       </c>
@@ -12850,6 +16192,15 @@
       <c r="AO23" t="n">
         <v>0.144651648170134</v>
       </c>
+      <c r="AP23" t="n">
+        <v/>
+      </c>
+      <c r="AQ23" t="n">
+        <v/>
+      </c>
+      <c r="AR23" t="n">
+        <v/>
+      </c>
       <c r="AS23" t="n">
         <v>0.218597745387017</v>
       </c>
@@ -12886,6 +16237,15 @@
       <c r="BD23" t="n">
         <v>0.5820289454740207</v>
       </c>
+      <c r="BE23" t="n">
+        <v/>
+      </c>
+      <c r="BF23" t="n">
+        <v/>
+      </c>
+      <c r="BG23" t="n">
+        <v/>
+      </c>
       <c r="BH23" t="n">
         <v>0.1132554852690722</v>
       </c>
@@ -12919,6 +16279,15 @@
       <c r="BR23" t="n">
         <v>0.1067243345675545</v>
       </c>
+      <c r="BS23" t="n">
+        <v/>
+      </c>
+      <c r="BT23" t="n">
+        <v/>
+      </c>
+      <c r="BU23" t="n">
+        <v/>
+      </c>
       <c r="BV23" t="n">
         <v>0.679179765383634</v>
       </c>
@@ -12949,6 +16318,15 @@
       <c r="CE23" t="n">
         <v>0.3099197560768402</v>
       </c>
+      <c r="CF23" t="n">
+        <v/>
+      </c>
+      <c r="CG23" t="n">
+        <v/>
+      </c>
+      <c r="CH23" t="n">
+        <v/>
+      </c>
       <c r="CI23" t="n">
         <v>0.2967659787325363</v>
       </c>
@@ -12976,6 +16354,15 @@
       <c r="CQ23" t="n">
         <v>0.1498972817002992</v>
       </c>
+      <c r="CR23" t="n">
+        <v/>
+      </c>
+      <c r="CS23" t="n">
+        <v/>
+      </c>
+      <c r="CT23" t="n">
+        <v/>
+      </c>
       <c r="CU23" t="n">
         <v>0.06084042043822215</v>
       </c>
@@ -13102,23 +16489,101 @@
       <c r="EJ23" t="n">
         <v>0.4108484454256229</v>
       </c>
+      <c r="EK23" t="n">
+        <v/>
+      </c>
+      <c r="EL23" t="n">
+        <v/>
+      </c>
+      <c r="EM23" t="n">
+        <v/>
+      </c>
+      <c r="EN23" t="n">
+        <v/>
+      </c>
+      <c r="EO23" t="n">
+        <v/>
+      </c>
       <c r="EP23" t="n">
         <v>0.3245148780127903</v>
       </c>
       <c r="EQ23" t="n">
         <v>0.5820542061470896</v>
       </c>
+      <c r="ER23" t="n">
+        <v/>
+      </c>
+      <c r="ES23" t="n">
+        <v/>
+      </c>
+      <c r="ET23" t="n">
+        <v/>
+      </c>
+      <c r="EU23" t="n">
+        <v/>
+      </c>
+      <c r="EV23" t="n">
+        <v/>
+      </c>
       <c r="EW23" t="n">
         <v>0.5874842139004092</v>
       </c>
+      <c r="EX23" t="n">
+        <v/>
+      </c>
+      <c r="EY23" t="n">
+        <v/>
+      </c>
+      <c r="EZ23" t="n">
+        <v/>
+      </c>
+      <c r="FA23" t="n">
+        <v/>
+      </c>
+      <c r="FB23" t="n">
+        <v/>
+      </c>
+      <c r="FC23" t="n">
+        <v/>
+      </c>
+      <c r="FD23" t="n">
+        <v/>
+      </c>
+      <c r="FE23" t="n">
+        <v/>
+      </c>
+      <c r="FF23" t="n">
+        <v/>
+      </c>
+      <c r="FG23" t="n">
+        <v/>
+      </c>
       <c r="FH23" t="n">
         <v>0.3869022856193193</v>
       </c>
       <c r="FI23" t="n">
         <v>0.4086358105558179</v>
       </c>
+      <c r="FJ23" t="n">
+        <v/>
+      </c>
+      <c r="FK23" t="n">
+        <v/>
+      </c>
       <c r="FL23" t="n">
         <v>0.4345928119659767</v>
+      </c>
+      <c r="FM23" t="n">
+        <v/>
+      </c>
+      <c r="FN23" t="n">
+        <v/>
+      </c>
+      <c r="FO23" t="n">
+        <v/>
+      </c>
+      <c r="FP23" t="n">
+        <v/>
       </c>
       <c r="FQ23" t="n">
         <v>0.629861722084566</v>
@@ -13303,9 +16768,30 @@
       <c r="C24" t="n">
         <v>0.2843793702708486</v>
       </c>
+      <c r="D24" t="n">
+        <v/>
+      </c>
+      <c r="E24" t="n">
+        <v/>
+      </c>
+      <c r="F24" t="n">
+        <v/>
+      </c>
+      <c r="G24" t="n">
+        <v/>
+      </c>
       <c r="H24" t="n">
         <v>0.3535400783026634</v>
       </c>
+      <c r="I24" t="n">
+        <v/>
+      </c>
+      <c r="J24" t="n">
+        <v/>
+      </c>
+      <c r="K24" t="n">
+        <v/>
+      </c>
       <c r="L24" t="n">
         <v>0.3317855744258513</v>
       </c>
@@ -13333,9 +16819,30 @@
       <c r="T24" t="n">
         <v>0.06898778239723061</v>
       </c>
+      <c r="U24" t="n">
+        <v/>
+      </c>
+      <c r="V24" t="n">
+        <v/>
+      </c>
+      <c r="W24" t="n">
+        <v/>
+      </c>
+      <c r="X24" t="n">
+        <v/>
+      </c>
       <c r="Y24" t="n">
         <v>0.8245338433261422</v>
       </c>
+      <c r="Z24" t="n">
+        <v/>
+      </c>
+      <c r="AA24" t="n">
+        <v/>
+      </c>
+      <c r="AB24" t="n">
+        <v/>
+      </c>
       <c r="AC24" t="n">
         <v>0.07627925012362199</v>
       </c>
@@ -13375,6 +16882,15 @@
       <c r="AO24" t="n">
         <v>0.3590940649293821</v>
       </c>
+      <c r="AP24" t="n">
+        <v/>
+      </c>
+      <c r="AQ24" t="n">
+        <v/>
+      </c>
+      <c r="AR24" t="n">
+        <v/>
+      </c>
       <c r="AS24" t="n">
         <v>0.3977734791490866</v>
       </c>
@@ -13411,6 +16927,15 @@
       <c r="BD24" t="n">
         <v>0.7320835053050213</v>
       </c>
+      <c r="BE24" t="n">
+        <v/>
+      </c>
+      <c r="BF24" t="n">
+        <v/>
+      </c>
+      <c r="BG24" t="n">
+        <v/>
+      </c>
       <c r="BH24" t="n">
         <v>0.03290195916900261</v>
       </c>
@@ -13444,6 +16969,15 @@
       <c r="BR24" t="n">
         <v>0.1859261048073086</v>
       </c>
+      <c r="BS24" t="n">
+        <v/>
+      </c>
+      <c r="BT24" t="n">
+        <v/>
+      </c>
+      <c r="BU24" t="n">
+        <v/>
+      </c>
       <c r="BV24" t="n">
         <v>0.6146967182916738</v>
       </c>
@@ -13474,6 +17008,15 @@
       <c r="CE24" t="n">
         <v>0.04984530807680369</v>
       </c>
+      <c r="CF24" t="n">
+        <v/>
+      </c>
+      <c r="CG24" t="n">
+        <v/>
+      </c>
+      <c r="CH24" t="n">
+        <v/>
+      </c>
       <c r="CI24" t="n">
         <v>0.1221173086290379</v>
       </c>
@@ -13501,6 +17044,15 @@
       <c r="CQ24" t="n">
         <v>0.7663992649865572</v>
       </c>
+      <c r="CR24" t="n">
+        <v/>
+      </c>
+      <c r="CS24" t="n">
+        <v/>
+      </c>
+      <c r="CT24" t="n">
+        <v/>
+      </c>
       <c r="CU24" t="n">
         <v>0.07107692255171054</v>
       </c>
@@ -13627,23 +17179,101 @@
       <c r="EJ24" t="n">
         <v>0.1541721312096158</v>
       </c>
+      <c r="EK24" t="n">
+        <v/>
+      </c>
+      <c r="EL24" t="n">
+        <v/>
+      </c>
+      <c r="EM24" t="n">
+        <v/>
+      </c>
+      <c r="EN24" t="n">
+        <v/>
+      </c>
+      <c r="EO24" t="n">
+        <v/>
+      </c>
       <c r="EP24" t="n">
         <v>0.1675166327367911</v>
       </c>
       <c r="EQ24" t="n">
         <v>0.7524808021554622</v>
       </c>
+      <c r="ER24" t="n">
+        <v/>
+      </c>
+      <c r="ES24" t="n">
+        <v/>
+      </c>
+      <c r="ET24" t="n">
+        <v/>
+      </c>
+      <c r="EU24" t="n">
+        <v/>
+      </c>
+      <c r="EV24" t="n">
+        <v/>
+      </c>
       <c r="EW24" t="n">
         <v>0.2876895458183508</v>
       </c>
+      <c r="EX24" t="n">
+        <v/>
+      </c>
+      <c r="EY24" t="n">
+        <v/>
+      </c>
+      <c r="EZ24" t="n">
+        <v/>
+      </c>
+      <c r="FA24" t="n">
+        <v/>
+      </c>
+      <c r="FB24" t="n">
+        <v/>
+      </c>
+      <c r="FC24" t="n">
+        <v/>
+      </c>
+      <c r="FD24" t="n">
+        <v/>
+      </c>
+      <c r="FE24" t="n">
+        <v/>
+      </c>
+      <c r="FF24" t="n">
+        <v/>
+      </c>
+      <c r="FG24" t="n">
+        <v/>
+      </c>
       <c r="FH24" t="n">
         <v>0.1975737666524887</v>
       </c>
       <c r="FI24" t="n">
         <v>0.3182359547339494</v>
       </c>
+      <c r="FJ24" t="n">
+        <v/>
+      </c>
+      <c r="FK24" t="n">
+        <v/>
+      </c>
       <c r="FL24" t="n">
         <v>0.1931510002217672</v>
+      </c>
+      <c r="FM24" t="n">
+        <v/>
+      </c>
+      <c r="FN24" t="n">
+        <v/>
+      </c>
+      <c r="FO24" t="n">
+        <v/>
+      </c>
+      <c r="FP24" t="n">
+        <v/>
       </c>
       <c r="FQ24" t="n">
         <v>0.8181603989220481</v>
@@ -13828,9 +17458,30 @@
       <c r="C25" t="n">
         <v>0.8375072251819681</v>
       </c>
+      <c r="D25" t="n">
+        <v/>
+      </c>
+      <c r="E25" t="n">
+        <v/>
+      </c>
+      <c r="F25" t="n">
+        <v/>
+      </c>
+      <c r="G25" t="n">
+        <v/>
+      </c>
       <c r="H25" t="n">
         <v>0.5702293066292832</v>
       </c>
+      <c r="I25" t="n">
+        <v/>
+      </c>
+      <c r="J25" t="n">
+        <v/>
+      </c>
+      <c r="K25" t="n">
+        <v/>
+      </c>
       <c r="L25" t="n">
         <v>0.2044114234744128</v>
       </c>
@@ -13858,9 +17509,30 @@
       <c r="T25" t="n">
         <v>0.1123449546757712</v>
       </c>
+      <c r="U25" t="n">
+        <v/>
+      </c>
+      <c r="V25" t="n">
+        <v/>
+      </c>
+      <c r="W25" t="n">
+        <v/>
+      </c>
+      <c r="X25" t="n">
+        <v/>
+      </c>
       <c r="Y25" t="n">
         <v>0.596525852254169</v>
       </c>
+      <c r="Z25" t="n">
+        <v/>
+      </c>
+      <c r="AA25" t="n">
+        <v/>
+      </c>
+      <c r="AB25" t="n">
+        <v/>
+      </c>
       <c r="AC25" t="n">
         <v>0.1516709118138863</v>
       </c>
@@ -13900,6 +17572,15 @@
       <c r="AO25" t="n">
         <v>0.7016077040912269</v>
       </c>
+      <c r="AP25" t="n">
+        <v/>
+      </c>
+      <c r="AQ25" t="n">
+        <v/>
+      </c>
+      <c r="AR25" t="n">
+        <v/>
+      </c>
       <c r="AS25" t="n">
         <v>0.2603295842441294</v>
       </c>
@@ -13936,6 +17617,15 @@
       <c r="BD25" t="n">
         <v>0.6968060794677042</v>
       </c>
+      <c r="BE25" t="n">
+        <v/>
+      </c>
+      <c r="BF25" t="n">
+        <v/>
+      </c>
+      <c r="BG25" t="n">
+        <v/>
+      </c>
       <c r="BH25" t="n">
         <v>0.1256514505242421</v>
       </c>
@@ -13969,6 +17659,15 @@
       <c r="BR25" t="n">
         <v>0.2536128946790528</v>
       </c>
+      <c r="BS25" t="n">
+        <v/>
+      </c>
+      <c r="BT25" t="n">
+        <v/>
+      </c>
+      <c r="BU25" t="n">
+        <v/>
+      </c>
       <c r="BV25" t="n">
         <v>0.5376824865744581</v>
       </c>
@@ -13999,6 +17698,15 @@
       <c r="CE25" t="n">
         <v>0.4329535010545055</v>
       </c>
+      <c r="CF25" t="n">
+        <v/>
+      </c>
+      <c r="CG25" t="n">
+        <v/>
+      </c>
+      <c r="CH25" t="n">
+        <v/>
+      </c>
       <c r="CI25" t="n">
         <v>0.1427790622064776</v>
       </c>
@@ -14026,6 +17734,15 @@
       <c r="CQ25" t="n">
         <v>0.1012867320434425</v>
       </c>
+      <c r="CR25" t="n">
+        <v/>
+      </c>
+      <c r="CS25" t="n">
+        <v/>
+      </c>
+      <c r="CT25" t="n">
+        <v/>
+      </c>
       <c r="CU25" t="n">
         <v>0.1627125729104094</v>
       </c>
@@ -14152,23 +17869,101 @@
       <c r="EJ25" t="n">
         <v>0.2820063821364714</v>
       </c>
+      <c r="EK25" t="n">
+        <v/>
+      </c>
+      <c r="EL25" t="n">
+        <v/>
+      </c>
+      <c r="EM25" t="n">
+        <v/>
+      </c>
+      <c r="EN25" t="n">
+        <v/>
+      </c>
+      <c r="EO25" t="n">
+        <v/>
+      </c>
       <c r="EP25" t="n">
         <v>0.1415715853603322</v>
       </c>
       <c r="EQ25" t="n">
         <v>0.550892099534797</v>
       </c>
+      <c r="ER25" t="n">
+        <v/>
+      </c>
+      <c r="ES25" t="n">
+        <v/>
+      </c>
+      <c r="ET25" t="n">
+        <v/>
+      </c>
+      <c r="EU25" t="n">
+        <v/>
+      </c>
+      <c r="EV25" t="n">
+        <v/>
+      </c>
       <c r="EW25" t="n">
         <v>0.4033123699781636</v>
       </c>
+      <c r="EX25" t="n">
+        <v/>
+      </c>
+      <c r="EY25" t="n">
+        <v/>
+      </c>
+      <c r="EZ25" t="n">
+        <v/>
+      </c>
+      <c r="FA25" t="n">
+        <v/>
+      </c>
+      <c r="FB25" t="n">
+        <v/>
+      </c>
+      <c r="FC25" t="n">
+        <v/>
+      </c>
+      <c r="FD25" t="n">
+        <v/>
+      </c>
+      <c r="FE25" t="n">
+        <v/>
+      </c>
+      <c r="FF25" t="n">
+        <v/>
+      </c>
+      <c r="FG25" t="n">
+        <v/>
+      </c>
       <c r="FH25" t="n">
         <v>0.1017968606858445</v>
       </c>
       <c r="FI25" t="n">
         <v>0.1619859693510681</v>
       </c>
+      <c r="FJ25" t="n">
+        <v/>
+      </c>
+      <c r="FK25" t="n">
+        <v/>
+      </c>
       <c r="FL25" t="n">
         <v>0.4502389693669059</v>
+      </c>
+      <c r="FM25" t="n">
+        <v/>
+      </c>
+      <c r="FN25" t="n">
+        <v/>
+      </c>
+      <c r="FO25" t="n">
+        <v/>
+      </c>
+      <c r="FP25" t="n">
+        <v/>
       </c>
       <c r="FQ25" t="n">
         <v>0.6501761386721212</v>
@@ -14353,9 +18148,30 @@
       <c r="C26" t="n">
         <v>0.4530162013379807</v>
       </c>
+      <c r="D26" t="n">
+        <v/>
+      </c>
+      <c r="E26" t="n">
+        <v/>
+      </c>
+      <c r="F26" t="n">
+        <v/>
+      </c>
+      <c r="G26" t="n">
+        <v/>
+      </c>
       <c r="H26" t="n">
         <v>0.5260941455863892</v>
       </c>
+      <c r="I26" t="n">
+        <v/>
+      </c>
+      <c r="J26" t="n">
+        <v/>
+      </c>
+      <c r="K26" t="n">
+        <v/>
+      </c>
       <c r="L26" t="n">
         <v>0.1602224307321968</v>
       </c>
@@ -14383,9 +18199,30 @@
       <c r="T26" t="n">
         <v>0.1897886587139866</v>
       </c>
+      <c r="U26" t="n">
+        <v/>
+      </c>
+      <c r="V26" t="n">
+        <v/>
+      </c>
+      <c r="W26" t="n">
+        <v/>
+      </c>
+      <c r="X26" t="n">
+        <v/>
+      </c>
       <c r="Y26" t="n">
         <v>0.4455251094441641</v>
       </c>
+      <c r="Z26" t="n">
+        <v/>
+      </c>
+      <c r="AA26" t="n">
+        <v/>
+      </c>
+      <c r="AB26" t="n">
+        <v/>
+      </c>
       <c r="AC26" t="n">
         <v>0.2672124148633443</v>
       </c>
@@ -14425,6 +18262,15 @@
       <c r="AO26" t="n">
         <v>0.4531275817078907</v>
       </c>
+      <c r="AP26" t="n">
+        <v/>
+      </c>
+      <c r="AQ26" t="n">
+        <v/>
+      </c>
+      <c r="AR26" t="n">
+        <v/>
+      </c>
       <c r="AS26" t="n">
         <v>0.662336947411108</v>
       </c>
@@ -14461,6 +18307,15 @@
       <c r="BD26" t="n">
         <v>0.498544723928489</v>
       </c>
+      <c r="BE26" t="n">
+        <v/>
+      </c>
+      <c r="BF26" t="n">
+        <v/>
+      </c>
+      <c r="BG26" t="n">
+        <v/>
+      </c>
       <c r="BH26" t="n">
         <v>0.3671054239580554</v>
       </c>
@@ -14494,6 +18349,15 @@
       <c r="BR26" t="n">
         <v>0.1537541633156894</v>
       </c>
+      <c r="BS26" t="n">
+        <v/>
+      </c>
+      <c r="BT26" t="n">
+        <v/>
+      </c>
+      <c r="BU26" t="n">
+        <v/>
+      </c>
       <c r="BV26" t="n">
         <v>0.7178696659745368</v>
       </c>
@@ -14524,6 +18388,15 @@
       <c r="CE26" t="n">
         <v>0.221045244590713</v>
       </c>
+      <c r="CF26" t="n">
+        <v/>
+      </c>
+      <c r="CG26" t="n">
+        <v/>
+      </c>
+      <c r="CH26" t="n">
+        <v/>
+      </c>
       <c r="CI26" t="n">
         <v>0.408021678666526</v>
       </c>
@@ -14551,6 +18424,15 @@
       <c r="CQ26" t="n">
         <v>0.4271190707662999</v>
       </c>
+      <c r="CR26" t="n">
+        <v/>
+      </c>
+      <c r="CS26" t="n">
+        <v/>
+      </c>
+      <c r="CT26" t="n">
+        <v/>
+      </c>
       <c r="CU26" t="n">
         <v>0.320129515135102</v>
       </c>
@@ -14677,23 +18559,101 @@
       <c r="EJ26" t="n">
         <v>0.6888615575134447</v>
       </c>
+      <c r="EK26" t="n">
+        <v/>
+      </c>
+      <c r="EL26" t="n">
+        <v/>
+      </c>
+      <c r="EM26" t="n">
+        <v/>
+      </c>
+      <c r="EN26" t="n">
+        <v/>
+      </c>
+      <c r="EO26" t="n">
+        <v/>
+      </c>
       <c r="EP26" t="n">
         <v>0.5676530537800071</v>
       </c>
       <c r="EQ26" t="n">
         <v>0.8824029322428999</v>
       </c>
+      <c r="ER26" t="n">
+        <v/>
+      </c>
+      <c r="ES26" t="n">
+        <v/>
+      </c>
+      <c r="ET26" t="n">
+        <v/>
+      </c>
+      <c r="EU26" t="n">
+        <v/>
+      </c>
+      <c r="EV26" t="n">
+        <v/>
+      </c>
       <c r="EW26" t="n">
         <v>0.6324557021764747</v>
       </c>
+      <c r="EX26" t="n">
+        <v/>
+      </c>
+      <c r="EY26" t="n">
+        <v/>
+      </c>
+      <c r="EZ26" t="n">
+        <v/>
+      </c>
+      <c r="FA26" t="n">
+        <v/>
+      </c>
+      <c r="FB26" t="n">
+        <v/>
+      </c>
+      <c r="FC26" t="n">
+        <v/>
+      </c>
+      <c r="FD26" t="n">
+        <v/>
+      </c>
+      <c r="FE26" t="n">
+        <v/>
+      </c>
+      <c r="FF26" t="n">
+        <v/>
+      </c>
+      <c r="FG26" t="n">
+        <v/>
+      </c>
       <c r="FH26" t="n">
         <v>0.8236508758181407</v>
       </c>
       <c r="FI26" t="n">
         <v>0.8108728951275301</v>
       </c>
+      <c r="FJ26" t="n">
+        <v/>
+      </c>
+      <c r="FK26" t="n">
+        <v/>
+      </c>
       <c r="FL26" t="n">
         <v>0.8865739873168421</v>
+      </c>
+      <c r="FM26" t="n">
+        <v/>
+      </c>
+      <c r="FN26" t="n">
+        <v/>
+      </c>
+      <c r="FO26" t="n">
+        <v/>
+      </c>
+      <c r="FP26" t="n">
+        <v/>
       </c>
       <c r="FQ26" t="n">
         <v>0.9082460606999163</v>
@@ -14878,9 +18838,30 @@
       <c r="C27" t="n">
         <v>0.7955062993788145</v>
       </c>
+      <c r="D27" t="n">
+        <v/>
+      </c>
+      <c r="E27" t="n">
+        <v/>
+      </c>
+      <c r="F27" t="n">
+        <v/>
+      </c>
+      <c r="G27" t="n">
+        <v/>
+      </c>
       <c r="H27" t="n">
         <v>0.6197666102372505</v>
       </c>
+      <c r="I27" t="n">
+        <v/>
+      </c>
+      <c r="J27" t="n">
+        <v/>
+      </c>
+      <c r="K27" t="n">
+        <v/>
+      </c>
       <c r="L27" t="n">
         <v>0.3290233482595739</v>
       </c>
@@ -14908,9 +18889,30 @@
       <c r="T27" t="n">
         <v>0.1334920399293263</v>
       </c>
+      <c r="U27" t="n">
+        <v/>
+      </c>
+      <c r="V27" t="n">
+        <v/>
+      </c>
+      <c r="W27" t="n">
+        <v/>
+      </c>
+      <c r="X27" t="n">
+        <v/>
+      </c>
       <c r="Y27" t="n">
         <v>0.7469302883271974</v>
       </c>
+      <c r="Z27" t="n">
+        <v/>
+      </c>
+      <c r="AA27" t="n">
+        <v/>
+      </c>
+      <c r="AB27" t="n">
+        <v/>
+      </c>
       <c r="AC27" t="n">
         <v>0.2955719360930679</v>
       </c>
@@ -14950,6 +18952,15 @@
       <c r="AO27" t="n">
         <v>0.5605449375210168</v>
       </c>
+      <c r="AP27" t="n">
+        <v/>
+      </c>
+      <c r="AQ27" t="n">
+        <v/>
+      </c>
+      <c r="AR27" t="n">
+        <v/>
+      </c>
       <c r="AS27" t="n">
         <v>0.2243680978565317</v>
       </c>
@@ -14986,6 +18997,15 @@
       <c r="BD27" t="n">
         <v>0.7538710100775308</v>
       </c>
+      <c r="BE27" t="n">
+        <v/>
+      </c>
+      <c r="BF27" t="n">
+        <v/>
+      </c>
+      <c r="BG27" t="n">
+        <v/>
+      </c>
       <c r="BH27" t="n">
         <v>0.1768615747651788</v>
       </c>
@@ -15019,6 +19039,15 @@
       <c r="BR27" t="n">
         <v>0.3651089471242815</v>
       </c>
+      <c r="BS27" t="n">
+        <v/>
+      </c>
+      <c r="BT27" t="n">
+        <v/>
+      </c>
+      <c r="BU27" t="n">
+        <v/>
+      </c>
       <c r="BV27" t="n">
         <v>0.6939709953351149</v>
       </c>
@@ -15049,6 +19078,15 @@
       <c r="CE27" t="n">
         <v>0.5324479387747928</v>
       </c>
+      <c r="CF27" t="n">
+        <v/>
+      </c>
+      <c r="CG27" t="n">
+        <v/>
+      </c>
+      <c r="CH27" t="n">
+        <v/>
+      </c>
       <c r="CI27" t="n">
         <v>0.2812265715179306</v>
       </c>
@@ -15076,6 +19114,15 @@
       <c r="CQ27" t="n">
         <v>0.155273214032309</v>
       </c>
+      <c r="CR27" t="n">
+        <v/>
+      </c>
+      <c r="CS27" t="n">
+        <v/>
+      </c>
+      <c r="CT27" t="n">
+        <v/>
+      </c>
       <c r="CU27" t="n">
         <v>0.2292178860305737</v>
       </c>
@@ -15202,23 +19249,101 @@
       <c r="EJ27" t="n">
         <v>0.2988733571403993</v>
       </c>
+      <c r="EK27" t="n">
+        <v/>
+      </c>
+      <c r="EL27" t="n">
+        <v/>
+      </c>
+      <c r="EM27" t="n">
+        <v/>
+      </c>
+      <c r="EN27" t="n">
+        <v/>
+      </c>
+      <c r="EO27" t="n">
+        <v/>
+      </c>
       <c r="EP27" t="n">
         <v>0.237152781771068</v>
       </c>
       <c r="EQ27" t="n">
         <v>0.7175762551134601</v>
       </c>
+      <c r="ER27" t="n">
+        <v/>
+      </c>
+      <c r="ES27" t="n">
+        <v/>
+      </c>
+      <c r="ET27" t="n">
+        <v/>
+      </c>
+      <c r="EU27" t="n">
+        <v/>
+      </c>
+      <c r="EV27" t="n">
+        <v/>
+      </c>
       <c r="EW27" t="n">
         <v>0.3356163265910937</v>
       </c>
+      <c r="EX27" t="n">
+        <v/>
+      </c>
+      <c r="EY27" t="n">
+        <v/>
+      </c>
+      <c r="EZ27" t="n">
+        <v/>
+      </c>
+      <c r="FA27" t="n">
+        <v/>
+      </c>
+      <c r="FB27" t="n">
+        <v/>
+      </c>
+      <c r="FC27" t="n">
+        <v/>
+      </c>
+      <c r="FD27" t="n">
+        <v/>
+      </c>
+      <c r="FE27" t="n">
+        <v/>
+      </c>
+      <c r="FF27" t="n">
+        <v/>
+      </c>
+      <c r="FG27" t="n">
+        <v/>
+      </c>
       <c r="FH27" t="n">
         <v>0.3622031972395828</v>
       </c>
       <c r="FI27" t="n">
         <v>0.5772920002477766</v>
       </c>
+      <c r="FJ27" t="n">
+        <v/>
+      </c>
+      <c r="FK27" t="n">
+        <v/>
+      </c>
       <c r="FL27" t="n">
         <v>0.6010381626126067</v>
+      </c>
+      <c r="FM27" t="n">
+        <v/>
+      </c>
+      <c r="FN27" t="n">
+        <v/>
+      </c>
+      <c r="FO27" t="n">
+        <v/>
+      </c>
+      <c r="FP27" t="n">
+        <v/>
       </c>
       <c r="FQ27" t="n">
         <v>0.7120523237770042</v>
@@ -15403,9 +19528,30 @@
       <c r="C28" t="n">
         <v>0.6295999497976242</v>
       </c>
+      <c r="D28" t="n">
+        <v/>
+      </c>
+      <c r="E28" t="n">
+        <v/>
+      </c>
+      <c r="F28" t="n">
+        <v/>
+      </c>
+      <c r="G28" t="n">
+        <v/>
+      </c>
       <c r="H28" t="n">
         <v>0.5746415219664514</v>
       </c>
+      <c r="I28" t="n">
+        <v/>
+      </c>
+      <c r="J28" t="n">
+        <v/>
+      </c>
+      <c r="K28" t="n">
+        <v/>
+      </c>
       <c r="L28" t="n">
         <v>0.2531462443833356</v>
       </c>
@@ -15433,9 +19579,30 @@
       <c r="T28" t="n">
         <v>0.08245026806877175</v>
       </c>
+      <c r="U28" t="n">
+        <v/>
+      </c>
+      <c r="V28" t="n">
+        <v/>
+      </c>
+      <c r="W28" t="n">
+        <v/>
+      </c>
+      <c r="X28" t="n">
+        <v/>
+      </c>
       <c r="Y28" t="n">
         <v>0.6508278931163489</v>
       </c>
+      <c r="Z28" t="n">
+        <v/>
+      </c>
+      <c r="AA28" t="n">
+        <v/>
+      </c>
+      <c r="AB28" t="n">
+        <v/>
+      </c>
       <c r="AC28" t="n">
         <v>0.1492279688894387</v>
       </c>
@@ -15475,6 +19642,15 @@
       <c r="AO28" t="n">
         <v>0.5336816258986589</v>
       </c>
+      <c r="AP28" t="n">
+        <v/>
+      </c>
+      <c r="AQ28" t="n">
+        <v/>
+      </c>
+      <c r="AR28" t="n">
+        <v/>
+      </c>
       <c r="AS28" t="n">
         <v>0.2806937042199611</v>
       </c>
@@ -15511,6 +19687,15 @@
       <c r="BD28" t="n">
         <v>0.7496458614447349</v>
       </c>
+      <c r="BE28" t="n">
+        <v/>
+      </c>
+      <c r="BF28" t="n">
+        <v/>
+      </c>
+      <c r="BG28" t="n">
+        <v/>
+      </c>
       <c r="BH28" t="n">
         <v>0.1116137598520498</v>
       </c>
@@ -15544,6 +19729,15 @@
       <c r="BR28" t="n">
         <v>0.3463031723198523</v>
       </c>
+      <c r="BS28" t="n">
+        <v/>
+      </c>
+      <c r="BT28" t="n">
+        <v/>
+      </c>
+      <c r="BU28" t="n">
+        <v/>
+      </c>
       <c r="BV28" t="n">
         <v>0.6621784478401985</v>
       </c>
@@ -15574,6 +19768,15 @@
       <c r="CE28" t="n">
         <v>0.3400607660023082</v>
       </c>
+      <c r="CF28" t="n">
+        <v/>
+      </c>
+      <c r="CG28" t="n">
+        <v/>
+      </c>
+      <c r="CH28" t="n">
+        <v/>
+      </c>
       <c r="CI28" t="n">
         <v>0.2203164657670189</v>
       </c>
@@ -15601,6 +19804,15 @@
       <c r="CQ28" t="n">
         <v>0.1979431616201525</v>
       </c>
+      <c r="CR28" t="n">
+        <v/>
+      </c>
+      <c r="CS28" t="n">
+        <v/>
+      </c>
+      <c r="CT28" t="n">
+        <v/>
+      </c>
       <c r="CU28" t="n">
         <v>0.1598655580043482</v>
       </c>
@@ -15727,23 +19939,101 @@
       <c r="EJ28" t="n">
         <v>0.1901104438691165</v>
       </c>
+      <c r="EK28" t="n">
+        <v/>
+      </c>
+      <c r="EL28" t="n">
+        <v/>
+      </c>
+      <c r="EM28" t="n">
+        <v/>
+      </c>
+      <c r="EN28" t="n">
+        <v/>
+      </c>
+      <c r="EO28" t="n">
+        <v/>
+      </c>
       <c r="EP28" t="n">
         <v>0.1976937059670505</v>
       </c>
       <c r="EQ28" t="n">
         <v>0.5034240941196685</v>
       </c>
+      <c r="ER28" t="n">
+        <v/>
+      </c>
+      <c r="ES28" t="n">
+        <v/>
+      </c>
+      <c r="ET28" t="n">
+        <v/>
+      </c>
+      <c r="EU28" t="n">
+        <v/>
+      </c>
+      <c r="EV28" t="n">
+        <v/>
+      </c>
       <c r="EW28" t="n">
         <v>0.3227054384671634</v>
       </c>
+      <c r="EX28" t="n">
+        <v/>
+      </c>
+      <c r="EY28" t="n">
+        <v/>
+      </c>
+      <c r="EZ28" t="n">
+        <v/>
+      </c>
+      <c r="FA28" t="n">
+        <v/>
+      </c>
+      <c r="FB28" t="n">
+        <v/>
+      </c>
+      <c r="FC28" t="n">
+        <v/>
+      </c>
+      <c r="FD28" t="n">
+        <v/>
+      </c>
+      <c r="FE28" t="n">
+        <v/>
+      </c>
+      <c r="FF28" t="n">
+        <v/>
+      </c>
+      <c r="FG28" t="n">
+        <v/>
+      </c>
       <c r="FH28" t="n">
         <v>0.1832326459824432</v>
       </c>
       <c r="FI28" t="n">
         <v>0.3066401673874991</v>
       </c>
+      <c r="FJ28" t="n">
+        <v/>
+      </c>
+      <c r="FK28" t="n">
+        <v/>
+      </c>
       <c r="FL28" t="n">
         <v>0.4129198259529009</v>
+      </c>
+      <c r="FM28" t="n">
+        <v/>
+      </c>
+      <c r="FN28" t="n">
+        <v/>
+      </c>
+      <c r="FO28" t="n">
+        <v/>
+      </c>
+      <c r="FP28" t="n">
+        <v/>
       </c>
       <c r="FQ28" t="n">
         <v>0.7267652332309787</v>
@@ -15928,9 +20218,30 @@
       <c r="C29" t="n">
         <v>0.8685368232519117</v>
       </c>
+      <c r="D29" t="n">
+        <v/>
+      </c>
+      <c r="E29" t="n">
+        <v/>
+      </c>
+      <c r="F29" t="n">
+        <v/>
+      </c>
+      <c r="G29" t="n">
+        <v/>
+      </c>
       <c r="H29" t="n">
         <v>0.5036168543905181</v>
       </c>
+      <c r="I29" t="n">
+        <v/>
+      </c>
+      <c r="J29" t="n">
+        <v/>
+      </c>
+      <c r="K29" t="n">
+        <v/>
+      </c>
       <c r="L29" t="n">
         <v>0.05909560983694745</v>
       </c>
@@ -15958,9 +20269,30 @@
       <c r="T29" t="n">
         <v>0.04609449082331198</v>
       </c>
+      <c r="U29" t="n">
+        <v/>
+      </c>
+      <c r="V29" t="n">
+        <v/>
+      </c>
+      <c r="W29" t="n">
+        <v/>
+      </c>
+      <c r="X29" t="n">
+        <v/>
+      </c>
       <c r="Y29" t="n">
         <v>0.4861625471192849</v>
       </c>
+      <c r="Z29" t="n">
+        <v/>
+      </c>
+      <c r="AA29" t="n">
+        <v/>
+      </c>
+      <c r="AB29" t="n">
+        <v/>
+      </c>
       <c r="AC29" t="n">
         <v>0.06221121395288194</v>
       </c>
@@ -16000,6 +20332,15 @@
       <c r="AO29" t="n">
         <v>0.5466723492160688</v>
       </c>
+      <c r="AP29" t="n">
+        <v/>
+      </c>
+      <c r="AQ29" t="n">
+        <v/>
+      </c>
+      <c r="AR29" t="n">
+        <v/>
+      </c>
       <c r="AS29" t="n">
         <v>0.290529381813815</v>
       </c>
@@ -16036,6 +20377,15 @@
       <c r="BD29" t="n">
         <v>0.7220609492755495</v>
       </c>
+      <c r="BE29" t="n">
+        <v/>
+      </c>
+      <c r="BF29" t="n">
+        <v/>
+      </c>
+      <c r="BG29" t="n">
+        <v/>
+      </c>
       <c r="BH29" t="n">
         <v>0.09813754222342064</v>
       </c>
@@ -16069,6 +20419,15 @@
       <c r="BR29" t="n">
         <v>0.2220579797908758</v>
       </c>
+      <c r="BS29" t="n">
+        <v/>
+      </c>
+      <c r="BT29" t="n">
+        <v/>
+      </c>
+      <c r="BU29" t="n">
+        <v/>
+      </c>
       <c r="BV29" t="n">
         <v>0.4880738334190607</v>
       </c>
@@ -16099,6 +20458,15 @@
       <c r="CE29" t="n">
         <v>0.2461644979336421</v>
       </c>
+      <c r="CF29" t="n">
+        <v/>
+      </c>
+      <c r="CG29" t="n">
+        <v/>
+      </c>
+      <c r="CH29" t="n">
+        <v/>
+      </c>
       <c r="CI29" t="n">
         <v>0.1032195530161205</v>
       </c>
@@ -16126,6 +20494,15 @@
       <c r="CQ29" t="n">
         <v>0.0745132879866354</v>
       </c>
+      <c r="CR29" t="n">
+        <v/>
+      </c>
+      <c r="CS29" t="n">
+        <v/>
+      </c>
+      <c r="CT29" t="n">
+        <v/>
+      </c>
       <c r="CU29" t="n">
         <v>0.1042768021305148</v>
       </c>
@@ -16252,24 +20629,102 @@
       <c r="EJ29" t="n">
         <v>0.3845476322651088</v>
       </c>
+      <c r="EK29" t="n">
+        <v/>
+      </c>
+      <c r="EL29" t="n">
+        <v/>
+      </c>
+      <c r="EM29" t="n">
+        <v/>
+      </c>
+      <c r="EN29" t="n">
+        <v/>
+      </c>
+      <c r="EO29" t="n">
+        <v/>
+      </c>
       <c r="EP29" t="n">
         <v>0.3681158333905717</v>
       </c>
       <c r="EQ29" t="n">
         <v>0.5855304387162537</v>
       </c>
+      <c r="ER29" t="n">
+        <v/>
+      </c>
+      <c r="ES29" t="n">
+        <v/>
+      </c>
+      <c r="ET29" t="n">
+        <v/>
+      </c>
+      <c r="EU29" t="n">
+        <v/>
+      </c>
+      <c r="EV29" t="n">
+        <v/>
+      </c>
       <c r="EW29" t="n">
         <v>0.5897539206533884</v>
       </c>
+      <c r="EX29" t="n">
+        <v/>
+      </c>
+      <c r="EY29" t="n">
+        <v/>
+      </c>
+      <c r="EZ29" t="n">
+        <v/>
+      </c>
+      <c r="FA29" t="n">
+        <v/>
+      </c>
+      <c r="FB29" t="n">
+        <v/>
+      </c>
+      <c r="FC29" t="n">
+        <v/>
+      </c>
+      <c r="FD29" t="n">
+        <v/>
+      </c>
+      <c r="FE29" t="n">
+        <v/>
+      </c>
+      <c r="FF29" t="n">
+        <v/>
+      </c>
+      <c r="FG29" t="n">
+        <v/>
+      </c>
       <c r="FH29" t="n">
         <v>0.3660496889692003</v>
       </c>
       <c r="FI29" t="n">
         <v>0.4292437829802861</v>
       </c>
+      <c r="FJ29" t="n">
+        <v/>
+      </c>
+      <c r="FK29" t="n">
+        <v/>
+      </c>
       <c r="FL29" t="n">
         <v>0.5926912680524923</v>
       </c>
+      <c r="FM29" t="n">
+        <v/>
+      </c>
+      <c r="FN29" t="n">
+        <v/>
+      </c>
+      <c r="FO29" t="n">
+        <v/>
+      </c>
+      <c r="FP29" t="n">
+        <v/>
+      </c>
       <c r="FQ29" t="n">
         <v>0.6521947877464398</v>
       </c>
@@ -16437,6 +20892,2766 @@
       </c>
       <c r="HT29" t="n">
         <v>0.2362926685604101</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>NON_SEIZURE_AVG</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Subset</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.4943250183168776</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.4146700529763684</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.2454927259441102</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.4071881900639731</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.2530701871506612</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.3879649237251844</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.1351891006244853</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.09665229657930871</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.1118904006757993</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.1850456134893413</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.1358624052022541</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.1129964147650324</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.09869277777689471</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.07146020501105446</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.0704194872702659</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0.06990738877699083</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0.08969122932261149</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0.08564934966889629</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0.2427788061441095</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0.427750521670813</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0.2136952753508085</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0.4806737820018151</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0.42744288531742</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0.08420338147692008</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0.1526914428721203</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0.1185557696411288</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0.1314906682486718</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.2012810657067686</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0.09604628580200303</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0.1230364191169576</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0.06057325907079465</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0.09459810503040215</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0.06371168703974674</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0.08632357239128843</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0.09416767139137122</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>0.2060764325589819</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0.4167004758975035</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>0.1637492589459678</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0.3685073168113947</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0.2663518629698852</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0.08923744041500621</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>0.1478758234098754</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0.2354325235999895</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>0.112257965013369</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>0.1342764951475212</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>0.08539954809395973</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>0.1198854837167455</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>0.06995244485540228</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>0.110828809376658</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>0.08900035824072471</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>0.07874986498168449</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>0.1496359319459592</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>0.4381534740449949</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>0.4917066524554959</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>0.08945067333029472</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>0.3253057997928064</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>0.2243157189058858</v>
+      </c>
+      <c r="BH30" t="n">
+        <v>0.1100501512032979</v>
+      </c>
+      <c r="BI30" t="n">
+        <v>0.2720921580502312</v>
+      </c>
+      <c r="BJ30" t="n">
+        <v>0.08530704504338822</v>
+      </c>
+      <c r="BK30" t="n">
+        <v>0.1550170811895268</v>
+      </c>
+      <c r="BL30" t="n">
+        <v>0.06980135514485472</v>
+      </c>
+      <c r="BM30" t="n">
+        <v>0.1724125160005332</v>
+      </c>
+      <c r="BN30" t="n">
+        <v>0.09364136240047471</v>
+      </c>
+      <c r="BO30" t="n">
+        <v>0.08320222456492035</v>
+      </c>
+      <c r="BP30" t="n">
+        <v>0.09809811974799552</v>
+      </c>
+      <c r="BQ30" t="n">
+        <v>0.2206326668983812</v>
+      </c>
+      <c r="BR30" t="n">
+        <v>0.2102319495551424</v>
+      </c>
+      <c r="BS30" t="n">
+        <v>0.2471380511188413</v>
+      </c>
+      <c r="BT30" t="n">
+        <v>0.09207031269146419</v>
+      </c>
+      <c r="BU30" t="n">
+        <v>0.1135230266403208</v>
+      </c>
+      <c r="BV30" t="n">
+        <v>0.5026666670924563</v>
+      </c>
+      <c r="BW30" t="n">
+        <v>0.1942071464321483</v>
+      </c>
+      <c r="BX30" t="n">
+        <v>0.2490365144116553</v>
+      </c>
+      <c r="BY30" t="n">
+        <v>0.162274736488103</v>
+      </c>
+      <c r="BZ30" t="n">
+        <v>0.1518955093039452</v>
+      </c>
+      <c r="CA30" t="n">
+        <v>0.1017313524701459</v>
+      </c>
+      <c r="CB30" t="n">
+        <v>0.09423806480553937</v>
+      </c>
+      <c r="CC30" t="n">
+        <v>0.1675969500823442</v>
+      </c>
+      <c r="CD30" t="n">
+        <v>0.1486303506839184</v>
+      </c>
+      <c r="CE30" t="n">
+        <v>0.2649041354189839</v>
+      </c>
+      <c r="CF30" t="n">
+        <v>0.08998232932402681</v>
+      </c>
+      <c r="CG30" t="n">
+        <v>0.2698038832010928</v>
+      </c>
+      <c r="CH30" t="n">
+        <v>0.1296618961313255</v>
+      </c>
+      <c r="CI30" t="n">
+        <v>0.1782260108327959</v>
+      </c>
+      <c r="CJ30" t="n">
+        <v>0.4747589903572733</v>
+      </c>
+      <c r="CK30" t="n">
+        <v>0.1488505341557475</v>
+      </c>
+      <c r="CL30" t="n">
+        <v>0.2667322630898229</v>
+      </c>
+      <c r="CM30" t="n">
+        <v>0.09892393347760113</v>
+      </c>
+      <c r="CN30" t="n">
+        <v>0.196947649828779</v>
+      </c>
+      <c r="CO30" t="n">
+        <v>0.09638658728438212</v>
+      </c>
+      <c r="CP30" t="n">
+        <v>0.1558080435058591</v>
+      </c>
+      <c r="CQ30" t="n">
+        <v>0.1936818043449673</v>
+      </c>
+      <c r="CR30" t="n">
+        <v>0.1283973943645401</v>
+      </c>
+      <c r="CS30" t="n">
+        <v>0.1895837048723101</v>
+      </c>
+      <c r="CT30" t="n">
+        <v>0.2353641231082469</v>
+      </c>
+      <c r="CU30" t="n">
+        <v>0.1228578681267496</v>
+      </c>
+      <c r="CV30" t="n">
+        <v>0.1541749020326879</v>
+      </c>
+      <c r="CW30" t="n">
+        <v>0.08193288734479467</v>
+      </c>
+      <c r="CX30" t="n">
+        <v>0.09428219602326249</v>
+      </c>
+      <c r="CY30" t="n">
+        <v>0.08370625398406453</v>
+      </c>
+      <c r="CZ30" t="n">
+        <v>0.08698868252224339</v>
+      </c>
+      <c r="DA30" t="n">
+        <v>0.09964999038618987</v>
+      </c>
+      <c r="DB30" t="n">
+        <v>0.07130831344938741</v>
+      </c>
+      <c r="DC30" t="n">
+        <v>0.0821827572096971</v>
+      </c>
+      <c r="DD30" t="n">
+        <v>0.1053957154738645</v>
+      </c>
+      <c r="DE30" t="n">
+        <v>0.2141277065033851</v>
+      </c>
+      <c r="DF30" t="n">
+        <v>0.3181850868657941</v>
+      </c>
+      <c r="DG30" t="n">
+        <v>0.106223828973255</v>
+      </c>
+      <c r="DH30" t="n">
+        <v>0.2680681139087027</v>
+      </c>
+      <c r="DI30" t="n">
+        <v>0.1116731347510533</v>
+      </c>
+      <c r="DJ30" t="n">
+        <v>0.432932699619898</v>
+      </c>
+      <c r="DK30" t="n">
+        <v>0.1179875807313833</v>
+      </c>
+      <c r="DL30" t="n">
+        <v>0.1867381717822895</v>
+      </c>
+      <c r="DM30" t="n">
+        <v>0.1768420364970624</v>
+      </c>
+      <c r="DN30" t="n">
+        <v>0.1341543115493523</v>
+      </c>
+      <c r="DO30" t="n">
+        <v>0.3031211771032767</v>
+      </c>
+      <c r="DP30" t="n">
+        <v>0.1112224643929139</v>
+      </c>
+      <c r="DQ30" t="n">
+        <v>0.3696240148489475</v>
+      </c>
+      <c r="DR30" t="n">
+        <v>0.1156339454858886</v>
+      </c>
+      <c r="DS30" t="n">
+        <v>0.3038199161115939</v>
+      </c>
+      <c r="DT30" t="n">
+        <v>0.1243684998403564</v>
+      </c>
+      <c r="DU30" t="n">
+        <v>0.5781619077985265</v>
+      </c>
+      <c r="DV30" t="n">
+        <v>0.2544357351612093</v>
+      </c>
+      <c r="DW30" t="n">
+        <v>0.1371179953416874</v>
+      </c>
+      <c r="DX30" t="n">
+        <v>0.185518772587524</v>
+      </c>
+      <c r="DY30" t="n">
+        <v>0.09377251862601632</v>
+      </c>
+      <c r="DZ30" t="n">
+        <v>0.1005151975547993</v>
+      </c>
+      <c r="EA30" t="n">
+        <v>0.08826179129088668</v>
+      </c>
+      <c r="EB30" t="n">
+        <v>0.09284681435746914</v>
+      </c>
+      <c r="EC30" t="n">
+        <v>0.1710498261415226</v>
+      </c>
+      <c r="ED30" t="n">
+        <v>0.1724287710619703</v>
+      </c>
+      <c r="EE30" t="n">
+        <v>0.2750420577315783</v>
+      </c>
+      <c r="EF30" t="n">
+        <v>0.09375233275011274</v>
+      </c>
+      <c r="EG30" t="n">
+        <v>0.09289238174373279</v>
+      </c>
+      <c r="EH30" t="n">
+        <v>0.2219528659337974</v>
+      </c>
+      <c r="EI30" t="n">
+        <v>0.4719902875556014</v>
+      </c>
+      <c r="EJ30" t="n">
+        <v>0.2149325972074081</v>
+      </c>
+      <c r="EK30" t="n">
+        <v>0.2607992487733423</v>
+      </c>
+      <c r="EL30" t="n">
+        <v>0.1174435611577341</v>
+      </c>
+      <c r="EM30" t="n">
+        <v>0.1251033910935072</v>
+      </c>
+      <c r="EN30" t="n">
+        <v>0.2411456356310824</v>
+      </c>
+      <c r="EO30" t="n">
+        <v>0.1737508199894172</v>
+      </c>
+      <c r="EP30" t="n">
+        <v>0.1979567737169052</v>
+      </c>
+      <c r="EQ30" t="n">
+        <v>0.5096351737412246</v>
+      </c>
+      <c r="ER30" t="n">
+        <v>0.1056771759121067</v>
+      </c>
+      <c r="ES30" t="n">
+        <v>0.3051810422788489</v>
+      </c>
+      <c r="ET30" t="n">
+        <v>0.1267384856385838</v>
+      </c>
+      <c r="EU30" t="n">
+        <v>0.1678358392458701</v>
+      </c>
+      <c r="EV30" t="n">
+        <v>0.2160564724493847</v>
+      </c>
+      <c r="EW30" t="n">
+        <v>0.2901267493107712</v>
+      </c>
+      <c r="EX30" t="n">
+        <v>0.4825267529811205</v>
+      </c>
+      <c r="EY30" t="n">
+        <v>0.1912507943799927</v>
+      </c>
+      <c r="EZ30" t="n">
+        <v>0.2299073995921361</v>
+      </c>
+      <c r="FA30" t="n">
+        <v>0.6040379981515454</v>
+      </c>
+      <c r="FB30" t="n">
+        <v>0.3472834145345711</v>
+      </c>
+      <c r="FC30" t="n">
+        <v>0.1814429538253948</v>
+      </c>
+      <c r="FD30" t="n">
+        <v>0.5064178223649043</v>
+      </c>
+      <c r="FE30" t="n">
+        <v>0.2353122938466802</v>
+      </c>
+      <c r="FF30" t="n">
+        <v>0.2982229918419234</v>
+      </c>
+      <c r="FG30" t="n">
+        <v>0.4938842440485948</v>
+      </c>
+      <c r="FH30" t="n">
+        <v>0.259208079909035</v>
+      </c>
+      <c r="FI30" t="n">
+        <v>0.4179291331676757</v>
+      </c>
+      <c r="FJ30" t="n">
+        <v>0.4677443290854234</v>
+      </c>
+      <c r="FK30" t="n">
+        <v>0.2974554397681122</v>
+      </c>
+      <c r="FL30" t="n">
+        <v>0.4876773866133965</v>
+      </c>
+      <c r="FM30" t="n">
+        <v>0.2790057725811907</v>
+      </c>
+      <c r="FN30" t="n">
+        <v>0.4184858891158346</v>
+      </c>
+      <c r="FO30" t="n">
+        <v>0.343623280230235</v>
+      </c>
+      <c r="FP30" t="n">
+        <v>0.354935920349032</v>
+      </c>
+      <c r="FQ30" t="n">
+        <v>0.6109720989678158</v>
+      </c>
+      <c r="FR30" t="n">
+        <v>0.3274162225113725</v>
+      </c>
+      <c r="FS30" t="n">
+        <v>0.1044669772822153</v>
+      </c>
+      <c r="FT30" t="n">
+        <v>0.2760313720959339</v>
+      </c>
+      <c r="FU30" t="n">
+        <v>0.1162756674113925</v>
+      </c>
+      <c r="FV30" t="n">
+        <v>0.1363138884794859</v>
+      </c>
+      <c r="FW30" t="n">
+        <v>0.09394648181636869</v>
+      </c>
+      <c r="FX30" t="n">
+        <v>0.1288173721960441</v>
+      </c>
+      <c r="FY30" t="n">
+        <v>0.1024482243971911</v>
+      </c>
+      <c r="FZ30" t="n">
+        <v>0.4754650313925153</v>
+      </c>
+      <c r="GA30" t="n">
+        <v>0.1118261874222276</v>
+      </c>
+      <c r="GB30" t="n">
+        <v>0.3286561365150883</v>
+      </c>
+      <c r="GC30" t="n">
+        <v>0.1009638720897075</v>
+      </c>
+      <c r="GD30" t="n">
+        <v>0.1730004583603095</v>
+      </c>
+      <c r="GE30" t="n">
+        <v>0.2171421228281025</v>
+      </c>
+      <c r="GF30" t="n">
+        <v>0.1317555601015199</v>
+      </c>
+      <c r="GG30" t="n">
+        <v>0.2468421547522539</v>
+      </c>
+      <c r="GH30" t="n">
+        <v>0.07178526815377165</v>
+      </c>
+      <c r="GI30" t="n">
+        <v>0.1086889534538944</v>
+      </c>
+      <c r="GJ30" t="n">
+        <v>0.08047861123160222</v>
+      </c>
+      <c r="GK30" t="n">
+        <v>0.1014126656419303</v>
+      </c>
+      <c r="GL30" t="n">
+        <v>0.2504941886696651</v>
+      </c>
+      <c r="GM30" t="n">
+        <v>0.4577242751635914</v>
+      </c>
+      <c r="GN30" t="n">
+        <v>0.2490513366238351</v>
+      </c>
+      <c r="GO30" t="n">
+        <v>0.2472757607108441</v>
+      </c>
+      <c r="GP30" t="n">
+        <v>0.4372630705152483</v>
+      </c>
+      <c r="GQ30" t="n">
+        <v>0.3982638520684514</v>
+      </c>
+      <c r="GR30" t="n">
+        <v>0.23679319885618</v>
+      </c>
+      <c r="GS30" t="n">
+        <v>0.2516600133451777</v>
+      </c>
+      <c r="GT30" t="n">
+        <v>0.4244355732171524</v>
+      </c>
+      <c r="GU30" t="n">
+        <v>0.3751532275858158</v>
+      </c>
+      <c r="GV30" t="n">
+        <v>0.2622917872578561</v>
+      </c>
+      <c r="GW30" t="n">
+        <v>0.2390512395869803</v>
+      </c>
+      <c r="GX30" t="n">
+        <v>0.3104239950735746</v>
+      </c>
+      <c r="GY30" t="n">
+        <v>0.224045342299537</v>
+      </c>
+      <c r="GZ30" t="n">
+        <v>0.6474836470195418</v>
+      </c>
+      <c r="HA30" t="n">
+        <v>0.3794961662130142</v>
+      </c>
+      <c r="HB30" t="n">
+        <v>0.3134817242168209</v>
+      </c>
+      <c r="HC30" t="n">
+        <v>0.3660502743706082</v>
+      </c>
+      <c r="HD30" t="n">
+        <v>0.2766641876236787</v>
+      </c>
+      <c r="HE30" t="n">
+        <v>0.2387772557454288</v>
+      </c>
+      <c r="HF30" t="n">
+        <v>0.28835799261565</v>
+      </c>
+      <c r="HG30" t="n">
+        <v>0.3934476691344815</v>
+      </c>
+      <c r="HH30" t="n">
+        <v>0.5555206120405103</v>
+      </c>
+      <c r="HI30" t="n">
+        <v>0.2948630320547556</v>
+      </c>
+      <c r="HJ30" t="n">
+        <v>0.1429800254486978</v>
+      </c>
+      <c r="HK30" t="n">
+        <v>0.4216406197899898</v>
+      </c>
+      <c r="HL30" t="n">
+        <v>0.2106097662032876</v>
+      </c>
+      <c r="HM30" t="n">
+        <v>0.1562416011442276</v>
+      </c>
+      <c r="HN30" t="n">
+        <v>0.4166842734419174</v>
+      </c>
+      <c r="HO30" t="n">
+        <v>0.2046597149556486</v>
+      </c>
+      <c r="HP30" t="n">
+        <v>0.5081569877427251</v>
+      </c>
+      <c r="HQ30" t="n">
+        <v>0.1183296027959784</v>
+      </c>
+      <c r="HR30" t="n">
+        <v>0.1500230596532592</v>
+      </c>
+      <c r="HS30" t="n">
+        <v>0.1783342722128243</v>
+      </c>
+      <c r="HT30" t="n">
+        <v>0.2298639572533895</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>SEIZURE_AVG</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Subset</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.5389507917485223</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.4389108501795393</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.2679992876840234</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.4898031485481884</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.285575778533862</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.451165536060141</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.122110271215733</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.122410930268127</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.1005644597404472</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.2214529730605854</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.1775465163519948</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.1286969635910453</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.125033260175089</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.08353439276380174</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.08344692186408711</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.09561261334341876</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.1080324673727871</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0.1068067199074662</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0.2776347026440291</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0.4370525809993802</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0.2953352470663844</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0.480544495609291</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0.4832624238909353</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0.09745252212192529</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0.1875854943458425</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0.1128212608665298</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0.1665012984495374</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.2526340181600691</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0.1146398731502181</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0.151174652210637</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0.07548822768702042</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0.1019875070144009</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0.08227552774582297</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0.1063597004235863</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0.116191160510121</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>0.2010318874707814</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>0.4491571449953281</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>0.1749058621345702</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0.4001259050673582</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>0.2847344139847801</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0.1084759530946289</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>0.1794770854909833</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0.2238925426166972</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>0.1098748277190012</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>0.1336477394891732</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>0.08971907358177411</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>0.1170459434871753</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>0.07270422461900607</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>0.1127691723245217</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>0.09306154687240255</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>0.0846994621261844</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>0.1629346137451153</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>0.4879085429770776</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>0.509192362158056</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>0.08984271878005365</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>0.4702031406735619</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>0.2347863358269689</v>
+      </c>
+      <c r="BH31" t="n">
+        <v>0.1078595338429901</v>
+      </c>
+      <c r="BI31" t="n">
+        <v>0.2815859630210135</v>
+      </c>
+      <c r="BJ31" t="n">
+        <v>0.08806400399614768</v>
+      </c>
+      <c r="BK31" t="n">
+        <v>0.1696549864540814</v>
+      </c>
+      <c r="BL31" t="n">
+        <v>0.07178437051907395</v>
+      </c>
+      <c r="BM31" t="n">
+        <v>0.1615840873594215</v>
+      </c>
+      <c r="BN31" t="n">
+        <v>0.1132564808742714</v>
+      </c>
+      <c r="BO31" t="n">
+        <v>0.08906173179893061</v>
+      </c>
+      <c r="BP31" t="n">
+        <v>0.1073371117672016</v>
+      </c>
+      <c r="BQ31" t="n">
+        <v>0.2525285621323308</v>
+      </c>
+      <c r="BR31" t="n">
+        <v>0.2313255032485828</v>
+      </c>
+      <c r="BS31" t="n">
+        <v>0.2312721893437407</v>
+      </c>
+      <c r="BT31" t="n">
+        <v>0.1050531826262229</v>
+      </c>
+      <c r="BU31" t="n">
+        <v>0.08899998076233115</v>
+      </c>
+      <c r="BV31" t="n">
+        <v>0.5140335249469853</v>
+      </c>
+      <c r="BW31" t="n">
+        <v>0.2024630006149873</v>
+      </c>
+      <c r="BX31" t="n">
+        <v>0.2545307889156721</v>
+      </c>
+      <c r="BY31" t="n">
+        <v>0.1618319062350224</v>
+      </c>
+      <c r="BZ31" t="n">
+        <v>0.1465047464320747</v>
+      </c>
+      <c r="CA31" t="n">
+        <v>0.09645454831826142</v>
+      </c>
+      <c r="CB31" t="n">
+        <v>0.09101619811464029</v>
+      </c>
+      <c r="CC31" t="n">
+        <v>0.1740917956801854</v>
+      </c>
+      <c r="CD31" t="n">
+        <v>0.1473907205722511</v>
+      </c>
+      <c r="CE31" t="n">
+        <v>0.2929018142345378</v>
+      </c>
+      <c r="CF31" t="n">
+        <v>0.08977118360050901</v>
+      </c>
+      <c r="CG31" t="n">
+        <v>0.3191610827250771</v>
+      </c>
+      <c r="CH31" t="n">
+        <v>0.1164396879553668</v>
+      </c>
+      <c r="CI31" t="n">
+        <v>0.1946044142908493</v>
+      </c>
+      <c r="CJ31" t="n">
+        <v>0.5383816332600616</v>
+      </c>
+      <c r="CK31" t="n">
+        <v>0.1500632078397176</v>
+      </c>
+      <c r="CL31" t="n">
+        <v>0.2744678550045164</v>
+      </c>
+      <c r="CM31" t="n">
+        <v>0.09073076003632491</v>
+      </c>
+      <c r="CN31" t="n">
+        <v>0.1815887373377319</v>
+      </c>
+      <c r="CO31" t="n">
+        <v>0.1018697718643029</v>
+      </c>
+      <c r="CP31" t="n">
+        <v>0.1421984818812732</v>
+      </c>
+      <c r="CQ31" t="n">
+        <v>0.1741567246855945</v>
+      </c>
+      <c r="CR31" t="n">
+        <v>0.1565703658823871</v>
+      </c>
+      <c r="CS31" t="n">
+        <v>0.2330585862841819</v>
+      </c>
+      <c r="CT31" t="n">
+        <v>0.2554079519133478</v>
+      </c>
+      <c r="CU31" t="n">
+        <v>0.1276677105090764</v>
+      </c>
+      <c r="CV31" t="n">
+        <v>0.1655759707990809</v>
+      </c>
+      <c r="CW31" t="n">
+        <v>0.09063380728813362</v>
+      </c>
+      <c r="CX31" t="n">
+        <v>0.1107506551416857</v>
+      </c>
+      <c r="CY31" t="n">
+        <v>0.08882052116052563</v>
+      </c>
+      <c r="CZ31" t="n">
+        <v>0.09621196854427345</v>
+      </c>
+      <c r="DA31" t="n">
+        <v>0.1212737411949433</v>
+      </c>
+      <c r="DB31" t="n">
+        <v>0.08123795099879605</v>
+      </c>
+      <c r="DC31" t="n">
+        <v>0.08579762793113231</v>
+      </c>
+      <c r="DD31" t="n">
+        <v>0.1185764685367329</v>
+      </c>
+      <c r="DE31" t="n">
+        <v>0.2876463842891168</v>
+      </c>
+      <c r="DF31" t="n">
+        <v>0.3227684310852456</v>
+      </c>
+      <c r="DG31" t="n">
+        <v>0.1063769707116455</v>
+      </c>
+      <c r="DH31" t="n">
+        <v>0.3521471191703363</v>
+      </c>
+      <c r="DI31" t="n">
+        <v>0.1449017401525906</v>
+      </c>
+      <c r="DJ31" t="n">
+        <v>0.5025384178014219</v>
+      </c>
+      <c r="DK31" t="n">
+        <v>0.1732027453165191</v>
+      </c>
+      <c r="DL31" t="n">
+        <v>0.2448253739065577</v>
+      </c>
+      <c r="DM31" t="n">
+        <v>0.2929579954086876</v>
+      </c>
+      <c r="DN31" t="n">
+        <v>0.1765087297085652</v>
+      </c>
+      <c r="DO31" t="n">
+        <v>0.3331464640318076</v>
+      </c>
+      <c r="DP31" t="n">
+        <v>0.1081512537900472</v>
+      </c>
+      <c r="DQ31" t="n">
+        <v>0.3642803452260555</v>
+      </c>
+      <c r="DR31" t="n">
+        <v>0.1227522512384544</v>
+      </c>
+      <c r="DS31" t="n">
+        <v>0.3536096074422266</v>
+      </c>
+      <c r="DT31" t="n">
+        <v>0.1337784305378721</v>
+      </c>
+      <c r="DU31" t="n">
+        <v>0.5144035615669766</v>
+      </c>
+      <c r="DV31" t="n">
+        <v>0.2410063983503876</v>
+      </c>
+      <c r="DW31" t="n">
+        <v>0.1559606302176018</v>
+      </c>
+      <c r="DX31" t="n">
+        <v>0.2196386985504553</v>
+      </c>
+      <c r="DY31" t="n">
+        <v>0.09558571342182019</v>
+      </c>
+      <c r="DZ31" t="n">
+        <v>0.1080123163577278</v>
+      </c>
+      <c r="EA31" t="n">
+        <v>0.1097605639921837</v>
+      </c>
+      <c r="EB31" t="n">
+        <v>0.1303476366954107</v>
+      </c>
+      <c r="EC31" t="n">
+        <v>0.2210683414497735</v>
+      </c>
+      <c r="ED31" t="n">
+        <v>0.2397254394854972</v>
+      </c>
+      <c r="EE31" t="n">
+        <v>0.2789434851412195</v>
+      </c>
+      <c r="EF31" t="n">
+        <v>0.1159140151741253</v>
+      </c>
+      <c r="EG31" t="n">
+        <v>0.1265897893834763</v>
+      </c>
+      <c r="EH31" t="n">
+        <v>0.2263058343238356</v>
+      </c>
+      <c r="EI31" t="n">
+        <v>0.4961366228383176</v>
+      </c>
+      <c r="EJ31" t="n">
+        <v>0.2103942478049337</v>
+      </c>
+      <c r="EK31" t="n">
+        <v>0.2919289324260866</v>
+      </c>
+      <c r="EL31" t="n">
+        <v>0.1349755141614139</v>
+      </c>
+      <c r="EM31" t="n">
+        <v>0.1228744666118435</v>
+      </c>
+      <c r="EN31" t="n">
+        <v>0.2921426445652299</v>
+      </c>
+      <c r="EO31" t="n">
+        <v>0.203407936630338</v>
+      </c>
+      <c r="EP31" t="n">
+        <v>0.2057966731254355</v>
+      </c>
+      <c r="EQ31" t="n">
+        <v>0.5144509703822402</v>
+      </c>
+      <c r="ER31" t="n">
+        <v>0.1269827947808667</v>
+      </c>
+      <c r="ES31" t="n">
+        <v>0.3177280980767536</v>
+      </c>
+      <c r="ET31" t="n">
+        <v>0.1457124274422408</v>
+      </c>
+      <c r="EU31" t="n">
+        <v>0.2026749211585894</v>
+      </c>
+      <c r="EV31" t="n">
+        <v>0.2739953851629793</v>
+      </c>
+      <c r="EW31" t="n">
+        <v>0.2879996755596843</v>
+      </c>
+      <c r="EX31" t="n">
+        <v>0.489430069329072</v>
+      </c>
+      <c r="EY31" t="n">
+        <v>0.2137510413229325</v>
+      </c>
+      <c r="EZ31" t="n">
+        <v>0.2167791427578541</v>
+      </c>
+      <c r="FA31" t="n">
+        <v>0.6306793214841838</v>
+      </c>
+      <c r="FB31" t="n">
+        <v>0.3566251156937379</v>
+      </c>
+      <c r="FC31" t="n">
+        <v>0.2097078958569407</v>
+      </c>
+      <c r="FD31" t="n">
+        <v>0.5479229653441314</v>
+      </c>
+      <c r="FE31" t="n">
+        <v>0.2428193067813328</v>
+      </c>
+      <c r="FF31" t="n">
+        <v>0.3618989292832018</v>
+      </c>
+      <c r="FG31" t="n">
+        <v>0.5889638127774788</v>
+      </c>
+      <c r="FH31" t="n">
+        <v>0.2566975592691529</v>
+      </c>
+      <c r="FI31" t="n">
+        <v>0.3666010699041772</v>
+      </c>
+      <c r="FJ31" t="n">
+        <v>0.4708280166132277</v>
+      </c>
+      <c r="FK31" t="n">
+        <v>0.2977044765524611</v>
+      </c>
+      <c r="FL31" t="n">
+        <v>0.4824327196311715</v>
+      </c>
+      <c r="FM31" t="n">
+        <v>0.3253800682730009</v>
+      </c>
+      <c r="FN31" t="n">
+        <v>0.4591865187439024</v>
+      </c>
+      <c r="FO31" t="n">
+        <v>0.285041498056089</v>
+      </c>
+      <c r="FP31" t="n">
+        <v>0.2901692667262084</v>
+      </c>
+      <c r="FQ31" t="n">
+        <v>0.6077605665945239</v>
+      </c>
+      <c r="FR31" t="n">
+        <v/>
+      </c>
+      <c r="FS31" t="n">
+        <v/>
+      </c>
+      <c r="FT31" t="n">
+        <v/>
+      </c>
+      <c r="FU31" t="n">
+        <v/>
+      </c>
+      <c r="FV31" t="n">
+        <v/>
+      </c>
+      <c r="FW31" t="n">
+        <v/>
+      </c>
+      <c r="FX31" t="n">
+        <v/>
+      </c>
+      <c r="FY31" t="n">
+        <v/>
+      </c>
+      <c r="FZ31" t="n">
+        <v/>
+      </c>
+      <c r="GA31" t="n">
+        <v/>
+      </c>
+      <c r="GB31" t="n">
+        <v/>
+      </c>
+      <c r="GC31" t="n">
+        <v/>
+      </c>
+      <c r="GD31" t="n">
+        <v/>
+      </c>
+      <c r="GE31" t="n">
+        <v/>
+      </c>
+      <c r="GF31" t="n">
+        <v/>
+      </c>
+      <c r="GG31" t="n">
+        <v/>
+      </c>
+      <c r="GH31" t="n">
+        <v/>
+      </c>
+      <c r="GI31" t="n">
+        <v/>
+      </c>
+      <c r="GJ31" t="n">
+        <v/>
+      </c>
+      <c r="GK31" t="n">
+        <v/>
+      </c>
+      <c r="GL31" t="n">
+        <v/>
+      </c>
+      <c r="GM31" t="n">
+        <v/>
+      </c>
+      <c r="GN31" t="n">
+        <v/>
+      </c>
+      <c r="GO31" t="n">
+        <v/>
+      </c>
+      <c r="GP31" t="n">
+        <v/>
+      </c>
+      <c r="GQ31" t="n">
+        <v/>
+      </c>
+      <c r="GR31" t="n">
+        <v/>
+      </c>
+      <c r="GS31" t="n">
+        <v/>
+      </c>
+      <c r="GT31" t="n">
+        <v/>
+      </c>
+      <c r="GU31" t="n">
+        <v/>
+      </c>
+      <c r="GV31" t="n">
+        <v/>
+      </c>
+      <c r="GW31" t="n">
+        <v/>
+      </c>
+      <c r="GX31" t="n">
+        <v/>
+      </c>
+      <c r="GY31" t="n">
+        <v/>
+      </c>
+      <c r="GZ31" t="n">
+        <v/>
+      </c>
+      <c r="HA31" t="n">
+        <v/>
+      </c>
+      <c r="HB31" t="n">
+        <v/>
+      </c>
+      <c r="HC31" t="n">
+        <v/>
+      </c>
+      <c r="HD31" t="n">
+        <v/>
+      </c>
+      <c r="HE31" t="n">
+        <v/>
+      </c>
+      <c r="HF31" t="n">
+        <v/>
+      </c>
+      <c r="HG31" t="n">
+        <v/>
+      </c>
+      <c r="HH31" t="n">
+        <v/>
+      </c>
+      <c r="HI31" t="n">
+        <v/>
+      </c>
+      <c r="HJ31" t="n">
+        <v/>
+      </c>
+      <c r="HK31" t="n">
+        <v/>
+      </c>
+      <c r="HL31" t="n">
+        <v/>
+      </c>
+      <c r="HM31" t="n">
+        <v/>
+      </c>
+      <c r="HN31" t="n">
+        <v/>
+      </c>
+      <c r="HO31" t="n">
+        <v/>
+      </c>
+      <c r="HP31" t="n">
+        <v/>
+      </c>
+      <c r="HQ31" t="n">
+        <v/>
+      </c>
+      <c r="HR31" t="n">
+        <v/>
+      </c>
+      <c r="HS31" t="n">
+        <v/>
+      </c>
+      <c r="HT31" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>APRAXIA_AVG</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Subset</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.5197589340020333</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.4405541009113773</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.2795985708831946</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.4709395880972277</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.281557964198838</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.4026023152818521</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.127291161608716</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.1185329928891904</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.09479705430941389</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.1978873819293548</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.1549891440608101</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.1220787729519893</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.1162283214826352</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.07417120080865756</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.08050161029073323</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0.07329700993578717</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0.1000839594537052</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0.09967535613898439</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0.2559920330466665</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0.5017979173491004</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0.2630498500395998</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0.5089989118766259</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0.4553432310226893</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0.08446683472227647</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0.1880402469531765</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0.1051784554358021</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0.1414090005716983</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.2279017011688546</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0.105275073755338</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0.1425715639230015</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0.06610388265474035</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0.1058238642687317</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0.07235948771241835</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0.09774791940655676</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0.1084639364468824</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0.2056990652472348</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0.439654814760529</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>0.1623289981242348</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0.3721898530019064</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>0.2831675972454784</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0.1084836241665964</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>0.1633725606545576</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>0.2468480861743821</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>0.1248835771532341</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>0.1419471937057552</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>0.1025641504276091</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>0.1200797339967901</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>0.08736301253717006</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>0.1117892286719333</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>0.09705513111054712</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>0.08960839083931722</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>0.1643961072131863</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>0.4733015507944575</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>0.5129357249527153</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>0.0873494981382153</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>0.3841043645864499</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>0.2015932013180955</v>
+      </c>
+      <c r="BH32" t="n">
+        <v>0.1216660511025325</v>
+      </c>
+      <c r="BI32" t="n">
+        <v>0.3005572858562007</v>
+      </c>
+      <c r="BJ32" t="n">
+        <v>0.09868745586729226</v>
+      </c>
+      <c r="BK32" t="n">
+        <v>0.1799862809748428</v>
+      </c>
+      <c r="BL32" t="n">
+        <v>0.08135765230377502</v>
+      </c>
+      <c r="BM32" t="n">
+        <v>0.1937240638014039</v>
+      </c>
+      <c r="BN32" t="n">
+        <v>0.1140180598985253</v>
+      </c>
+      <c r="BO32" t="n">
+        <v>0.0967136795357217</v>
+      </c>
+      <c r="BP32" t="n">
+        <v>0.1183696511200116</v>
+      </c>
+      <c r="BQ32" t="n">
+        <v>0.2324263025951696</v>
+      </c>
+      <c r="BR32" t="n">
+        <v>0.2144368475288885</v>
+      </c>
+      <c r="BS32" t="n">
+        <v>0.2545734758475376</v>
+      </c>
+      <c r="BT32" t="n">
+        <v>0.1132437625822421</v>
+      </c>
+      <c r="BU32" t="n">
+        <v>0.1006397704201662</v>
+      </c>
+      <c r="BV32" t="n">
+        <v>0.5045126859951725</v>
+      </c>
+      <c r="BW32" t="n">
+        <v>0.2082970158604573</v>
+      </c>
+      <c r="BX32" t="n">
+        <v>0.2610426084735069</v>
+      </c>
+      <c r="BY32" t="n">
+        <v>0.1795408441140272</v>
+      </c>
+      <c r="BZ32" t="n">
+        <v>0.1541873722329136</v>
+      </c>
+      <c r="CA32" t="n">
+        <v>0.1092709246767708</v>
+      </c>
+      <c r="CB32" t="n">
+        <v>0.09246947899469449</v>
+      </c>
+      <c r="CC32" t="n">
+        <v>0.1790775121047053</v>
+      </c>
+      <c r="CD32" t="n">
+        <v>0.1592192836922677</v>
+      </c>
+      <c r="CE32" t="n">
+        <v>0.2665219037212395</v>
+      </c>
+      <c r="CF32" t="n">
+        <v>0.08963941333534048</v>
+      </c>
+      <c r="CG32" t="n">
+        <v>0.3165822864336819</v>
+      </c>
+      <c r="CH32" t="n">
+        <v>0.1204699815103143</v>
+      </c>
+      <c r="CI32" t="n">
+        <v>0.1888098646473533</v>
+      </c>
+      <c r="CJ32" t="n">
+        <v>0.5109073252037415</v>
+      </c>
+      <c r="CK32" t="n">
+        <v>0.1644631670856127</v>
+      </c>
+      <c r="CL32" t="n">
+        <v>0.3039042004834285</v>
+      </c>
+      <c r="CM32" t="n">
+        <v>0.1113042834359441</v>
+      </c>
+      <c r="CN32" t="n">
+        <v>0.2185755282754565</v>
+      </c>
+      <c r="CO32" t="n">
+        <v>0.1108939441612987</v>
+      </c>
+      <c r="CP32" t="n">
+        <v>0.1754217636418991</v>
+      </c>
+      <c r="CQ32" t="n">
+        <v>0.2194631511168099</v>
+      </c>
+      <c r="CR32" t="n">
+        <v>0.1305315026117434</v>
+      </c>
+      <c r="CS32" t="n">
+        <v>0.2006904796974717</v>
+      </c>
+      <c r="CT32" t="n">
+        <v>0.1981673268273867</v>
+      </c>
+      <c r="CU32" t="n">
+        <v>0.1242133687871559</v>
+      </c>
+      <c r="CV32" t="n">
+        <v>0.1637274034985089</v>
+      </c>
+      <c r="CW32" t="n">
+        <v>0.08651508730112004</v>
+      </c>
+      <c r="CX32" t="n">
+        <v>0.1096740867096775</v>
+      </c>
+      <c r="CY32" t="n">
+        <v>0.09127998549334371</v>
+      </c>
+      <c r="CZ32" t="n">
+        <v>0.1024485770091396</v>
+      </c>
+      <c r="DA32" t="n">
+        <v>0.1060475085068363</v>
+      </c>
+      <c r="DB32" t="n">
+        <v>0.07703599246545063</v>
+      </c>
+      <c r="DC32" t="n">
+        <v>0.09105811939298061</v>
+      </c>
+      <c r="DD32" t="n">
+        <v>0.1163971378192939</v>
+      </c>
+      <c r="DE32" t="n">
+        <v>0.2405419203759534</v>
+      </c>
+      <c r="DF32" t="n">
+        <v>0.3369812427351844</v>
+      </c>
+      <c r="DG32" t="n">
+        <v>0.1129908322078403</v>
+      </c>
+      <c r="DH32" t="n">
+        <v>0.2889317675509696</v>
+      </c>
+      <c r="DI32" t="n">
+        <v>0.1266708912229301</v>
+      </c>
+      <c r="DJ32" t="n">
+        <v>0.4711338533609694</v>
+      </c>
+      <c r="DK32" t="n">
+        <v>0.1343206732998055</v>
+      </c>
+      <c r="DL32" t="n">
+        <v>0.1814802770497589</v>
+      </c>
+      <c r="DM32" t="n">
+        <v>0.1967196662719061</v>
+      </c>
+      <c r="DN32" t="n">
+        <v>0.1461009590801535</v>
+      </c>
+      <c r="DO32" t="n">
+        <v>0.2952507953776511</v>
+      </c>
+      <c r="DP32" t="n">
+        <v>0.1264083023035106</v>
+      </c>
+      <c r="DQ32" t="n">
+        <v>0.393506300234801</v>
+      </c>
+      <c r="DR32" t="n">
+        <v>0.1412161967568989</v>
+      </c>
+      <c r="DS32" t="n">
+        <v>0.341593947062144</v>
+      </c>
+      <c r="DT32" t="n">
+        <v>0.1500427486749549</v>
+      </c>
+      <c r="DU32" t="n">
+        <v>0.6104578843535737</v>
+      </c>
+      <c r="DV32" t="n">
+        <v>0.2890772369843512</v>
+      </c>
+      <c r="DW32" t="n">
+        <v>0.1640845583483762</v>
+      </c>
+      <c r="DX32" t="n">
+        <v>0.2225235573745198</v>
+      </c>
+      <c r="DY32" t="n">
+        <v>0.09432720791856264</v>
+      </c>
+      <c r="DZ32" t="n">
+        <v>0.105743395490054</v>
+      </c>
+      <c r="EA32" t="n">
+        <v>0.0918289722909377</v>
+      </c>
+      <c r="EB32" t="n">
+        <v>0.1094002617210036</v>
+      </c>
+      <c r="EC32" t="n">
+        <v>0.1750935651445931</v>
+      </c>
+      <c r="ED32" t="n">
+        <v>0.2012579004166664</v>
+      </c>
+      <c r="EE32" t="n">
+        <v>0.2378903278686159</v>
+      </c>
+      <c r="EF32" t="n">
+        <v>0.09251139336943881</v>
+      </c>
+      <c r="EG32" t="n">
+        <v>0.1063814540481746</v>
+      </c>
+      <c r="EH32" t="n">
+        <v>0.2392974794358589</v>
+      </c>
+      <c r="EI32" t="n">
+        <v>0.4975923107317843</v>
+      </c>
+      <c r="EJ32" t="n">
+        <v>0.2376736188785612</v>
+      </c>
+      <c r="EK32" t="n">
+        <v>0.2743923035432718</v>
+      </c>
+      <c r="EL32" t="n">
+        <v>0.1347020928737858</v>
+      </c>
+      <c r="EM32" t="n">
+        <v>0.1280117876852626</v>
+      </c>
+      <c r="EN32" t="n">
+        <v>0.2888871937179092</v>
+      </c>
+      <c r="EO32" t="n">
+        <v>0.2062555383532666</v>
+      </c>
+      <c r="EP32" t="n">
+        <v>0.2215217198082716</v>
+      </c>
+      <c r="EQ32" t="n">
+        <v>0.5347317222444421</v>
+      </c>
+      <c r="ER32" t="n">
+        <v>0.1188325738826943</v>
+      </c>
+      <c r="ES32" t="n">
+        <v>0.3279044833333073</v>
+      </c>
+      <c r="ET32" t="n">
+        <v>0.1489060321534763</v>
+      </c>
+      <c r="EU32" t="n">
+        <v>0.2076136982529755</v>
+      </c>
+      <c r="EV32" t="n">
+        <v>0.2725344110071027</v>
+      </c>
+      <c r="EW32" t="n">
+        <v>0.3206740955914994</v>
+      </c>
+      <c r="EX32" t="n">
+        <v>0.4659057702003043</v>
+      </c>
+      <c r="EY32" t="n">
+        <v>0.2173890136801589</v>
+      </c>
+      <c r="EZ32" t="n">
+        <v>0.2307667485092695</v>
+      </c>
+      <c r="FA32" t="n">
+        <v>0.6141770105982469</v>
+      </c>
+      <c r="FB32" t="n">
+        <v>0.3646641749071415</v>
+      </c>
+      <c r="FC32" t="n">
+        <v>0.1991260498689253</v>
+      </c>
+      <c r="FD32" t="n">
+        <v>0.5390318038379383</v>
+      </c>
+      <c r="FE32" t="n">
+        <v>0.2663761170254322</v>
+      </c>
+      <c r="FF32" t="n">
+        <v>0.3598712270301658</v>
+      </c>
+      <c r="FG32" t="n">
+        <v>0.5709178779800779</v>
+      </c>
+      <c r="FH32" t="n">
+        <v>0.258385756194169</v>
+      </c>
+      <c r="FI32" t="n">
+        <v>0.3913205816459221</v>
+      </c>
+      <c r="FJ32" t="n">
+        <v>0.4316704862258264</v>
+      </c>
+      <c r="FK32" t="n">
+        <v>0.284455214002864</v>
+      </c>
+      <c r="FL32" t="n">
+        <v>0.4851041019597293</v>
+      </c>
+      <c r="FM32" t="n">
+        <v>0.3097642005143835</v>
+      </c>
+      <c r="FN32" t="n">
+        <v>0.4576373609113898</v>
+      </c>
+      <c r="FO32" t="n">
+        <v>0.3164840386478783</v>
+      </c>
+      <c r="FP32" t="n">
+        <v>0.3459695035983741</v>
+      </c>
+      <c r="FQ32" t="n">
+        <v>0.6182672743888418</v>
+      </c>
+      <c r="FR32" t="n">
+        <v>0.3117566287838964</v>
+      </c>
+      <c r="FS32" t="n">
+        <v>0.1110307534070545</v>
+      </c>
+      <c r="FT32" t="n">
+        <v>0.2748115121490469</v>
+      </c>
+      <c r="FU32" t="n">
+        <v>0.12264279528853</v>
+      </c>
+      <c r="FV32" t="n">
+        <v>0.1254315813524578</v>
+      </c>
+      <c r="FW32" t="n">
+        <v>0.09183118402925938</v>
+      </c>
+      <c r="FX32" t="n">
+        <v>0.131552418747409</v>
+      </c>
+      <c r="FY32" t="n">
+        <v>0.1117076090319409</v>
+      </c>
+      <c r="FZ32" t="n">
+        <v>0.4784885298419999</v>
+      </c>
+      <c r="GA32" t="n">
+        <v>0.118721538350443</v>
+      </c>
+      <c r="GB32" t="n">
+        <v>0.3479846484671863</v>
+      </c>
+      <c r="GC32" t="n">
+        <v>0.1032709674040674</v>
+      </c>
+      <c r="GD32" t="n">
+        <v>0.1691056869125412</v>
+      </c>
+      <c r="GE32" t="n">
+        <v>0.2120080117357159</v>
+      </c>
+      <c r="GF32" t="n">
+        <v>0.1493730836574212</v>
+      </c>
+      <c r="GG32" t="n">
+        <v>0.2370973105236895</v>
+      </c>
+      <c r="GH32" t="n">
+        <v>0.0773113842355202</v>
+      </c>
+      <c r="GI32" t="n">
+        <v>0.1111724535995281</v>
+      </c>
+      <c r="GJ32" t="n">
+        <v>0.08385664334600258</v>
+      </c>
+      <c r="GK32" t="n">
+        <v>0.09601005929545392</v>
+      </c>
+      <c r="GL32" t="n">
+        <v>0.2436286572841015</v>
+      </c>
+      <c r="GM32" t="n">
+        <v>0.4687562005905332</v>
+      </c>
+      <c r="GN32" t="n">
+        <v>0.2524646176891746</v>
+      </c>
+      <c r="GO32" t="n">
+        <v>0.2431877594517942</v>
+      </c>
+      <c r="GP32" t="n">
+        <v>0.4289720339836766</v>
+      </c>
+      <c r="GQ32" t="n">
+        <v>0.3867248719302253</v>
+      </c>
+      <c r="GR32" t="n">
+        <v>0.2259114716218133</v>
+      </c>
+      <c r="GS32" t="n">
+        <v>0.2366142442567223</v>
+      </c>
+      <c r="GT32" t="n">
+        <v>0.3967865028235709</v>
+      </c>
+      <c r="GU32" t="n">
+        <v>0.3724882285816841</v>
+      </c>
+      <c r="GV32" t="n">
+        <v>0.2786613719803122</v>
+      </c>
+      <c r="GW32" t="n">
+        <v>0.2458886770978121</v>
+      </c>
+      <c r="GX32" t="n">
+        <v>0.3148190703984228</v>
+      </c>
+      <c r="GY32" t="n">
+        <v>0.2382832050877674</v>
+      </c>
+      <c r="GZ32" t="n">
+        <v>0.6475484588050777</v>
+      </c>
+      <c r="HA32" t="n">
+        <v>0.3963265417661735</v>
+      </c>
+      <c r="HB32" t="n">
+        <v>0.2995309788285606</v>
+      </c>
+      <c r="HC32" t="n">
+        <v>0.3664835988332257</v>
+      </c>
+      <c r="HD32" t="n">
+        <v>0.2609255203944419</v>
+      </c>
+      <c r="HE32" t="n">
+        <v>0.2513547765743049</v>
+      </c>
+      <c r="HF32" t="n">
+        <v>0.3074932796678707</v>
+      </c>
+      <c r="HG32" t="n">
+        <v>0.4080560954527206</v>
+      </c>
+      <c r="HH32" t="n">
+        <v>0.5633847369927325</v>
+      </c>
+      <c r="HI32" t="n">
+        <v>0.3247725360461501</v>
+      </c>
+      <c r="HJ32" t="n">
+        <v>0.1592437356523549</v>
+      </c>
+      <c r="HK32" t="n">
+        <v>0.4432690812094967</v>
+      </c>
+      <c r="HL32" t="n">
+        <v>0.2199667624168688</v>
+      </c>
+      <c r="HM32" t="n">
+        <v>0.1731737895766672</v>
+      </c>
+      <c r="HN32" t="n">
+        <v>0.4333447380846854</v>
+      </c>
+      <c r="HO32" t="n">
+        <v>0.2252746441295403</v>
+      </c>
+      <c r="HP32" t="n">
+        <v>0.499791298166353</v>
+      </c>
+      <c r="HQ32" t="n">
+        <v>0.1312458629866507</v>
+      </c>
+      <c r="HR32" t="n">
+        <v>0.1569436722807048</v>
+      </c>
+      <c r="HS32" t="n">
+        <v>0.1944075320217598</v>
+      </c>
+      <c r="HT32" t="n">
+        <v>0.2217077123109459</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>NON_APRAXIA_AVG</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Subset</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.5034395826894403</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.4180392867583486</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.2395546834128387</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.4406883861666807</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.263187338328823</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.4276020789197268</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.1279105333890501</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.1052941669581152</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.1148158773766588</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.2023668158796315</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.1501644168496546</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.1160356367885148</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.1009187903430639</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0.07913946570406895</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0.06975864853901781</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0.08923348484772101</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0.09351311820473859</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0.08751109763330853</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0.2692283880817198</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0.3713401308217782</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0.2590801270180299</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0.4550389500827087</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0.4437353635448892</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0.09854032826560508</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0.1592609758202642</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0.124287392773864</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0.1511858305290154</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.2150788111280199</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0.1015544225961981</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0.1244108684452756</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0.06733203415573615</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0.08733952446782235</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0.06991879017947708</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0.09040958931847604</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>0.09648553843083613</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>0.2019239753678152</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>0.4177594989917276</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>0.1757514712293529</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0.3928878524745549</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>0.2714385082382356</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0.09307823898615997</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>0.16869014817888</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>0.2105847544806475</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>0.09429140731870035</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>0.1241117625962431</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>0.06790336020739449</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>0.1170397589895838</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>0.05071170003649602</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>0.1114069512931057</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>0.08265464839915139</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>0.07063050504210183</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>0.1433761711778185</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>0.4398271912959096</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>0.4811988790613185</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>0.091772980997901</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>0.4317741664473583</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>0.2562836633480885</v>
+      </c>
+      <c r="BH33" t="n">
+        <v>0.09352221041563916</v>
+      </c>
+      <c r="BI33" t="n">
+        <v>0.2452134028493199</v>
+      </c>
+      <c r="BJ33" t="n">
+        <v>0.07110874388687101</v>
+      </c>
+      <c r="BK33" t="n">
+        <v>0.1372236612837234</v>
+      </c>
+      <c r="BL33" t="n">
+        <v>0.05717374778923864</v>
+      </c>
+      <c r="BM33" t="n">
+        <v>0.135847021661759</v>
+      </c>
+      <c r="BN33" t="n">
+        <v>0.08615101579555841</v>
+      </c>
+      <c r="BO33" t="n">
+        <v>0.07168412081592804</v>
+      </c>
+      <c r="BP33" t="n">
+        <v>0.08122778155058101</v>
+      </c>
+      <c r="BQ33" t="n">
+        <v>0.2351285262418495</v>
+      </c>
+      <c r="BR33" t="n">
+        <v>0.22431158464028</v>
+      </c>
+      <c r="BS33" t="n">
+        <v>0.222993720910404</v>
+      </c>
+      <c r="BT33" t="n">
+        <v>0.0872953647179987</v>
+      </c>
+      <c r="BU33" t="n">
+        <v>0.09814260677267132</v>
+      </c>
+      <c r="BV33" t="n">
+        <v>0.510778763164046</v>
+      </c>
+      <c r="BW33" t="n">
+        <v>0.1841626759810311</v>
+      </c>
+      <c r="BX33" t="n">
+        <v>0.2390653151296896</v>
+      </c>
+      <c r="BY33" t="n">
+        <v>0.1402861742237073</v>
+      </c>
+      <c r="BZ33" t="n">
+        <v>0.1440891480101868</v>
+      </c>
+      <c r="CA33" t="n">
+        <v>0.08746981673930398</v>
+      </c>
+      <c r="CB33" t="n">
+        <v>0.09349541926910462</v>
+      </c>
+      <c r="CC33" t="n">
+        <v>0.1591998560190805</v>
+      </c>
+      <c r="CD33" t="n">
+        <v>0.1342578568211201</v>
+      </c>
+      <c r="CE33" t="n">
+        <v>0.2885464639554221</v>
+      </c>
+      <c r="CF33" t="n">
+        <v>0.09005869341797494</v>
+      </c>
+      <c r="CG33" t="n">
+        <v>0.2819962397681452</v>
+      </c>
+      <c r="CH33" t="n">
+        <v>0.123390190296681</v>
+      </c>
+      <c r="CI33" t="n">
+        <v>0.1800097300678147</v>
+      </c>
+      <c r="CJ33" t="n">
+        <v>0.4878943277934106</v>
+      </c>
+      <c r="CK33" t="n">
+        <v>0.1304463605370553</v>
+      </c>
+      <c r="CL33" t="n">
+        <v>0.2273583006029515</v>
+      </c>
+      <c r="CM33" t="n">
+        <v>0.07593808704183588</v>
+      </c>
+      <c r="CN33" t="n">
+        <v>0.1558337986536391</v>
+      </c>
+      <c r="CO33" t="n">
+        <v>0.08327864371983043</v>
+      </c>
+      <c r="CP33" t="n">
+        <v>0.1188154618466053</v>
+      </c>
+      <c r="CQ33" t="n">
+        <v>0.1435571311924056</v>
+      </c>
+      <c r="CR33" t="n">
+        <v>0.1574669656116888</v>
+      </c>
+      <c r="CS33" t="n">
+        <v>0.2274099770827237</v>
+      </c>
+      <c r="CT33" t="n">
+        <v>0.290889451446632</v>
+      </c>
+      <c r="CU33" t="n">
+        <v>0.1255725144850414</v>
+      </c>
+      <c r="CV33" t="n">
+        <v>0.1526852549029387</v>
+      </c>
+      <c r="CW33" t="n">
+        <v>0.08418098068078197</v>
+      </c>
+      <c r="CX33" t="n">
+        <v>0.090138420190465</v>
+      </c>
+      <c r="CY33" t="n">
+        <v>0.07892716784255491</v>
+      </c>
+      <c r="CZ33" t="n">
+        <v>0.0761184932671506</v>
+      </c>
+      <c r="DA33" t="n">
+        <v>0.1114748643100724</v>
+      </c>
+      <c r="DB33" t="n">
+        <v>0.07325088243293298</v>
+      </c>
+      <c r="DC33" t="n">
+        <v>0.07440218597524163</v>
+      </c>
+      <c r="DD33" t="n">
+        <v>0.1037262945163738</v>
+      </c>
+      <c r="DE33" t="n">
+        <v>0.2485020604662622</v>
+      </c>
+      <c r="DF33" t="n">
+        <v>0.2988912908968869</v>
+      </c>
+      <c r="DG33" t="n">
+        <v>0.0979054548568813</v>
+      </c>
+      <c r="DH33" t="n">
+        <v>0.3190609683456999</v>
+      </c>
+      <c r="DI33" t="n">
+        <v>0.1233854941126165</v>
+      </c>
+      <c r="DJ33" t="n">
+        <v>0.4489864991099558</v>
+      </c>
+      <c r="DK33" t="n">
+        <v>0.1481851158905633</v>
+      </c>
+      <c r="DL33" t="n">
+        <v>0.2465571421451986</v>
+      </c>
+      <c r="DM33" t="n">
+        <v>0.2584346282808308</v>
+      </c>
+      <c r="DN33" t="n">
+        <v>0.1580458854484627</v>
+      </c>
+      <c r="DO33" t="n">
+        <v>0.3404823339447954</v>
+      </c>
+      <c r="DP33" t="n">
+        <v>0.08942489061870686</v>
+      </c>
+      <c r="DQ33" t="n">
+        <v>0.3348727942956462</v>
+      </c>
+      <c r="DR33" t="n">
+        <v>0.09018124500364443</v>
+      </c>
+      <c r="DS33" t="n">
+        <v>0.3022429278098197</v>
+      </c>
+      <c r="DT33" t="n">
+        <v>0.1009014586031644</v>
+      </c>
+      <c r="DU33" t="n">
+        <v>0.4793467863924633</v>
+      </c>
+      <c r="DV33" t="n">
+        <v>0.198823632472362</v>
+      </c>
+      <c r="DW33" t="n">
+        <v>0.120682206886248</v>
+      </c>
+      <c r="DX33" t="n">
+        <v>0.170539390403133</v>
+      </c>
+      <c r="DY33" t="n">
+        <v>0.09474125223982029</v>
+      </c>
+      <c r="DZ33" t="n">
+        <v>0.1008523090384154</v>
+      </c>
+      <c r="EA33" t="n">
+        <v>0.1035100233503451</v>
+      </c>
+      <c r="EB33" t="n">
+        <v>0.1065307589628308</v>
+      </c>
+      <c r="EC33" t="n">
+        <v>0.2118454580869146</v>
+      </c>
+      <c r="ED33" t="n">
+        <v>0.1980809720901666</v>
+      </c>
+      <c r="EE33" t="n">
+        <v>0.3250580285191191</v>
+      </c>
+      <c r="EF33" t="n">
+        <v>0.1156183825312999</v>
+      </c>
+      <c r="EG33" t="n">
+        <v>0.1069203316996121</v>
+      </c>
+      <c r="EH33" t="n">
+        <v>0.2042623200804223</v>
+      </c>
+      <c r="EI33" t="n">
+        <v>0.4621218992611957</v>
+      </c>
+      <c r="EJ33" t="n">
+        <v>0.1823461664995319</v>
+      </c>
+      <c r="EK33" t="n">
+        <v>0.2828081514984245</v>
+      </c>
+      <c r="EL33" t="n">
+        <v>0.1211960309173353</v>
+      </c>
+      <c r="EM33" t="n">
+        <v>0.1200340172310973</v>
+      </c>
+      <c r="EN33" t="n">
+        <v>0.2542749431805006</v>
+      </c>
+      <c r="EO33" t="n">
+        <v>0.1771194017669656</v>
+      </c>
+      <c r="EP33" t="n">
+        <v>0.1756871655605168</v>
+      </c>
+      <c r="EQ33" t="n">
+        <v>0.482678968366467</v>
+      </c>
+      <c r="ER33" t="n">
+        <v>0.1172734984942139</v>
+      </c>
+      <c r="ES33" t="n">
+        <v>0.2985317067075315</v>
+      </c>
+      <c r="ET33" t="n">
+        <v>0.1276590297592033</v>
+      </c>
+      <c r="EU33" t="n">
+        <v>0.1703587562434665</v>
+      </c>
+      <c r="EV33" t="n">
+        <v>0.2289591317323925</v>
+      </c>
+      <c r="EW33" t="n">
+        <v>0.2499927488546979</v>
+      </c>
+      <c r="EX33" t="n">
+        <v>0.5050792854666016</v>
+      </c>
+      <c r="EY33" t="n">
+        <v>0.1924766686470769</v>
+      </c>
+      <c r="EZ33" t="n">
+        <v>0.2146929030490058</v>
+      </c>
+      <c r="FA33" t="n">
+        <v>0.6242183426154164</v>
+      </c>
+      <c r="FB33" t="n">
+        <v>0.3419166014743412</v>
+      </c>
+      <c r="FC33" t="n">
+        <v>0.1966196036209179</v>
+      </c>
+      <c r="FD33" t="n">
+        <v>0.5227208963163233</v>
+      </c>
+      <c r="FE33" t="n">
+        <v>0.2156125672139213</v>
+      </c>
+      <c r="FF33" t="n">
+        <v>0.3127831113579115</v>
+      </c>
+      <c r="FG33" t="n">
+        <v>0.5291414991120326</v>
+      </c>
+      <c r="FH33" t="n">
+        <v>0.2579346739660588</v>
+      </c>
+      <c r="FI33" t="n">
+        <v>0.4041390979116607</v>
+      </c>
+      <c r="FJ33" t="n">
+        <v>0.5036028439396454</v>
+      </c>
+      <c r="FK33" t="n">
+        <v>0.3094295834196195</v>
+      </c>
+      <c r="FL33" t="n">
+        <v>0.4860863810301074</v>
+      </c>
+      <c r="FM33" t="n">
+        <v>0.3023349127023086</v>
+      </c>
+      <c r="FN33" t="n">
+        <v>0.4280202570907095</v>
+      </c>
+      <c r="FO33" t="n">
+        <v>0.3036086372627955</v>
+      </c>
+      <c r="FP33" t="n">
+        <v>0.291762376439518</v>
+      </c>
+      <c r="FQ33" t="n">
+        <v>0.5989092250160158</v>
+      </c>
+      <c r="FR33" t="n">
+        <v>0.3822248005575389</v>
+      </c>
+      <c r="FS33" t="n">
+        <v>0.08149376084527785</v>
+      </c>
+      <c r="FT33" t="n">
+        <v>0.2803008819100382</v>
+      </c>
+      <c r="FU33" t="n">
+        <v>0.09399071984141101</v>
+      </c>
+      <c r="FV33" t="n">
+        <v>0.1744019634240841</v>
+      </c>
+      <c r="FW33" t="n">
+        <v>0.1013500240712512</v>
+      </c>
+      <c r="FX33" t="n">
+        <v>0.119244709266267</v>
+      </c>
+      <c r="FY33" t="n">
+        <v>0.07004037817556683</v>
+      </c>
+      <c r="FZ33" t="n">
+        <v>0.4648827868193196</v>
+      </c>
+      <c r="GA33" t="n">
+        <v>0.08769245917347389</v>
+      </c>
+      <c r="GB33" t="n">
+        <v>0.2610063446827455</v>
+      </c>
+      <c r="GC33" t="n">
+        <v>0.09288903848944768</v>
+      </c>
+      <c r="GD33" t="n">
+        <v>0.1866321584274984</v>
+      </c>
+      <c r="GE33" t="n">
+        <v>0.2351115116514556</v>
+      </c>
+      <c r="GF33" t="n">
+        <v>0.07009422765586523</v>
+      </c>
+      <c r="GG33" t="n">
+        <v>0.2809491095522288</v>
+      </c>
+      <c r="GH33" t="n">
+        <v>0.05244386186765167</v>
+      </c>
+      <c r="GI33" t="n">
+        <v>0.09999670294417616</v>
+      </c>
+      <c r="GJ33" t="n">
+        <v>0.06865549883120095</v>
+      </c>
+      <c r="GK33" t="n">
+        <v>0.1203217878545977</v>
+      </c>
+      <c r="GL33" t="n">
+        <v>0.2745235485191377</v>
+      </c>
+      <c r="GM33" t="n">
+        <v>0.4191125361692952</v>
+      </c>
+      <c r="GN33" t="n">
+        <v>0.2371048528951469</v>
+      </c>
+      <c r="GO33" t="n">
+        <v>0.2615837651175187</v>
+      </c>
+      <c r="GP33" t="n">
+        <v>0.4662816983757493</v>
+      </c>
+      <c r="GQ33" t="n">
+        <v>0.4386502825522428</v>
+      </c>
+      <c r="GR33" t="n">
+        <v>0.2748792441764633</v>
+      </c>
+      <c r="GS33" t="n">
+        <v>0.3043202051547717</v>
+      </c>
+      <c r="GT33" t="n">
+        <v>0.521207319594688</v>
+      </c>
+      <c r="GU33" t="n">
+        <v>0.3844807241002768</v>
+      </c>
+      <c r="GV33" t="n">
+        <v>0.2049982407292596</v>
+      </c>
+      <c r="GW33" t="n">
+        <v>0.2151202082990689</v>
+      </c>
+      <c r="GX33" t="n">
+        <v>0.2950412314366058</v>
+      </c>
+      <c r="GY33" t="n">
+        <v>0.1742128225407305</v>
+      </c>
+      <c r="GZ33" t="n">
+        <v>0.6472568057701668</v>
+      </c>
+      <c r="HA33" t="n">
+        <v>0.3205898517769569</v>
+      </c>
+      <c r="HB33" t="n">
+        <v>0.3623093330757318</v>
+      </c>
+      <c r="HC33" t="n">
+        <v>0.3645336387514466</v>
+      </c>
+      <c r="HD33" t="n">
+        <v>0.3317495229260075</v>
+      </c>
+      <c r="HE33" t="n">
+        <v>0.1947559328443627</v>
+      </c>
+      <c r="HF33" t="n">
+        <v>0.2213844879328775</v>
+      </c>
+      <c r="HG33" t="n">
+        <v>0.3423181770206443</v>
+      </c>
+      <c r="HH33" t="n">
+        <v>0.5279961747077325</v>
+      </c>
+      <c r="HI33" t="n">
+        <v>0.1901797680848748</v>
+      </c>
+      <c r="HJ33" t="n">
+        <v>0.08605703973589809</v>
+      </c>
+      <c r="HK33" t="n">
+        <v>0.3459410048217156</v>
+      </c>
+      <c r="HL33" t="n">
+        <v>0.1778602794557534</v>
+      </c>
+      <c r="HM33" t="n">
+        <v>0.09697894163068892</v>
+      </c>
+      <c r="HN33" t="n">
+        <v>0.3583726471922296</v>
+      </c>
+      <c r="HO33" t="n">
+        <v>0.1325074628470274</v>
+      </c>
+      <c r="HP33" t="n">
+        <v>0.5374369012600277</v>
+      </c>
+      <c r="HQ33" t="n">
+        <v>0.07312269212862527</v>
+      </c>
+      <c r="HR33" t="n">
+        <v>0.1258009154571996</v>
+      </c>
+      <c r="HS33" t="n">
+        <v>0.1220778628815502</v>
+      </c>
+      <c r="HT33" t="n">
+        <v>0.258410814551942</v>
       </c>
     </row>
   </sheetData>
